--- a/FOA SETS/Youth-Set.xlsx
+++ b/FOA SETS/Youth-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -763,22 +763,22 @@
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALECIA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.
-Product Dimensions: 80 1/2"L X 58 5/8"W X 54"H
-Size: Full
-Features
-- Bell-shape Design
-- Crown Molding
-- Faux Wood Carved Details
-- Nickel Hanging Pulls
-- Felt-lined Top Drawer
-- Foundation Required Included items and dimensions:
-- Nightstand w/ USB: color: White; dimensions: 24" W x 16"D x 24" H; feature: Transitional
-- Dresser: color: White; dimensions: 54" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood.
-Color: White
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALECIA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 58 5/8"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bell-shape Design&lt;br&gt;
+- Crown Molding&lt;br&gt;
+- Faux Wood Carved Details&lt;br&gt;
+- Nickel Hanging Pulls&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand w/ USB: color: White; dimensions: 24" W x 16"D x 24" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 54" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
@@ -904,22 +904,22 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with ALECIA 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and White tones, it blends durability with visual warmth.
-Product Dimensions: 80 1/2"L X 43 5/8"W X 52"H
-Size: Twin
-Features
-- Bell-shape Design
-- Crown Molding
-- Faux Wood Carved Details
-- Nickel Hanging Pulls
-- Felt-lined Top Drawer
-- Foundation Required Included items and dimensions:
-- Nightstand w/ USB: color: White; dimensions: 24" W x 16"D x 24" H; feature: Transitional
-- Dresser: color: White; dimensions: 54" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood.
-Color: White
-Weight: 305.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with ALECIA 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 43 5/8"W X 52"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bell-shape Design&lt;br&gt;
+- Crown Molding&lt;br&gt;
+- Faux Wood Carved Details&lt;br&gt;
+- Nickel Hanging Pulls&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand w/ USB: color: White; dimensions: 24" W x 16"D x 24" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 54" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 305.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -1045,20 +1045,20 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Fabric, Acrylic, Solid Wood, and finished in Pearl White tones for a clean, cohesive look.
-Size: Full
-Features
-- Padded Headboard w/ Radial Pleats &amp; LED Light
-- English Dovetail Drawers &amp; Ball-bearing Glides
-- Felt-lined Top Drawers
-- Optional Convertible Trundle
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary
-- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Pearl White
-Weight: 439.56 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Fabric, Acrylic, Solid Wood, and finished in Pearl White tones for a clean, cohesive look.&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
+- English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Optional Convertible Trundle&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 439.56 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -1180,21 +1180,21 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Fabric, Acrylic, Solid Wood, then finished in Rose Gold tones to suit a range of interiors.
-Product Dimensions: 80 1/2"L X 58"W X 54"H
-Size: Full
-Features
-- Padded Fabric Headboard w/ Radial Pleats and LED Light
-- English Dovetail Drawers with Ball-bearing Metal Side Glides
-- Felt-lined Top Drawer
-- Slat Kit Included
-- Optional Convertible Trundle or Drawer Included items and dimensions:
-- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary
-- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Rose Gold
-Weight: 442.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Fabric, Acrylic, Solid Wood, then finished in Rose Gold tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 58"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Fabric Headboard w/ Radial Pleats and LED Light&lt;br&gt;
+- English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Slat Kit Included&lt;br&gt;
+- Optional Convertible Trundle or Drawer Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 442.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -1320,21 +1320,21 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Acrylic, Solid Wood, construction and Pearl White tones, it blends durability with visual warmth.
-Size: Full
-Features
-- Padded Headboard w/ Radial Pleats &amp; LED Light
-- English Dovetail Drawers &amp; Ball-bearing Glides
-- Felt-lined Top Drawers
-- Optional Convertible Trundle
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary
-- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary
-- Trundle: color: Pearl White; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Pearl White
-Weight: 506.76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Acrylic, Solid Wood, construction and Pearl White tones, it blends durability with visual warmth.&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
+- English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Optional Convertible Trundle&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;br&gt;
+- Trundle: color: Pearl White; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 506.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Rose Gold tones, the Fabric, Acrylic, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: 80 1/2"L X 58"W X 54"H
-Size: Full
-Features
-- Padded Fabric Headboard w/ Radial Pleats and LED Light
-- English Dovetail Drawers with Ball-bearing Metal Side Glides
-- Felt-lined Top Drawer
-- Slat Kit Included
-- Optional Convertible Trundle or Drawer Included items and dimensions:
-- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary
-- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary
-- Trundle or Drawer: color: Rose Gold; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Rose Gold
-Weight: 510.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Rose Gold tones, the Fabric, Acrylic, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 58"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Fabric Headboard w/ Radial Pleats and LED Light&lt;br&gt;
+- English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Slat Kit Included&lt;br&gt;
+- Optional Convertible Trundle or Drawer Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;br&gt;
+- Trundle or Drawer: color: Rose Gold; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 510.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -1597,21 +1597,21 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Acrylic, Solid Wood, and finished in Rose Gold tones for a clean, cohesive look.
-Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H
-Size: Twin
-Features
-- Padded Fabric Headboard w/ Radial Pleats and LED Light
-- English Dovetail Drawers with Ball-bearing Metal Side Glides
-- Felt-lined Top Drawer
-- Slat Kit Included
-- Optional Convertible Trundle or Drawer Included items and dimensions:
-- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary
-- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Rose Gold
-Weight: 415 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Acrylic, Solid Wood, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Fabric Headboard w/ Radial Pleats and LED Light&lt;br&gt;
+- English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Slat Kit Included&lt;br&gt;
+- Optional Convertible Trundle or Drawer Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 415 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -1737,20 +1737,20 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Acrylic, Solid Wood, then finished in Pearl White tones to suit a range of interiors.
-Size: Twin
-Features
-- Padded Headboard w/ Radial Pleats &amp; LED Light
-- English Dovetail Drawers &amp; Ball-bearing Glides
-- Felt-lined Top Drawers
-- Optional Convertible Trundle
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary
-- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Pearl White
-Weight: 413.22 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Acrylic, Solid Wood, then finished in Pearl White tones to suit a range of interiors.&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
+- English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Optional Convertible Trundle&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 413.22 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -1872,22 +1872,22 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Fabric, Acrylic, Solid Wood, construction and Rose Gold tones, it blends durability with visual warmth.
-Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H
-Size: Twin
-Features
-- Padded Fabric Headboard w/ Radial Pleats and LED Light
-- English Dovetail Drawers with Ball-bearing Metal Side Glides
-- Felt-lined Top Drawer
-- Slat Kit Included
-- Optional Convertible Trundle or Drawer Included items and dimensions:
-- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary
-- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary
-- Trundle or Drawer: color: Rose Gold; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Rose Gold
-Weight: 483 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Fabric, Acrylic, Solid Wood, construction and Rose Gold tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Fabric Headboard w/ Radial Pleats and LED Light&lt;br&gt;
+- English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Slat Kit Included&lt;br&gt;
+- Optional Convertible Trundle or Drawer Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;br&gt;
+- Trundle or Drawer: color: Rose Gold; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 483 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -2013,21 +2013,21 @@
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALLIE 4 Pc. Bedroom Set w/ Trundle completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Pearl White tones, the Fabric, Acrylic, Solid Wood, build keeps the look polished and practical.
-Size: Twin
-Features
-- Padded Headboard w/ Radial Pleats &amp; LED Light
-- English Dovetail Drawers &amp; Ball-bearing Glides
-- Felt-lined Top Drawers
-- Optional Convertible Trundle
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary
-- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary
-- Trundle: color: Pearl White; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary
-Materials: Fabric, Acrylic, Solid Wood.
-Color: Pearl White
-Weight: 480.42 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE 4 Pc. Bedroom Set w/ Trundle completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Pearl White tones, the Fabric, Acrylic, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
+- English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Optional Convertible Trundle&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;br&gt;
+- Trundle: color: Pearl White; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 480.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
@@ -2149,21 +2149,21 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.
-Product Dimensions: 82 1/4"L X 58"W X 54"H
-Size: Full
-Features
-- Padded Headboard
-- Button Tufted
-- Crystal-like Acrylic Buttons
-- Felt-lined Top Drawers
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 396.34 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 58"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Crystal-like Acrylic Buttons&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 396.34 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
@@ -2289,21 +2289,21 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with ARISTON 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Leatherette, Mirror, Solid Wood, Wood Veneer, then finished in Rose Gold tones to suit a range of interiors.
-Product Dimensions: 82 3/4"L X 59"W X 58"H
-Size: Full
-Features
-- Padded Headboard
-- Button Tufted
-- Crystal-like Acrylic Buttons
-- Felt-lined Top Drawers
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 399.18 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with ARISTON 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Leatherette, Mirror, Solid Wood, Wood Veneer, then finished in Rose Gold tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 82 3/4"L X 59"W X 58"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Crystal-like Acrylic Buttons&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 399.18 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -2429,21 +2429,21 @@
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARISTON 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Leatherette, Mirror, Solid Wood, Wood Veneer, construction and Rose Gold tones, it blends durability with visual warmth.
-Product Dimensions: 88 1/4 "L X 65"W X 58"H
-Size: Queen
-Features
-- Padded Headboard
-- Button Tufted
-- Crystal-like Acrylic Buttons
-- Felt-lined Top Drawers
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 414.08 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARISTON 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Leatherette, Mirror, Solid Wood, Wood Veneer, construction and Rose Gold tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 88 1/4 "L X 65"W X 58"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Crystal-like Acrylic Buttons&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 414.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -2569,21 +2569,21 @@
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Rose Gold tones, the Leatherette, Mirror, Solid Wood, Wood Veneer, build keeps the look polished and practical.
-Product Dimensions: 87 3/4"L X 65"W X 58"H
-Size: Queen
-Features
-- Padded Headboard
-- Button Tufted
-- Crystal-like Acrylic Buttons
-- Felt-lined Top Drawers
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 415.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Rose Gold tones, the Leatherette, Mirror, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 87 3/4"L X 65"W X 58"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Crystal-like Acrylic Buttons&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 415.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -2709,21 +2709,21 @@
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with ARISTON 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.
-Product Dimensions: 82 1/4"L X 43"W X 54"H
-Size: Twin
-Features
-- Padded Headboard
-- Button Tufted
-- Crystal-like Acrylic Buttons
-- Felt-lined Top Drawers
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 377.92 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with ARISTON 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 43"W X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Crystal-like Acrylic Buttons&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 377.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -2849,21 +2849,21 @@
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARISTON 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Leatherette, Mirror, Solid Wood, Wood Veneer, then finished in Rose Gold tones to suit a range of interiors.
-Product Dimensions: 82 3/4"L X 43"W X 58"H
-Size: Twin
-Features
-- Padded Headboard
-- Button Tufted
-- Crystal-like Acrylic Buttons
-- Felt-lined Top Drawers
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary
-Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.
-Color: Rose Gold
-Weight: 387.36 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARISTON 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Leatherette, Mirror, Solid Wood, Wood Veneer, then finished in Rose Gold tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 82 3/4"L X 43"W X 58"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Crystal-like Acrylic Buttons&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rose Gold&lt;br&gt;
+Weight: 387.36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
@@ -2989,24 +2989,24 @@
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BELVA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Finished in White tones, the Leatherette, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: 82"L X 58"W X 57 7/8"H
-Size: Full
-Features
-- Traditional
-- Button Tufted Headboard w/ Nailhead Trim
-- Elegant Molding &amp; Trim Accents
-- Turned Legs &amp; Acrylic Finials
-- Crystal-like Acrylic Buttons
-- USB Charger in Night Stand
-- Felt-lined Top Drawers
-- Foundation Required Included items and dimensions:
-- Nightstand w/ USB: color: White; dimensions: 24" L X16" W x 27" H; feature: Traditional
-- Dresser: color: White; dimensions: 56" L x 17" W x 37" H; feature: Traditional
-Materials: Leatherette, Solid Wood.
-Color: White
-Weight: 374 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BELVA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Finished in White tones, the Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 82"L X 58"W X 57 7/8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Button Tufted Headboard w/ Nailhead Trim&lt;br&gt;
+- Elegant Molding &amp;amp; Trim Accents&lt;br&gt;
+- Turned Legs &amp;amp; Acrylic Finials&lt;br&gt;
+- Crystal-like Acrylic Buttons&lt;br&gt;
+- USB Charger in Night Stand&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand w/ USB: color: White; dimensions: 24" L X16" W x 27" H; feature: Traditional&lt;br&gt;
+- Dresser: color: White; dimensions: 56" L x 17" W x 37" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 374 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
@@ -3132,24 +3132,24 @@
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BELVA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Built from Leatherette, Solid Wood, and finished in White tones for a clean, cohesive look.
-Product Dimensions: 82"L X 43"W X 56"H
-Size: Twin
-Features
-- Traditional
-- Button Tufted Headboard w/ Nailhead Trim
-- Elegant Molding &amp; Trim Accents
-- Turned Legs &amp; Acrylic Finials
-- Crystal-like Acrylic Buttons
-- USB Charger in Night Stand
-- Felt-lined Top Drawers
-- Foundation Required Included items and dimensions:
-- Nightstand w/ USB: color: White; dimensions: 24" L X16" W x 27" H; feature: Traditional
-- Dresser: color: White; dimensions: 56" L x 17" W x 37" H; feature: Traditional
-Materials: Leatherette, Solid Wood.
-Color: White
-Weight: 356.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BELVA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Built from Leatherette, Solid Wood, and finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 82"L X 43"W X 56"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Button Tufted Headboard w/ Nailhead Trim&lt;br&gt;
+- Elegant Molding &amp;amp; Trim Accents&lt;br&gt;
+- Turned Legs &amp;amp; Acrylic Finials&lt;br&gt;
+- Crystal-like Acrylic Buttons&lt;br&gt;
+- USB Charger in Night Stand&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand w/ USB: color: White; dimensions: 24" L X16" W x 27" H; feature: Traditional&lt;br&gt;
+- Dresser: color: White; dimensions: 56" L x 17" W x 37" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 356.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H19" s="19" t="inlineStr">
@@ -3275,20 +3275,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CARA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Cottage character adds definition without feeling heavy. Built from Solid Wood, Wood Veneer, and finished in Cherry tones for a clean, cohesive look.
-Product Dimensions: 79"L X 41 3/4"W X 45"H
-Size: Twin
-Features
-- Cottage
-- Paneled Headboard
-- Optional Drawers or Trundle
-- Slat Kit Included Included items and dimensions:
-- Nightstand: color: Cherry; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: Cherry; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 212.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CARA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Cottage character adds definition without feeling heavy. Built from Solid Wood, Wood Veneer, and finished in Cherry tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 79"L X 41 3/4"W X 45"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cottage&lt;br&gt;
+- Paneled Headboard&lt;br&gt;
+- Optional Drawers or Trundle&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Cherry; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Cherry; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 212.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3410,19 +3410,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CAREN 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, Wood Veneer, then finished in White tones to suit a range of interiors.
-Product Dimensions: 79"L X 41 3/4"W X 45"H
-Size: Twin
-Features
-- Paneled Headboard
-- Optional Drawers or Trundle
-- Slat Kit Included Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 211.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CAREN 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, Wood Veneer, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 79"L X 41 3/4"W X 45"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Paneled Headboard&lt;br&gt;
+- Optional Drawers or Trundle&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 211.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3544,19 +3544,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CARUS 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Cherry tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.
-Product Dimensions: 80"L X 43 1/2"W X 45"H
-Size: Twin
-Features
-- Paneled Headboard
-- Optional Drawers or Trundle
-- Slat Kit Included Included items and dimensions:
-- Nightstand: color: Cherry; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: Cherry; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 216.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CARUS 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Cherry tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 80"L X 43 1/2"W X 45"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Paneled Headboard&lt;br&gt;
+- Optional Drawers or Trundle&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Cherry; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Cherry; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 216.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3678,23 +3678,23 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CASTILE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.
-Product Dimensions: 81 3/4"L X 60 7/8"W X 54"H
-Size: Full
-Features
-- Crown Molding Details
-- Cup Pulls and Round Knobs
-- Side Rail Drawers
-- Felt-lined Top Drawer and Cedarlined Bottom Drawer
-- Full-extension Ball Bearing Glides
-- USB Port on Night Stand
-- Mattress Ready Included items and dimensions:
-- Nightstand w/ USB: color: White; dimensions: 26" W x 16"D x 28" H; feature: Transitional
-- Dresser: color: White; dimensions: 56" W x 18"D x 36" H; feature: Transitional
-Materials: Solid Wood.
-Color: White
-Weight: 546.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CASTILE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 81 3/4"L X 60 7/8"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Crown Molding Details&lt;br&gt;
+- Cup Pulls and Round Knobs&lt;br&gt;
+- Side Rail Drawers&lt;br&gt;
+- Felt-lined Top Drawer and Cedarlined Bottom Drawer&lt;br&gt;
+- Full-extension Ball Bearing Glides&lt;br&gt;
+- USB Port on Night Stand&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand w/ USB: color: White; dimensions: 26" W x 16"D x 28" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 56" W x 18"D x 36" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 546.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -3820,23 +3820,23 @@
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CASTILE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in White tones, the Solid Wood, build keeps the look polished and practical.
-Product Dimensions: 81 3/4"L X 45 5/8"W X 54"H
-Size: Twin
-Features
-- Crown Molding Details
-- Cup Pulls and Round Knobs
-- Side Rail Drawers
-- Felt-lined Top Drawer and Cedarlined Bottom Drawer
-- Full-extension Ball Bearing Glides
-- USB Port on Night Stand
-- Mattress Ready Included items and dimensions:
-- Nightstand w/ USB: color: White; dimensions: 26" W x 16"D x 28" H; feature: Transitional
-- Dresser: color: White; dimensions: 56" W x 18"D x 36" H; feature: Transitional
-Materials: Solid Wood.
-Color: White
-Weight: 513.18 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CASTILE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in White tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 81 3/4"L X 45 5/8"W X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Crown Molding Details&lt;br&gt;
+- Cup Pulls and Round Knobs&lt;br&gt;
+- Side Rail Drawers&lt;br&gt;
+- Felt-lined Top Drawer and Cedarlined Bottom Drawer&lt;br&gt;
+- Full-extension Ball Bearing Glides&lt;br&gt;
+- USB Port on Night Stand&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand w/ USB: color: White; dimensions: 26" W x 16"D x 28" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 56" W x 18"D x 36" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 513.18 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -3962,23 +3962,23 @@
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CASTLILE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Wood, construction and Gray tones, it blends durability with visual warmth.
-Product Dimensions: 83"L X 60 7/8"W X 52"H
-Size: Full
-Features
-- Crown Molding Detail
-- Cup Pulls and Round Knobs
-- Underbed Side Drawers
-- Felt-lined Drawer and Cedar-Lined Bottom Drawer
-- Full-extension Ball Bearing Glides
-- USB Port on Night Stand
-- Mattress Ready Included items and dimensions:
-- Nightstand w/ USB: color: Gray; dimensions: 26" W x 16"D x 28" H; feature: Transitional
-- Dresser: color: Gray; dimensions: 56" W x 18"D x 36" H; feature: Transitional
-Materials: Solid Wood.
-Color: Gray
-Weight: 534.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CASTLILE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Wood, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 83"L X 60 7/8"W X 52"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Crown Molding Detail&lt;br&gt;
+- Cup Pulls and Round Knobs&lt;br&gt;
+- Underbed Side Drawers&lt;br&gt;
+- Felt-lined Drawer and Cedar-Lined Bottom Drawer&lt;br&gt;
+- Full-extension Ball Bearing Glides&lt;br&gt;
+- USB Port on Night Stand&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand w/ USB: color: Gray; dimensions: 26" W x 16"D x 28" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Gray; dimensions: 56" W x 18"D x 36" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 534.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -4104,23 +4104,23 @@
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with CASTLILE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Solid Wood, and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: 83"L X 45 5/8"W X 52"H
-Size: Twin
-Features
-- Crown Molding Detail
-- Cup Pulls and Round Knobs
-- Underbed Side Drawers
-- Felt-lined Drawer and Cedar-Lined Bottom Drawer
-- Full-extension Ball Bearing Glides
-- USB Port on Night Stand
-- Mattress Ready Included items and dimensions:
-- Nightstand w/ USB: color: Gray; dimensions: 26" W x 16"D x 28" H; feature: Transitional
-- Dresser: color: Gray; dimensions: 56" W x 18"D x 36" H; feature: Transitional
-Materials: Solid Wood.
-Color: Gray
-Weight: 512.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with CASTLILE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 83"L X 45 5/8"W X 52"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Crown Molding Detail&lt;br&gt;
+- Cup Pulls and Round Knobs&lt;br&gt;
+- Underbed Side Drawers&lt;br&gt;
+- Felt-lined Drawer and Cedar-Lined Bottom Drawer&lt;br&gt;
+- Full-extension Ball Bearing Glides&lt;br&gt;
+- USB Port on Night Stand&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand w/ USB: color: Gray; dimensions: 26" W x 16"D x 28" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Gray; dimensions: 56" W x 18"D x 36" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 512.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
@@ -4246,16 +4246,16 @@
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with CRESWELL 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and Mahogany tones, it blends durability with visual warmth.
-Size: Full
-Features
-- Rustic Included items and dimensions:
-- Nightstand: color: Mahogany; dimensions: 21" W x 15"D x 25" H; feature: Rustic
-- Dresser: color: Mahogany; dimensions: 52" W x 20.5"D x 34" H; feature: Rustic
-Materials: Solid Wood.
-Color: Mahogany
-Weight: 205.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with CRESWELL 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and Mahogany tones, it blends durability with visual warmth.&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Rustic Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Mahogany; dimensions: 21" W x 15"D x 25" H; feature: Rustic&lt;br&gt;
+- Dresser: color: Mahogany; dimensions: 52" W x 20.5"D x 34" H; feature: Rustic&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 205.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H27" s="25" t="inlineStr">
@@ -4377,16 +4377,16 @@
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CRESWELL 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Mahogany tones, the Solid Wood, build keeps the look polished and practical.
-Size: Twin
-Features
-- Rustic Included items and dimensions:
-- Nightstand: color: Mahogany; dimensions: 21" W x 15"D x 25" H; feature: Rustic
-- Dresser: color: Mahogany; dimensions: 52" W x 20.5"D x 34" H; feature: Rustic
-Materials: Solid Wood.
-Color: Mahogany
-Weight: 185.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CRESWELL 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Mahogany tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Rustic Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Mahogany; dimensions: 21" W x 15"D x 25" H; feature: Rustic&lt;br&gt;
+- Dresser: color: Mahogany; dimensions: 52" W x 20.5"D x 34" H; feature: Rustic&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Mahogany&lt;br&gt;
+Weight: 185.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H28" s="25" t="inlineStr">
@@ -4508,18 +4508,18 @@
       </c>
       <c r="G29" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DANI 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in White tones for a clean, cohesive look.
-Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H
-Size: Full
-Features
-- Plank Panel Headboard &amp; Footboard
-- Foundation Required Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 286 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DANI 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 286 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H29" s="27" t="inlineStr">
@@ -4645,19 +4645,19 @@
       </c>
       <c r="G30" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with DANI 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in White tones to suit a range of interiors.
-Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H
-Size: Full
-Features
-- Plank Panel Headboard &amp; Footboard
-- Foundation Required Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-- Trundle: color: White; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 385 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with DANI 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
+- Trundle: color: White; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 385 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" s="29" t="inlineStr">
@@ -4783,18 +4783,18 @@
       </c>
       <c r="G31" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DANI 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Wood, Wood Veneer, construction and White tones, it blends durability with visual warmth.
-Product Dimensions: 80 1/2"L X 42 1/4"W X 44 1/4"H
-Size: Twin
-Features
-- Plank Panel Headboard &amp; Footboard
-- Foundation Required Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 264 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DANI 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Wood, Wood Veneer, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 42 1/4"W X 44 1/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" s="27" t="inlineStr">
@@ -4920,19 +4920,19 @@
       </c>
       <c r="G32" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DANI 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in White tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.
-Product Dimensions: 80 1/2"L X 42 1/4"W X 44 1/4"H
-Size: Twin
-Features
-- Plank Panel Headboard &amp; Footboard
-- Foundation Required Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-- Trundle: color: White; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 363 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DANI 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in White tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 42 1/4"W X 44 1/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
+- Trundle: color: White; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 363 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H32" s="29" t="inlineStr">
@@ -5058,20 +5058,20 @@
       </c>
       <c r="G33" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DIANE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in Blue tones for a clean, cohesive look.
-Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H
-Size: Full
-Features
-- Plank Panel Headboard &amp; Footboard
-- Round Finials
-- Optional Armoire &amp; Closet Storage
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: Blue
-Weight: 286 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DIANE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in Blue tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
+- Round Finials&lt;br&gt;
+- Optional Armoire &amp;amp; Closet Storage&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 286 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H33" s="31" t="inlineStr">
@@ -5197,21 +5197,21 @@
       </c>
       <c r="G34" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with DIANE 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in Blue tones to suit a range of interiors.
-Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H
-Size: Full
-Features
-- Plank Panel Headboard &amp; Footboard
-- Round Finials
-- Optional Armoire &amp; Closet Storage
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-- Trundle: color: Blue; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: Blue
-Weight: 385 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with DIANE 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in Blue tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
+- Round Finials&lt;br&gt;
+- Optional Armoire &amp;amp; Closet Storage&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
+- Trundle: color: Blue; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 385 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H34" s="33" t="inlineStr">
@@ -5337,20 +5337,20 @@
       </c>
       <c r="G35" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DIANE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Wood, Wood Veneer, construction and Blue tones, it blends durability with visual warmth.
-Product Dimensions: 80 1/2"L X 41 3/8"W X 44 1/4"H
-Size: Twin
-Features
-- Plank Panel Headboard &amp; Footboard
-- Round Finials
-- Optional Armoire &amp; Closet Storage
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: Blue
-Weight: 264 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DIANE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Wood, Wood Veneer, construction and Blue tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 41 3/8"W X 44 1/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
+- Round Finials&lt;br&gt;
+- Optional Armoire &amp;amp; Closet Storage&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" s="31" t="inlineStr">
@@ -5476,21 +5476,21 @@
       </c>
       <c r="G36" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DIANE 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Blue tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.
-Product Dimensions: 80 1/2"L X 41 3/8"W X 44 1/4"H
-Size: Twin
-Features
-- Plank Panel Headboard &amp; Footboard
-- Round Finials
-- Optional Armoire &amp; Closet Storage
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-- Trundle: color: Blue; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: Blue
-Weight: 363 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DIANE 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Blue tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 41 3/8"W X 44 1/4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
+- Round Finials&lt;br&gt;
+- Optional Armoire &amp;amp; Closet Storage&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
+- Trundle: color: Blue; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 363 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H36" s="33" t="inlineStr">
@@ -5616,20 +5616,20 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GRIFFIN 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Rubberwood, Engineered Wood construction and Charcoal Brown tones, it blends durability with visual warmth.
-Product Dimensions: 45.5"W X 79.5"D X 48.5"H
-Size: Twin
-Features
-- Slat Design
-- Panel Headboard
-- Patented Insert &amp; Lock Joint Included items and dimensions:
-- Nightstand: color: Charcoal Brown; dimensions: 19.5" W x 18.5"D x 23.5" H; feature: Transitional
-- Dresser: color: Charcoal Brown; dimensions: 47.2" L x 18.5" W x 31.2" H; feature: Transitional
-- Chest: color: Charcoal Brown; dimensions: 31.5" W x 18.5"D x 23.5" H; feature: Transitional
-Materials: Solid Rubberwood, Engineered Wood.
-Color: Charcoal Brown
-Weight: 482.92 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GRIFFIN 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Rubberwood, Engineered Wood construction and Charcoal Brown tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 45.5"W X 79.5"D X 48.5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Slat Design&lt;br&gt;
+- Panel Headboard&lt;br&gt;
+- Patented Insert &amp;amp; Lock Joint Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Charcoal Brown; dimensions: 19.5" W x 18.5"D x 23.5" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Charcoal Brown; dimensions: 47.2" L x 18.5" W x 31.2" H; feature: Transitional&lt;br&gt;
+- Chest: color: Charcoal Brown; dimensions: 31.5" W x 18.5"D x 23.5" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Charcoal Brown&lt;br&gt;
+Weight: 482.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5751,23 +5751,23 @@
       </c>
       <c r="G38" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with LAREINA 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Pearl White tones, the Solid Rubberwood, Engineered Wood build keeps the look polished and practical.
-Product Dimensions: 58"W X 80.5"D X 52"H
-Size: Full
-Features
-- Hidden Jewelry Drawers in Dresser
-- Embossed Panels
-- Acrylic Handles &amp; Front Legs w/ Back Metal Legs
-- Felt-Lined Top Drawer
-- Metal Glide
-- English Dovetails
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: Pearl White; dimensions: 22.5" W x 17"D x 24" H; feature: Contemporary
-- Dresser: color: Pearl White; dimensions: 54.5" W x 17"D x 34" H; feature: Contemporary
-Materials: Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 514.58 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with LAREINA 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Pearl White tones, the Solid Rubberwood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 58"W X 80.5"D X 52"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Hidden Jewelry Drawers in Dresser&lt;br&gt;
+- Embossed Panels&lt;br&gt;
+- Acrylic Handles &amp;amp; Front Legs w/ Back Metal Legs&lt;br&gt;
+- Felt-Lined Top Drawer&lt;br&gt;
+- Metal Glide&lt;br&gt;
+- English Dovetails&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White; dimensions: 22.5" W x 17"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Pearl White; dimensions: 54.5" W x 17"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 514.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H38" s="35" t="inlineStr">
@@ -5893,23 +5893,23 @@
       </c>
       <c r="G39" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAREINA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Solid Rubberwood, Engineered Wood and finished in Pearl White tones for a clean, cohesive look.
-Product Dimensions: 42.5"W X 80.5"D X 52"H
-Size: Twin
-Features
-- Hidden Jewelry Drawers in Dresser
-- Embossed Panels
-- Acrylic Handles &amp; Front Legs w/ Back Metal Legs
-- Felt-Lined Top Drawer
-- Metal Glide
-- English Dovetails
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: Pearl White; dimensions: 22.5" W x 17"D x 24" H; feature: Contemporary
-- Dresser: color: Pearl White; dimensions: 54.5" W x 17"D x 34" H; feature: Contemporary
-Materials: Fabric, Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 516.81 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAREINA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Solid Rubberwood, Engineered Wood and finished in Pearl White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 42.5"W X 80.5"D X 52"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Hidden Jewelry Drawers in Dresser&lt;br&gt;
+- Embossed Panels&lt;br&gt;
+- Acrylic Handles &amp;amp; Front Legs w/ Back Metal Legs&lt;br&gt;
+- Felt-Lined Top Drawer&lt;br&gt;
+- Metal Glide&lt;br&gt;
+- English Dovetails&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White; dimensions: 22.5" W x 17"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Pearl White; dimensions: 54.5" W x 17"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 516.81 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H39" s="35" t="inlineStr">
@@ -6035,23 +6035,23 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAREINA 5 Pc. Bedroom Set w/ 2NS brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Solid Rubberwood, Engineered Wood, then finished in Pearl White tones to suit a range of interiors.
-Product Dimensions: 42.5"W X 80.5"D X 52"H
-Size: Twin
-Features
-- Hidden Jewelry Drawers in Dresser
-- Embossed Panels
-- Acrylic Handles &amp; Front Legs w/ Back Metal Legs
-- Felt-Lined Top Drawer
-- Metal Glide
-- English Dovetails
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: Pearl White; dimensions: 22.5" W x 17"D x 24" H; feature: Contemporary
-- Dresser: color: Pearl White; dimensions: 54.5" W x 17"D x 34" H; feature: Contemporary
-Materials: Fabric, Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 576.78 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAREINA 5 Pc. Bedroom Set w/ 2NS brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Solid Rubberwood, Engineered Wood, then finished in Pearl White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 42.5"W X 80.5"D X 52"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Hidden Jewelry Drawers in Dresser&lt;br&gt;
+- Embossed Panels&lt;br&gt;
+- Acrylic Handles &amp;amp; Front Legs w/ Back Metal Legs&lt;br&gt;
+- Felt-Lined Top Drawer&lt;br&gt;
+- Metal Glide&lt;br&gt;
+- English Dovetails&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White; dimensions: 22.5" W x 17"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Pearl White; dimensions: 54.5" W x 17"D x 34" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 576.78 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6173,24 +6173,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with LAREINA 5 Pc. Bedroom Set w/ Chest. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Fabric, Solid Rubberwood, Engineered Wood construction and Pearl White tones, it blends durability with visual warmth.
-Product Dimensions: 42.5"W X 80.5"D X 52"H
-Size: Twin
-Features
-- Hidden Jewelry Drawers in Dresser
-- Embossed Panels
-- Acrylic Handles &amp; Front Legs w/ Back Metal Legs
-- Felt-Lined Top Drawer
-- Metal Glide
-- English Dovetails
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: Pearl White; dimensions: 22.5" W x 17"D x 24" H; feature: Contemporary
-- Dresser: color: Pearl White; dimensions: 54.5" W x 17"D x 34" H; feature: Contemporary
-- Chest: color: Pearl White; dimensions: 30.5" W x 17"D x 43.5" H; feature: Contemporary
-Materials: Fabric, Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 701.38 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with LAREINA 5 Pc. Bedroom Set w/ Chest. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Fabric, Solid Rubberwood, Engineered Wood construction and Pearl White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 42.5"W X 80.5"D X 52"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Hidden Jewelry Drawers in Dresser&lt;br&gt;
+- Embossed Panels&lt;br&gt;
+- Acrylic Handles &amp;amp; Front Legs w/ Back Metal Legs&lt;br&gt;
+- Felt-Lined Top Drawer&lt;br&gt;
+- Metal Glide&lt;br&gt;
+- English Dovetails&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White; dimensions: 22.5" W x 17"D x 24" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: Pearl White; dimensions: 54.5" W x 17"D x 34" H; feature: Contemporary&lt;br&gt;
+- Chest: color: Pearl White; dimensions: 30.5" W x 17"D x 43.5" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 701.38 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6312,19 +6312,19 @@
       </c>
       <c r="G42" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Oak tones for a clean, cohesive look.
-Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H
-Size: Full
-Features
-- Round Tapered Legs
-- Recessed Drawer Handles
-- Slat Kit Included Included items and dimensions:
-- Nightstand: color: Oak; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern
-- Dresser: color: Oak; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern
-Materials: Solid Wood, Wood Veneer.
-Color: Oak
-Weight: 397.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Oak tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Round Tapered Legs&lt;br&gt;
+- Recessed Drawer Handles&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Oak; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
+- Dresser: color: Oak; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Oak&lt;br&gt;
+Weight: 397.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H42" s="37" t="inlineStr">
@@ -6450,19 +6450,19 @@
       </c>
       <c r="G43" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LENNART 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Crafted with Solid Wood, Wood Veneer, then finished in Black tones to suit a range of interiors.
-Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H
-Size: Full
-Features
-- Round Tapered Legs
-- Recessed Drawer Handles
-- Slat Kit Included Included items and dimensions:
-- II Nightstand: color: Black; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern
-- II Dresser: color: Black; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern
-Materials: Solid Wood, Wood Veneer.
-Color: Black
-Weight: 385.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LENNART 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Crafted with Solid Wood, Wood Veneer, then finished in Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Round Tapered Legs&lt;br&gt;
+- Recessed Drawer Handles&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- II Nightstand: color: Black; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
+- II Dresser: color: Black; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 385.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H43" s="37" t="inlineStr">
@@ -6588,19 +6588,19 @@
       </c>
       <c r="G44" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LENNART 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. With Solid Wood, Wood Veneer, construction and Gray tones, it blends durability with visual warmth.
-Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H
-Size: Full
-Features
-- Round Tapered Legs
-- Recessed Drawer Handles
-- Slat Kit Included Included items and dimensions:
-- Nightstand: color: Gray; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern
-- Dresser: color: Gray; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 344.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LENNART 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. With Solid Wood, Wood Veneer, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Round Tapered Legs&lt;br&gt;
+- Recessed Drawer Handles&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Gray; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
+- Dresser: color: Gray; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 344.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" s="37" t="inlineStr">
@@ -6726,19 +6726,19 @@
       </c>
       <c r="G45" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.
-Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H
-Size: Full
-Features
-- Round Tapered Legs
-- Recessed Drawer Handles
-- Slat Kit Included Included items and dimensions:
-- II Nightstand: color: White; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern
-- II Dresser: color: White; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 388.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Round Tapered Legs&lt;br&gt;
+- Recessed Drawer Handles&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- II Nightstand: color: White; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
+- II Dresser: color: White; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 388.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" s="37" t="inlineStr">
@@ -6864,19 +6864,19 @@
       </c>
       <c r="G46" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. With Solid Wood, Wood Veneer, construction and Oak tones, it blends durability with visual warmth.
-Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H
-Size: Twin
-Features
-- Round Tapered Legs
-- Recessed Drawer Handles
-- Slat Kit Included Included items and dimensions:
-- Nightstand: color: Oak; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern
-- Dresser: color: Oak; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern
-Materials: Solid Wood, Wood Veneer.
-Color: Oak
-Weight: 373.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. With Solid Wood, Wood Veneer, construction and Oak tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Round Tapered Legs&lt;br&gt;
+- Recessed Drawer Handles&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Oak; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
+- Dresser: color: Oak; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Oak&lt;br&gt;
+Weight: 373.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H46" s="37" t="inlineStr">
@@ -7002,19 +7002,19 @@
       </c>
       <c r="G47" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LENNART 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Finished in Black tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.
-Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H
-Size: Twin
-Features
-- Round Tapered Legs
-- Recessed Drawer Handles
-- Slat Kit Included Included items and dimensions:
-- II Nightstand: color: Black; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern
-- II Dresser: color: Black; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern
-Materials: Solid Wood, Wood Veneer.
-Color: Black
-Weight: 367.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LENNART 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Finished in Black tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Round Tapered Legs&lt;br&gt;
+- Recessed Drawer Handles&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- II Nightstand: color: Black; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
+- II Dresser: color: Black; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 367.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H47" s="37" t="inlineStr">
@@ -7140,19 +7140,19 @@
       </c>
       <c r="G48" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LENNART 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H
-Size: Twin
-Features
-- Round Tapered Legs
-- Recessed Drawer Handles
-- Slat Kit Included Included items and dimensions:
-- Nightstand: color: Gray; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern
-- Dresser: color: Gray; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern
-Materials: Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 321.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LENNART 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Round Tapered Legs&lt;br&gt;
+- Recessed Drawer Handles&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Gray; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
+- Dresser: color: Gray; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 321.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H48" s="37" t="inlineStr">
@@ -7278,19 +7278,19 @@
       </c>
       <c r="G49" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in White tones to suit a range of interiors.
-Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H
-Size: Twin
-Features
-- Round Tapered Legs
-- Recessed Drawer Handles
-- Slat Kit Included Included items and dimensions:
-- II Nightstand: color: White; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern
-- II Dresser: color: White; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 363.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Round Tapered Legs&lt;br&gt;
+- Recessed Drawer Handles&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- II Nightstand: color: White; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
+- II Dresser: color: White; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 363.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" s="37" t="inlineStr">
@@ -7416,18 +7416,18 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIDA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Light Gray tones, the Solid Wood, build keeps the look polished and practical.
-Product Dimensions: BED: 80 1/4"L X 56 3/4"W X 54"H
-Size: Full
-Features
-- #REF!
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: Light Gray; dimensions: 19" W x 16"D x 21 1 or 2" H; feature: Transitional
-- Dresser: color: Light Gray; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood.
-Color: Light Gray
-Weight: 365.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIDA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Light Gray tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: BED: 80 1/4"L X 56 3/4"W X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- #REF!&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Light Gray; dimensions: 19" W x 16"D x 21 1 or 2" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Light Gray; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 365.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -7553,23 +7553,23 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIDA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, and finished in Light Gray tones for a clean, cohesive look.
-Product Dimensions: BED: 80 1/4"L X 42"W X 54"H
-Size: Twin
-Features
-- Molding Details
-- Dovetail Drawers
-- Ball-bearing Glides
-- Felt-lined Top Drawer
-- Chrome Hanging Pulls
-- Trundle Converts to Drawers
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: Light Gray; dimensions: 19" W x 16"D x 21 1 or 2" H; feature: Transitional
-- Dresser: color: Light Gray; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood.
-Color: Light Gray
-Weight: 338.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIDA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, and finished in Light Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: BED: 80 1/4"L X 42"W X 54"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Molding Details&lt;br&gt;
+- Dovetail Drawers&lt;br&gt;
+- Ball-bearing Glides&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Chrome Hanging Pulls&lt;br&gt;
+- Trundle Converts to Drawers&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Light Gray; dimensions: 19" W x 16"D x 21 1 or 2" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Light Gray; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 338.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -7695,20 +7695,20 @@
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIS 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Solid Wood, Engineered Wood, then finished in White tones to suit a range of interiors.
-Product Dimensions: 56.5"W X 80"D X 54"H
-Size: Full
-Features
-- Poster Design w/ Finials
-- Molding Details
-- Trundle Converts into Drawers
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21.5" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood, Engineered Wood.
-Color: White
-Weight: 357.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIS 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Solid Wood, Engineered Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 56.5"W X 80"D X 54"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Poster Design w/ Finials&lt;br&gt;
+- Molding Details&lt;br&gt;
+- Trundle Converts into Drawers&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21.5" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 357.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -7834,20 +7834,20 @@
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIS 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Solid Wood, Engineered Wood construction and White tones, it blends durability with visual warmth.
-Product Dimensions: 81.5"W X 43"D X 47"H
-Size: Twin
-Features
-- Poster Design w/ Finials
-- Molding Details
-- Trundle Converts into Drawers
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21.5" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood, Engineered Wood.
-Color: White
-Weight: 331 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIS 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Solid Wood, Engineered Wood construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 81.5"W X 43"D X 47"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Poster Design w/ Finials&lt;br&gt;
+- Molding Details&lt;br&gt;
+- Trundle Converts into Drawers&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21.5" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 331 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -7973,22 +7973,22 @@
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARILLA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Solid Wood, construction and White tones, it blends durability with visual warmth.
-Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H
-Size: Full
-Features
-- Bookcase Headboard
-- Painted Hardware
-- Optional Underbed Drawers w/ Sliding Doors
-- Optional Underbed Trundle
-- Optional Underbed Trundle and Drawers Combo
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood.
-Color: White
-Weight: 267.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARILLA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Solid Wood, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bookcase Headboard&lt;br&gt;
+- Painted Hardware&lt;br&gt;
+- Optional Underbed Drawers w/ Sliding Doors&lt;br&gt;
+- Optional Underbed Trundle&lt;br&gt;
+- Optional Underbed Trundle and Drawers Combo&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 267.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
@@ -8114,23 +8114,23 @@
       </c>
       <c r="G55" s="19" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with MARILLA 4 Pc. Bedroom Set w/ Storage. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, build keeps the look polished and practical.
-Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H
-Size: Full
-Features
-- Bookcase Headboard
-- Painted Hardware
-- Optional Underbed Drawers w/ Sliding Doors
-- Optional Underbed Trundle
-- Optional Underbed Trundle and Drawers Combo
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional
-Materials: Solid Wood.
-Color: White
-Weight: 320.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with MARILLA 4 Pc. Bedroom Set w/ Storage. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bookcase Headboard&lt;br&gt;
+- Painted Hardware&lt;br&gt;
+- Optional Underbed Drawers w/ Sliding Doors&lt;br&gt;
+- Optional Underbed Trundle&lt;br&gt;
+- Optional Underbed Trundle and Drawers Combo&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
+- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 320.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H55" s="19" t="inlineStr">
@@ -8256,22 +8256,22 @@
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARILLA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Solid Wood, and finished in White tones for a clean, cohesive look.
-Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H
-Size: Twin
-Features
-- Bookcase Headboard
-- Painted Hardware
-- Optional Underbed Drawers w/ Sliding Doors
-- Optional Underbed Trundle
-- Optional Underbed Trundle and Drawers Combo
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-Materials: Solid Wood.
-Color: White
-Weight: 247.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARILLA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Solid Wood, and finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bookcase Headboard&lt;br&gt;
+- Painted Hardware&lt;br&gt;
+- Optional Underbed Drawers w/ Sliding Doors&lt;br&gt;
+- Optional Underbed Trundle&lt;br&gt;
+- Optional Underbed Trundle and Drawers Combo&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 247.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
@@ -8397,23 +8397,23 @@
       </c>
       <c r="G57" s="19" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARILLA 4 Pc. Bedroom Set w/ Storage brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.
-Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H
-Size: Twin
-Features
-- Bookcase Headboard
-- Painted Hardware
-- Optional Underbed Drawers w/ Sliding Doors
-- Optional Underbed Trundle
-- Optional Underbed Trundle and Drawers Combo
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional
-- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional
-Materials: Solid Wood.
-Color: White
-Weight: 300.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARILLA 4 Pc. Bedroom Set w/ Storage brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bookcase Headboard&lt;br&gt;
+- Painted Hardware&lt;br&gt;
+- Optional Underbed Drawers w/ Sliding Doors&lt;br&gt;
+- Optional Underbed Trundle&lt;br&gt;
+- Optional Underbed Trundle and Drawers Combo&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
+- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 300.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H57" s="19" t="inlineStr">
@@ -8539,22 +8539,22 @@
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARLEE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in White tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.
-Product Dimensions: 85 1/4"W X 59"D X 50"H
-Size: Full
-Features
-- Bookcase Headboard
-- Storage on Both Sides of Headboard
-- Optional Trundle
-- English Dovetail Drawer Construction
-- Round Drawer Pulls
-- Foundation Required Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34 1 or 8" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 341 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARLEE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in White tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 85 1/4"W X 59"D X 50"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bookcase Headboard&lt;br&gt;
+- Storage on Both Sides of Headboard&lt;br&gt;
+- Optional Trundle&lt;br&gt;
+- English Dovetail Drawer Construction&lt;br&gt;
+- Round Drawer Pulls&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34 1 or 8" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 341 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H58" s="23" t="inlineStr">
@@ -8680,22 +8680,22 @@
       </c>
       <c r="G59" s="23" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with MARLEE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in White tones for a clean, cohesive look.
-Product Dimensions: 85 1/4"W X 44"D X 50"H
-Size: Twin
-Features
-- Bookcase Headboard
-- Storage on Both Sides of Headboard
-- Optional Trundle
-- English Dovetail Drawer Construction
-- Round Drawer Pulls
-- Foundation Required Included items and dimensions:
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional
-- Dresser: color: White; dimensions: 48" W x 17"D x 34 1 or 8" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: White
-Weight: 321.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with MARLEE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 85 1/4"W X 44"D X 50"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bookcase Headboard&lt;br&gt;
+- Storage on Both Sides of Headboard&lt;br&gt;
+- Optional Trundle&lt;br&gt;
+- English Dovetail Drawer Construction&lt;br&gt;
+- Round Drawer Pulls&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
+- Dresser: color: White; dimensions: 48" W x 17"D x 34 1 or 8" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 321.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H59" s="23" t="inlineStr">
@@ -8821,22 +8821,22 @@
       </c>
       <c r="G60" s="25" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLIVIA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Leatherette, Solid Wood, Wood Veneer, construction and White tones, it blends durability with visual warmth.
-Product Dimensions: 80 1/4"L X 58 3/4"W X 55"H
-Size: Full
-Features
-- Traditional
-- Padded Camelback Headboard
-- Button Tufted
-- Optional Trundle
-- Turned Legs
-- Slat Kit Included Included items and dimensions:
-- Nightstand: color: White; dimensions: 24" W x 16"D x 26 5 or 8" H; feature: Traditional
-- Dresser: color: White; dimensions: 53" W x 17"D x 34" H; feature: Traditional
-Materials: Leatherette, Solid Wood, Wood Veneer.
-Color: White
-Weight: 372.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLIVIA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Leatherette, Solid Wood, Wood Veneer, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 80 1/4"L X 58 3/4"W X 55"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Padded Camelback Headboard&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Optional Trundle&lt;br&gt;
+- Turned Legs&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 24" W x 16"D x 26 5 or 8" H; feature: Traditional&lt;br&gt;
+- Dresser: color: White; dimensions: 53" W x 17"D x 34" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 372.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H60" s="25" t="inlineStr">
@@ -8962,22 +8962,22 @@
       </c>
       <c r="G61" s="25" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with OLIVIA 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in White tones, the Leatherette, Solid Wood, Wood Veneer, build keeps the look polished and practical.
-Product Dimensions: 80 1/4"L X 44"W X 55"H
-Size: Twin
-Features
-- Traditional
-- Padded Camelback Headboard
-- Button Tufted
-- Optional Trundle
-- Turned Legs
-- Slat Kit Included Included items and dimensions:
-- Nightstand: color: White; dimensions: 24" W x 16"D x 26 5 or 8" H; feature: Traditional
-- Dresser: color: White; dimensions: 53" W x 17"D x 34" H; feature: Traditional
-Materials: Leatherette, Solid Wood, Wood Veneer.
-Color: White
-Weight: 349.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with OLIVIA 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in White tones, the Leatherette, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 80 1/4"L X 44"W X 55"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Padded Camelback Headboard&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Optional Trundle&lt;br&gt;
+- Turned Legs&lt;br&gt;
+- Slat Kit Included Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White; dimensions: 24" W x 16"D x 26 5 or 8" H; feature: Traditional&lt;br&gt;
+- Dresser: color: White; dimensions: 53" W x 17"D x 34" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 349.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="25" t="inlineStr">
@@ -9103,24 +9103,24 @@
       </c>
       <c r="G62" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PRIAM 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Solid Wood, then finished in White or Gray tones to suit a range of interiors.
-Product Dimensions: 79 5/8"L X 56 1/4"W X 50"H
-Size: Full
-Features
-- White or Gray
-- Two-tone Color
-- Plank Design Headboard
-- Felt-lined Top Drawer
-- Ball Bearing Glides
-- Dovetail Drawers
-- Trundle Converts to Drawers
-- Mattress Ready Included items and dimensions:
-- Nightstand: color: White or Gray; dimensions: 22" W x 15 3 or 4"D x 23 7 or 8" H; feature: Contemporary
-- Dresser: color: White or Gray; dimensions: 47 5 or 8" W x 18"D x 33 7 or 8" H; feature: Contemporary
-Materials: Solid Wood.
-Color: White or Gray
-Weight: 306.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PRIAM 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Solid Wood, then finished in White or Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 79 5/8"L X 56 1/4"W X 50"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- White or Gray&lt;br&gt;
+- Two-tone Color&lt;br&gt;
+- Plank Design Headboard&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Ball Bearing Glides&lt;br&gt;
+- Dovetail Drawers&lt;br&gt;
+- Trundle Converts to Drawers&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Nightstand: color: White or Gray; dimensions: 22" W x 15 3 or 4"D x 23 7 or 8" H; feature: Contemporary&lt;br&gt;
+- Dresser: color: White or Gray; dimensions: 47 5 or 8" W x 18"D x 33 7 or 8" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 306.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="27" t="inlineStr">
@@ -9246,24 +9246,24 @@
       </c>
       <c r="G63" s="27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PRIAM 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Solid Wood, construction and White or Gray tones, it blends durability with visual warmth.
-Product Dimensions: 79 5/8"L X 41 1/2"W X 50"H
-Size: Twin
-Features
-- White or Gray
-- Two-tone Color
-- Plank Design Headboard
-- Felt-lined Top Drawer
-- Ball Bearing Glides
-- Dovetail Drawers
-- Trundle Converts to Drawers
-- Mattress Ready Included items and dimensions:
-- Dresser: color: White or Gray; dimensions: 47 5 or 8" W x 18"D x 33 7 or 8" H; feature: Contemporary
-- Nightstand: color: White or Gray; dimensions: 22" W x 15 3 or 4"D x 23 7 or 8" H; feature: Contemporary
-Materials: Solid Wood.
-Color: White or Gray
-Weight: 283 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PRIAM 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Solid Wood, construction and White or Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 79 5/8"L X 41 1/2"W X 50"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- White or Gray&lt;br&gt;
+- Two-tone Color&lt;br&gt;
+- Plank Design Headboard&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Ball Bearing Glides&lt;br&gt;
+- Dovetail Drawers&lt;br&gt;
+- Trundle Converts to Drawers&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Dresser: color: White or Gray; dimensions: 47 5 or 8" W x 18"D x 33 7 or 8" H; feature: Contemporary&lt;br&gt;
+- Nightstand: color: White or Gray; dimensions: 22" W x 15 3 or 4"D x 23 7 or 8" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 283 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="27" t="inlineStr">
@@ -9389,21 +9389,21 @@
       </c>
       <c r="G64" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with ROANNE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, Wood Veneer, and finished in Gray or Charcoal tones for a clean, cohesive look.
-Size: Full
-Features
-- Gray or Charcoal
-- Button-Tufted
-- Padded Headboard
-- Optional Trundle
-- Black Rectangular Pulls
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Gray; dimensions: 19" W x 16 3 or 8"D x 24" H; feature: Transitional
-- Dresser: color: Gray; dimensions: 47 1 or 4" W x 16 3 or 8"D x 31 5 or 8" H; feature: Transitional
-Materials: Fabric, Solid Wood, Wood Veneer.
-Color: Gray or Charcoal
-Weight: 272.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with ROANNE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, Wood Veneer, and finished in Gray or Charcoal tones for a clean, cohesive look.&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gray or Charcoal&lt;br&gt;
+- Button-Tufted&lt;br&gt;
+- Padded Headboard&lt;br&gt;
+- Optional Trundle&lt;br&gt;
+- Black Rectangular Pulls&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Gray; dimensions: 19" W x 16 3 or 8"D x 24" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Gray; dimensions: 47 1 or 4" W x 16 3 or 8"D x 31 5 or 8" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray or Charcoal&lt;br&gt;
+Weight: 272.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" s="31" t="inlineStr">
@@ -9525,21 +9525,21 @@
       </c>
       <c r="G65" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROANNE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Gray or Charcoal tones to suit a range of interiors.
-Size: Twin
-Features
-- Gray or Charcoal
-- Button-Tufted
-- Padded Headboard
-- Optional Trundle
-- Black Rectangular Pulls
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Gray; dimensions: 19" W x 16 3 or 8"D x 24" H; feature: Transitional
-- Dresser: color: Gray; dimensions: 47 1 or 4" W x 16 3 or 8"D x 31 5 or 8" H; feature: Transitional
-Materials: Fabric, Solid Wood, Wood Veneer.
-Color: Gray or Charcoal
-Weight: 258.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROANNE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Gray or Charcoal tones to suit a range of interiors.&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gray or Charcoal&lt;br&gt;
+- Button-Tufted&lt;br&gt;
+- Padded Headboard&lt;br&gt;
+- Optional Trundle&lt;br&gt;
+- Black Rectangular Pulls&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Gray; dimensions: 19" W x 16 3 or 8"D x 24" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Gray; dimensions: 47 1 or 4" W x 16 3 or 8"D x 31 5 or 8" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray or Charcoal&lt;br&gt;
+Weight: 258.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" s="31" t="inlineStr">
@@ -9661,21 +9661,21 @@
       </c>
       <c r="G66" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VEVEY 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Solid Wood, Wood Veneer, and finished in Wire-Brushed Warm Gray tones for a clean, cohesive look.
-Product Dimensions: 82 1/2"L X 58 3/8"W X 50"H
-Size: Full
-Features
-- Felt-lined Top Drawer
-- Optional Convertible Trundle
-- Wood Grain Texture
-- Round Pull Knobs
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Wire-Brushed Warm Gray; dimensions: 22" L x 15 3 or 4" W x 23 7 or 8" H; feature: Transitional
-- Dresser: color: Wire-Brushed Warm Gray; dimensions: 47 5 or 8" L x 18" W x 33 7 or 8" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: Wire-Brushed Warm Gray
-Weight: 293.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VEVEY 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Solid Wood, Wood Veneer, and finished in Wire-Brushed Warm Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 82 1/2"L X 58 3/8"W X 50"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Optional Convertible Trundle&lt;br&gt;
+- Wood Grain Texture&lt;br&gt;
+- Round Pull Knobs&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Wire-Brushed Warm Gray; dimensions: 22" L x 15 3 or 4" W x 23 7 or 8" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Wire-Brushed Warm Gray; dimensions: 47 5 or 8" L x 18" W x 33 7 or 8" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Wire-Brushed Warm Gray&lt;br&gt;
+Weight: 293.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" s="33" t="inlineStr">
@@ -9801,21 +9801,21 @@
       </c>
       <c r="G67" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VEVEY 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, Wood Veneer, then finished in Wire-Brushed Warm Gray tones to suit a range of interiors.
-Product Dimensions: 82 1/2"L X 42 7/8"W X 50"H
-Size: Twin
-Features
-- Felt-lined Top Drawer
-- Optional Convertible Trundle
-- Wood Grain Texture
-- Round Pull Knobs
-- Foundation Required Included items and dimensions:
-- Nightstand: color: Wire-Brushed Warm Gray; dimensions: 22" L x 15 3 or 4" W x 23 7 or 8" H; feature: Transitional
-- Dresser: color: Wire-Brushed Warm Gray; dimensions: 47 5 or 8" L x 18" W x 33 7 or 8" H; feature: Transitional
-Materials: Solid Wood, Wood Veneer.
-Color: Wire-Brushed Warm Gray
-Weight: 283.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VEVEY 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, Wood Veneer, then finished in Wire-Brushed Warm Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 82 1/2"L X 42 7/8"W X 50"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Felt-lined Top Drawer&lt;br&gt;
+- Optional Convertible Trundle&lt;br&gt;
+- Wood Grain Texture&lt;br&gt;
+- Round Pull Knobs&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Wire-Brushed Warm Gray; dimensions: 22" L x 15 3 or 4" W x 23 7 or 8" H; feature: Transitional&lt;br&gt;
+- Dresser: color: Wire-Brushed Warm Gray; dimensions: 47 5 or 8" L x 18" W x 33 7 or 8" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Wire-Brushed Warm Gray&lt;br&gt;
+Weight: 283.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" s="33" t="inlineStr">
@@ -9941,21 +9941,21 @@
       </c>
       <c r="G68" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZOHAR 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Finished in Pink tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: 88 1/8"L X 76 1/2"W X 56 1/2"H
-Size: Full
-Features
-- Fully Upholstered
-- Wingback Design
-- Button Tufted Headboard
-- Crystal-Like Acrylic Buttons
-- Cabriole Legs Included items and dimensions:
-- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam
-- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 512.16 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZOHAR 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Finished in Pink tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 88 1/8"L X 76 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Fully Upholstered&lt;br&gt;
+- Wingback Design&lt;br&gt;
+- Button Tufted Headboard&lt;br&gt;
+- Crystal-Like Acrylic Buttons&lt;br&gt;
+- Cabriole Legs Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam&lt;br&gt;
+- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 512.16 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" s="35" t="inlineStr">
@@ -10081,21 +10081,21 @@
       </c>
       <c r="G69" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZOHAR 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Built from Velvet-like, Solid Wood, and finished in Pink tones for a clean, cohesive look.
-Product Dimensions: 88 1/8"L X 82 1/2"W X 56 1/2"H
-Size: Queen
-Features
-- Fully Upholstered
-- Wingback Design
-- Button Tufted Headboard
-- Crystal-Like Acrylic Buttons
-- Cabriole Legs Included items and dimensions:
-- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam
-- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 530.16 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZOHAR 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Built from Velvet-like, Solid Wood, and finished in Pink tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 88 1/8"L X 82 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Fully Upholstered&lt;br&gt;
+- Wingback Design&lt;br&gt;
+- Button Tufted Headboard&lt;br&gt;
+- Crystal-Like Acrylic Buttons&lt;br&gt;
+- Cabriole Legs Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam&lt;br&gt;
+- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 530.16 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H69" s="35" t="inlineStr">
@@ -10221,21 +10221,21 @@
       </c>
       <c r="G70" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Create a calm, coordinated retreat with ZOHAR 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Crafted with Velvet-like, Solid Wood, then finished in Pink tones to suit a range of interiors.
-Product Dimensions: 88 1/8"L X 62 1/2"W X 56 1/2"H
-Size: Twin
-Features
-- Fully Upholstered
-- Wingback Design
-- Button Tufted Headboard
-- Crystal-Like Acrylic Buttons
-- Cabriole Legs Included items and dimensions:
-- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam
-- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 482.46 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with ZOHAR 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Crafted with Velvet-like, Solid Wood, then finished in Pink tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 88 1/8"L X 62 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Fully Upholstered&lt;br&gt;
+- Wingback Design&lt;br&gt;
+- Button Tufted Headboard&lt;br&gt;
+- Crystal-Like Acrylic Buttons&lt;br&gt;
+- Cabriole Legs Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam&lt;br&gt;
+- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 482.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H70" s="35" t="inlineStr">
@@ -10361,21 +10361,21 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZOHAR 5 Pc. Bedroom Set w/ 2NS completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. With Velvet-like, Solid Wood, construction and Pink tones, it blends durability with visual warmth.
-Product Dimensions: 88 1/8"L X 82 1/2"W X 56 1/2"H
-Size: Queen
-Features
-- Fully Upholstered
-- Wingback Design
-- Button Tufted Headboard
-- Crystal-Like Acrylic Buttons
-- Cabriole Legs Included items and dimensions:
-- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam
-- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 600.56 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZOHAR 5 Pc. Bedroom Set w/ 2NS completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. With Velvet-like, Solid Wood, construction and Pink tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 88 1/8"L X 82 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Fully Upholstered&lt;br&gt;
+- Wingback Design&lt;br&gt;
+- Button Tufted Headboard&lt;br&gt;
+- Crystal-Like Acrylic Buttons&lt;br&gt;
+- Cabriole Legs Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam&lt;br&gt;
+- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 600.56 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10497,22 +10497,22 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZOHAR 5 Pc. Bedroom Set w/ Chest brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Finished in Pink tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: 88 1/8"L X 82 1/2"W X 56 1/2"H
-Size: Queen
-Features
-- Fully Upholstered
-- Wingback Design
-- Button Tufted Headboard
-- Crystal-Like Acrylic Buttons
-- Cabriole Legs Included items and dimensions:
-- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam
-- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam
-- Chest: color: Pink; dimensions: 34 1 or 2" W x 17 1 or 2"D x 49" H; feature: Glam
-Materials: Velvet-like, Solid Wood.
-Color: Pink
-Weight: 703.96 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZOHAR 5 Pc. Bedroom Set w/ Chest brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Finished in Pink tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 88 1/8"L X 82 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Fully Upholstered&lt;br&gt;
+- Wingback Design&lt;br&gt;
+- Button Tufted Headboard&lt;br&gt;
+- Crystal-Like Acrylic Buttons&lt;br&gt;
+- Cabriole Legs Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam&lt;br&gt;
+- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam&lt;br&gt;
+- Chest: color: Pink; dimensions: 34 1 or 2" W x 17 1 or 2"D x 49" H; feature: Glam&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Pink&lt;br&gt;
+Weight: 703.96 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -10634,18 +10634,18 @@
       </c>
       <c r="G73" s="44" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAREINA Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. As a youth bed, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Pearl White tones, the Fabric, Solid Rubberwood, Engineered Wood build keeps the look polished and practical.
-Product Dimensions: 58"W X 80.5"D X 52"H
-Size: Full
-Features
-- Embossed Panels
-- Acrylic Handles &amp; Front Legs w/ Back Metal Legs
-- Mattress Ready Included items and dimensions:
-- Trundle: color: Pearl White; dimensions: 41" W x 75"D x 11" H; feature: Contemporary
-Materials: Fabric, Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 256.62 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAREINA Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. As a youth bed, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Pearl White tones, the Fabric, Solid Rubberwood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 58"W X 80.5"D X 52"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Embossed Panels&lt;br&gt;
+- Acrylic Handles &amp;amp; Front Legs w/ Back Metal Legs&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Trundle: color: Pearl White; dimensions: 41" W x 75"D x 11" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 256.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H73" s="44" t="inlineStr">
@@ -10771,18 +10771,18 @@
       </c>
       <c r="G74" s="44" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAREINA Bed w/ Trundle is designed for everyday living, balancing comfort with a clean, finished look. This youth bed is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Fabric, Solid Rubberwood, Engineered Wood and finished in Pearl White tones for a clean, cohesive look.
-Product Dimensions: 58"W X 80.5"D X 52"H
-Size: Twin
-Features
-- Embossed Panels
-- Acrylic Handles &amp; Front Legs w/ Back Metal Legs
-- Mattress Ready Included items and dimensions:
-- Trundle: color: Pearl White; dimensions: 41" W x 75"D x 11" H; feature: Contemporary
-Materials: Fabric, Solid Rubberwood, Engineered Wood.
-Color: Pearl White
-Weight: 258.85 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAREINA Bed w/ Trundle is designed for everyday living, balancing comfort with a clean, finished look. This youth bed is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Fabric, Solid Rubberwood, Engineered Wood and finished in Pearl White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 58"W X 80.5"D X 52"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Embossed Panels&lt;br&gt;
+- Acrylic Handles &amp;amp; Front Legs w/ Back Metal Legs&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Trundle: color: Pearl White; dimensions: 41" W x 75"D x 11" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Pearl White&lt;br&gt;
+Weight: 258.85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" s="44" t="inlineStr">
@@ -10908,14 +10908,14 @@
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIDA Bed w/ Trundle offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a youth bed, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Engineered Wood, then finished in Gray tones to suit a range of interiors.
-Product Dimensions: 56.5"W X 80"D X 54"H
-Size: Full Included items and dimensions:
-- Trundle or Drawer: color: Light Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Transitional
-Materials: Solid Wood, Engineered Wood.
-Color: Gray
-Weight: 203.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIDA Bed w/ Trundle offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a youth bed, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Engineered Wood, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 56.5"W X 80"D X 54"H&lt;br&gt;
+Size: Full Included items and dimensions:&lt;br&gt;
+- Trundle or Drawer: color: Light Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 203.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
@@ -11041,14 +11041,14 @@
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIDA Bed w/ Trundle creates a cohesive setup that feels inviting the moment you walk in. As a youth bed, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Solid Wood, Engineered Wood construction and White tones, it blends durability with visual warmth.
-Product Dimensions: 80 1/4"L X 56 3/4"W X 54"H
-Size: Full Included items and dimensions:
-- Trundle or Drawer: color: White; dimensions: 75.5" W x 40.5"D x 11" H; feature: Transitional
-Materials: Solid Wood, Engineered Wood.
-Color: White
-Weight: 203.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIDA Bed w/ Trundle creates a cohesive setup that feels inviting the moment you walk in. As a youth bed, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Solid Wood, Engineered Wood construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 80 1/4"L X 56 3/4"W X 54"H&lt;br&gt;
+Size: Full Included items and dimensions:&lt;br&gt;
+- Trundle or Drawer: color: White; dimensions: 75.5" W x 40.5"D x 11" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 203.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
@@ -11174,14 +11174,14 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIDA Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. This youth bed is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Light Gray tones, the Solid Wood, Engineered Wood build keeps the look polished and practical.
-Product Dimensions: 42"W X 80"D X 54"H
-Size: Twin Included items and dimensions:
-- Trundle or Drawer: color: Light Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Transitional
-Materials: Solid Wood, Engineered Wood.
-Color: Light Gray
-Weight: 177.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIDA Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. This youth bed is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Light Gray tones, the Solid Wood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 42"W X 80"D X 54"H&lt;br&gt;
+Size: Twin Included items and dimensions:&lt;br&gt;
+- Trundle or Drawer: color: Light Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 177.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
@@ -11311,14 +11311,14 @@
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYCORIDA Bed w/ Trundle is designed for everyday living, balancing comfort with a clean, finished look. Designed as a youth bed, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Transitional and finished in White tones for a clean, cohesive look.
-Product Dimensions: 80 1/4"L X 42"W X 54"H
-Size: Twin Included items and dimensions:
-- Trundle or Drawer: color: White; dimensions: 75.5" W x 40.5"D x 11" H; feature: Transitional
-Materials: Transitional.
-Color: White
-Weight: 177.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYCORIDA Bed w/ Trundle is designed for everyday living, balancing comfort with a clean, finished look. Designed as a youth bed, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Transitional and finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80 1/4"L X 42"W X 54"H&lt;br&gt;
+Size: Twin Included items and dimensions:&lt;br&gt;
+- Trundle or Drawer: color: White; dimensions: 75.5" W x 40.5"D x 11" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Transitional.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 177.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
@@ -11444,21 +11444,21 @@
       </c>
       <c r="G79" s="21" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARILLA Bed w/ Storage creates a cohesive setup that feels inviting the moment you walk in. Designed as a youth bed, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and White tones, it blends durability with visual warmth.
-Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H
-Size: Full
-Features
-- Bookcase Headboard
-- Painted Hardware
-- Optional Underbed Drawers w/ Sliding Doors
-- Optional Underbed Trundle
-- Optional Underbed Trundle and Drawers Combo
-- Mattress Ready Included items and dimensions:
-- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional
-Materials: Solid Wood.
-Color: White
-Weight: 176 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARILLA Bed w/ Storage creates a cohesive setup that feels inviting the moment you walk in. Designed as a youth bed, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bookcase Headboard&lt;br&gt;
+- Painted Hardware&lt;br&gt;
+- Optional Underbed Drawers w/ Sliding Doors&lt;br&gt;
+- Optional Underbed Trundle&lt;br&gt;
+- Optional Underbed Trundle and Drawers Combo&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 176 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H79" s="21" t="inlineStr">
@@ -11584,21 +11584,21 @@
       </c>
       <c r="G80" s="21" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARILLA Bed w/ Storage brings a composed, welcoming feel to the room without overwhelming the space. As a youth bed, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in White tones, the Solid Wood, build keeps the look polished and practical.
-Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H
-Size: Twin
-Features
-- Bookcase Headboard
-- Painted Hardware
-- Optional Underbed Drawers w/ Sliding Doors
-- Optional Underbed Trundle
-- Optional Underbed Trundle and Drawers Combo
-- Mattress Ready Included items and dimensions:
-- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional
-Materials: Solid Wood.
-Color: White
-Weight: 156.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARILLA Bed w/ Storage brings a composed, welcoming feel to the room without overwhelming the space. As a youth bed, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in White tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bookcase Headboard&lt;br&gt;
+- Painted Hardware&lt;br&gt;
+- Optional Underbed Drawers w/ Sliding Doors&lt;br&gt;
+- Optional Underbed Trundle&lt;br&gt;
+- Optional Underbed Trundle and Drawers Combo&lt;br&gt;
+- Mattress Ready Included items and dimensions:&lt;br&gt;
+- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 156.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H80" s="21" t="inlineStr">
@@ -11724,14 +11724,14 @@
       </c>
       <c r="G81" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PRIAM Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. Designed as a youth bed, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, Engineered Wood build keeps the look polished and practical.
-Product Dimensions: 56"W X 79.5"D X 50"H
-Size: Full Included items and dimensions:
-- Trundle or Drawers: color: White or Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Contemporary
-Materials: Solid Wood, Engineered Wood.
-Color: White
-Weight: 195.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PRIAM Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. Designed as a youth bed, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 56"W X 79.5"D X 50"H&lt;br&gt;
+Size: Full Included items and dimensions:&lt;br&gt;
+- Trundle or Drawers: color: White or Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 195.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H81" s="29" t="inlineStr">
@@ -11861,14 +11861,14 @@
       </c>
       <c r="G82" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PRIAM Bed w/ Trundle is designed for everyday living, balancing comfort with a clean, finished look. As a youth bed, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Solid Wood, Engineered Wood and finished in White tones for a clean, cohesive look.
-Product Dimensions: 41.5"W X 79.5"D X 50"H
-Size: Twin Included items and dimensions:
-- Trundle or Drawers: color: White or Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Contemporary
-Materials: Solid Wood, Engineered Wood.
-Color: White
-Weight: 172 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PRIAM Bed w/ Trundle is designed for everyday living, balancing comfort with a clean, finished look. As a youth bed, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Solid Wood, Engineered Wood and finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 41.5"W X 79.5"D X 50"H&lt;br&gt;
+Size: Twin Included items and dimensions:&lt;br&gt;
+- Trundle or Drawers: color: White or Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 172 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H82" s="29" t="inlineStr">

--- a/FOA SETS/Youth-Set.xlsx
+++ b/FOA SETS/Youth-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD82"/>
+  <dimension ref="A1:AG82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,6 +727,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -867,7 +882,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ALECIA</t>
+          <t>Youth, Bedroom Set, ALECIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1038,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ALECIA</t>
+          <t>Youth, Bedroom Set, ALECIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1188,22 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ALLIE</t>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1343,22 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ALLIE</t>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1494,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ALLIE</t>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1650,22 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ALLIE</t>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1805,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ALLIE</t>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1955,22 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ALLIE</t>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2111,22 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ALLIE</t>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2262,22 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ALLIE</t>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2417,22 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ARISTON</t>
+          <t>Youth, Bedroom Set, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2572,22 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ARISTON</t>
+          <t>Youth, Bedroom Set, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2727,22 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ARISTON</t>
+          <t>Youth, Bedroom Set, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2882,22 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ARISTON</t>
+          <t>Youth, Bedroom Set, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2812,7 +3037,22 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ARISTON</t>
+          <t>Youth, Bedroom Set, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2952,7 +3192,22 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ARISTON</t>
+          <t>Youth, Bedroom Set, ARISTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3350,22 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, BELVA</t>
+          <t>Youth, Bedroom Set, BELVA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3508,22 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, BELVA</t>
+          <t>Youth, Bedroom Set, BELVA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3658,22 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, CARA</t>
+          <t>Youth, Bedroom Set, CARA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3807,22 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, CAREN</t>
+          <t>Youth, Bedroom Set, CAREN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3956,22 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, CARUS</t>
+          <t>Youth, Bedroom Set, CARUS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3783,7 +4113,22 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, CASTILE</t>
+          <t>Youth, Bedroom Set, CASTILE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3925,7 +4270,22 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, CASTILE</t>
+          <t>Youth, Bedroom Set, CASTILE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4427,22 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, CASTLILE</t>
+          <t>Youth, Bedroom Set, CASTLILE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4584,22 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, CASTLILE</t>
+          <t>Youth, Bedroom Set, CASTLILE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4730,22 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, CRESWELL</t>
+          <t>Youth, Bedroom Set, CRESWELL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4876,22 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, CRESWELL</t>
+          <t>Youth, Bedroom Set, CRESWELL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4608,7 +5028,22 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, DANI</t>
+          <t>Youth, Bedroom Set, DANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4746,7 +5181,22 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, DANI</t>
+          <t>Youth, Bedroom Set, DANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4883,7 +5333,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, DANI</t>
+          <t>Youth, Bedroom Set, DANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5486,22 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, DANI</t>
+          <t>Youth, Bedroom Set, DANI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5640,22 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, DIANE</t>
+          <t>Youth, Bedroom Set, DIANE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5795,22 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, DIANE</t>
+          <t>Youth, Bedroom Set, DIANE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5949,22 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, DIANE</t>
+          <t>Youth, Bedroom Set, DIANE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5579,7 +6104,22 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, DIANE</t>
+          <t>Youth, Bedroom Set, DIANE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5714,7 +6254,22 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, GRIFFIN</t>
+          <t>Youth, Bedroom Set, GRIFFIN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5856,7 +6411,22 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LAREINA</t>
+          <t>Youth, Bedroom Set, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5998,7 +6568,22 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LAREINA</t>
+          <t>Youth, Bedroom Set, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6721,22 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LAREINA</t>
+          <t>Youth, Bedroom Set, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6875,22 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LAREINA</t>
+          <t>Youth, Bedroom Set, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6413,7 +7028,22 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LENNART</t>
+          <t>Youth, Bedroom Set, LENNART, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6551,7 +7181,22 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LENNART</t>
+          <t>Youth, Bedroom Set, LENNART, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6689,7 +7334,22 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LENNART</t>
+          <t>Youth, Bedroom Set, LENNART, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6827,7 +7487,22 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LENNART</t>
+          <t>Youth, Bedroom Set, LENNART, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6965,7 +7640,22 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LENNART</t>
+          <t>Youth, Bedroom Set, LENNART, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7793,22 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LENNART</t>
+          <t>Youth, Bedroom Set, LENNART, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7946,22 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LENNART</t>
+          <t>Youth, Bedroom Set, LENNART, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7379,7 +8099,22 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LENNART</t>
+          <t>Youth, Bedroom Set, LENNART, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7516,7 +8251,22 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LYCORIDA</t>
+          <t>Youth, Bedroom Set, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7658,7 +8408,22 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LYCORIDA</t>
+          <t>Youth, Bedroom Set, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7797,7 +8562,22 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LYCORIS</t>
+          <t>Youth, Bedroom Set, LYCORIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7936,7 +8716,22 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, LYCORIS</t>
+          <t>Youth, Bedroom Set, LYCORIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8872,22 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, MARILLA</t>
+          <t>Youth, Bedroom Set, MARILLA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8219,7 +9029,22 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, MARILLA</t>
+          <t>Youth, Bedroom Set, MARILLA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8360,7 +9185,22 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, MARILLA</t>
+          <t>Youth, Bedroom Set, MARILLA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8502,7 +9342,22 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, MARILLA</t>
+          <t>Youth, Bedroom Set, MARILLA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8643,7 +9498,22 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, MARLEE</t>
+          <t>Youth, Bedroom Set, MARLEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8784,7 +9654,22 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, MARLEE</t>
+          <t>Youth, Bedroom Set, MARLEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8925,7 +9810,22 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, OLIVIA</t>
+          <t>Youth, Bedroom Set, OLIVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9966,22 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, OLIVIA</t>
+          <t>Youth, Bedroom Set, OLIVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9209,7 +10124,22 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, PRIAM</t>
+          <t>Youth, Bedroom Set, PRIAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9352,7 +10282,22 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, PRIAM</t>
+          <t>Youth, Bedroom Set, PRIAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9488,7 +10433,22 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ROANNE</t>
+          <t>Youth, Bedroom Set, ROANNE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9624,7 +10584,22 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ROANNE</t>
+          <t>Youth, Bedroom Set, ROANNE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9764,7 +10739,22 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, VEVEY</t>
+          <t>Youth, Bedroom Set, VEVEY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9904,7 +10894,22 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, VEVEY</t>
+          <t>Youth, Bedroom Set, VEVEY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10044,7 +11049,22 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ZOHAR</t>
+          <t>Youth, Bedroom Set, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10184,7 +11204,22 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ZOHAR</t>
+          <t>Youth, Bedroom Set, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10324,7 +11359,22 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ZOHAR</t>
+          <t>Youth, Bedroom Set, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10460,7 +11510,22 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ZOHAR</t>
+          <t>Youth, Bedroom Set, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10597,7 +11662,22 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Youth, Bedroom Set, ZOHAR</t>
+          <t>Youth, Bedroom Set, ZOHAR, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10734,7 +11814,22 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Youth, Bed, LAREINA</t>
+          <t>Youth, Bed, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -10871,7 +11966,22 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Youth, Bed, LAREINA</t>
+          <t>Youth, Bed, LAREINA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11004,7 +12114,22 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Youth, Bed, LYCORIDA</t>
+          <t>Youth, Bed, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11137,7 +12262,22 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Youth, Bed, LYCORIDA</t>
+          <t>Youth, Bed, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11274,7 +12414,22 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Youth, Bed, LYCORIDA</t>
+          <t>Youth, Bed, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11407,7 +12562,22 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Youth, Bed, LYCORIDA</t>
+          <t>Youth, Bed, LYCORIDA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11547,7 +12717,22 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Youth, Bed, MARILLA</t>
+          <t>Youth, Bed, MARILLA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11687,7 +12872,22 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Youth, Bed, MARILLA</t>
+          <t>Youth, Bed, MARILLA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11824,7 +13024,22 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Youth, Bed, PRIAM</t>
+          <t>Youth, Bed, PRIAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -11961,7 +13176,22 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Youth, Bed, PRIAM</t>
+          <t>Youth, Bed, PRIAM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>

--- a/FOA SETS/Youth-Set.xlsx
+++ b/FOA SETS/Youth-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ALECIA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 58 5/8"W X 54"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 80 1/2"L X 58 5/8"W X 54"H / 80 1/2"L X 43 5/8"W X 52"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bell-shape Design&lt;br&gt;
 - Crown Molding&lt;br&gt;
@@ -789,11 +789,11 @@
 - Nickel Hanging Pulls&lt;br&gt;
 - Felt-lined Top Drawer&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand w/ USB: color: White; dimensions: 24" W x 16"D x 24" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 54" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand w/ USB: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 330 lbs&lt;/p&gt;</t>
+Weight: 330 or 305.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -935,9 +935,9 @@
       <c r="G3" s="9" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with ALECIA 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 43 5/8"W X 52"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+ALECIA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 58 5/8"W X 54"H / 80 1/2"L X 43 5/8"W X 52"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bell-shape Design&lt;br&gt;
 - Crown Molding&lt;br&gt;
@@ -945,11 +945,11 @@
 - Nickel Hanging Pulls&lt;br&gt;
 - Felt-lined Top Drawer&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand w/ USB: color: White; dimensions: 24" W x 16"D x 24" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 54" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand w/ USB: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 305.8 lbs&lt;/p&gt;</t>
+Weight: 330 or 305.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1092,18 +1092,18 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Fabric, Acrylic, Solid Wood, and finished in Pearl White tones for a clean, cohesive look.&lt;br&gt;
-Size: Full&lt;/p&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
 - English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Optional Convertible Trundle&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Pearl White&lt;br&gt;
-Weight: 439.56 lbs&lt;/p&gt;</t>
+- Nightstand: color: Pearl White or Rose Gold&lt;br&gt;
+- Dresser: color: Pearl White or Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 439.56 or 442.2 or 415 or 413.22 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1241,943 +1241,939 @@
       <c r="G5" s="11" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALLIE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Fabric, Acrylic, Solid Wood, then finished in Rose Gold tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 58"W X 54"H&lt;br&gt;
-Size: Full&lt;/p&gt;
-&lt;p&gt;Features&lt;br&gt;
-- Padded Fabric Headboard w/ Radial Pleats and LED Light&lt;br&gt;
-- English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
-- Felt-lined Top Drawer&lt;br&gt;
-- Slat Kit Included&lt;br&gt;
-- Optional Convertible Trundle or Drawer Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Rose Gold&lt;br&gt;
-Weight: 442.2 lbs&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>ALLIE 4 Pc. Bedroom Set Full in Rose Gold | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>The ALLIE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>ALLIE</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>4 Pc. Full Bedroom Set</t>
-        </is>
-      </c>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="inlineStr">
-        <is>
-          <t>CM7901RG-F-HB, CM7901RG-F-FB, CM7901RG-F-R, CM7901RG-N, CM7901RG-D, CM7901RG-M</t>
-        </is>
-      </c>
-      <c r="O5" s="11" t="inlineStr">
-        <is>
-          <t>CM7901RG-1-Z.jpg,CM7901RG-2.jpg,CM7901RG-3.jpg,CM7901RG-4.jpg,CM7901RG-5.jpg,CM7901RG-6.jpg,CM7901RG-7.jpg</t>
-        </is>
-      </c>
-      <c r="P5" s="11" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q5" s="12" t="n">
-        <v>1059</v>
-      </c>
-      <c r="R5" s="11" t="n">
-        <v>2667</v>
-      </c>
-      <c r="S5" s="11" t="n">
-        <v>442.2</v>
-      </c>
-      <c r="T5" s="11" t="inlineStr">
-        <is>
-          <t>80 1/2"L X 58"W X 54"H</t>
-        </is>
-      </c>
-      <c r="U5" s="11" t="inlineStr">
-        <is>
-          <t>Contemporary</t>
-        </is>
-      </c>
-      <c r="V5" s="11" t="inlineStr">
-        <is>
-          <t>Fabric, Acrylic, Solid Wood, Others</t>
-        </is>
-      </c>
-      <c r="W5" s="11" t="inlineStr">
-        <is>
-          <t>Contemporary,Rose Gold,Fabric, Acrylic, Solid Wood, Others,Padded Fabric Headboard w/ Radial Pleats and LED Light,Acrylic and Mirror Accents,English Dovetail Drawers with Ball-bearing Metal Side Glides,Felt-lined Top Drawer,Mirror w/ LED Light,Slat Kit Included,Optional Convertible Trundle/Drawer</t>
-        </is>
-      </c>
-      <c r="X5" s="11" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="Y5" s="11" t="n"/>
-      <c r="Z5" s="11" t="n"/>
-      <c r="AA5" s="11" t="n"/>
-      <c r="AB5" s="11" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>GOODDEGG</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Pearl White</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>CM7901F-4PC-TR</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Youth</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Bedroom Set</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALLIE 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Acrylic, Solid Wood, construction and Pearl White tones, it blends durability with visual warmth.&lt;br&gt;
-Size: Full&lt;/p&gt;
+Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Fabric, Acrylic, Solid Wood, and finished in Pearl White tones for a clean, cohesive look.&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
 - English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Optional Convertible Trundle&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;br&gt;
-- Trundle: color: Pearl White; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Pearl White&lt;br&gt;
-Weight: 506.76 lbs&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle Full in Pearl White | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>The ALLIE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
+- Nightstand: color: Pearl White or Rose Gold&lt;br&gt;
+- Dresser: color: Pearl White or Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 439.56 or 442.2 or 415 or 413.22 lbs&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>ALLIE 4 Pc. Bedroom Set Full in Rose Gold | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>The ALLIE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>ALLIE</t>
         </is>
       </c>
-      <c r="K6" s="13" t="inlineStr">
-        <is>
-          <t>4 Pc. Full Bedroom Set w/ Trundle</t>
-        </is>
-      </c>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>4 Pc. Full Bedroom Set</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="n"/>
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N6" s="13" t="inlineStr">
-        <is>
-          <t>CM7901F-HB, CM7901F-FB, CM7901F-R, CM7901N, CM7901D, CM7901M, CM7901TR</t>
-        </is>
-      </c>
-      <c r="O6" s="13" t="inlineStr">
-        <is>
-          <t>CM7901-1-Z.jpg,CM7901-2.jpg,CM7901-3.jpg,CM7901-4.jpg</t>
-        </is>
-      </c>
-      <c r="P6" s="13" t="n">
-        <v>1109</v>
-      </c>
-      <c r="Q6" s="14" t="n">
-        <v>1159</v>
-      </c>
-      <c r="R6" s="13" t="n">
-        <v>2967</v>
-      </c>
-      <c r="S6" s="13" t="n">
-        <v>506.76</v>
-      </c>
-      <c r="T6" s="13" t="n"/>
-      <c r="U6" s="13" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>CM7901RG-F-HB, CM7901RG-F-FB, CM7901RG-F-R, CM7901RG-N, CM7901RG-D, CM7901RG-M</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>CM7901RG-1-Z.jpg,CM7901RG-2.jpg,CM7901RG-3.jpg,CM7901RG-4.jpg,CM7901RG-5.jpg,CM7901RG-6.jpg,CM7901RG-7.jpg</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q5" s="12" t="n">
+        <v>1059</v>
+      </c>
+      <c r="R5" s="11" t="n">
+        <v>2667</v>
+      </c>
+      <c r="S5" s="11" t="n">
+        <v>442.2</v>
+      </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>80 1/2"L X 58"W X 54"H</t>
+        </is>
+      </c>
+      <c r="U5" s="11" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V6" s="13" t="inlineStr">
+      <c r="V5" s="11" t="inlineStr">
         <is>
           <t>Fabric, Acrylic, Solid Wood, Others</t>
         </is>
       </c>
-      <c r="W6" s="13" t="inlineStr">
-        <is>
-          <t>Contemporary,Pearl White,Fabric, Acrylic, Solid Wood, Others,Padded Headboard w/Radial Pleats &amp; LED Light,Acrylic &amp; Mirror Accents,Mirror w/ LED Light,English Dovetail Drawers &amp; Ball-bearing Glides,Felt-lined Top Drawers,Optional Convertible Trundle,Foundation Required</t>
-        </is>
-      </c>
-      <c r="X6" s="13" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>Contemporary,Rose Gold,Fabric, Acrylic, Solid Wood, Others,Padded Fabric Headboard w/ Radial Pleats and LED Light,Acrylic and Mirror Accents,English Dovetail Drawers with Ball-bearing Metal Side Glides,Felt-lined Top Drawer,Mirror w/ LED Light,Slat Kit Included,Optional Convertible Trundle/Drawer</t>
+        </is>
+      </c>
+      <c r="X5" s="11" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y6" s="13" t="n"/>
-      <c r="Z6" s="13" t="n"/>
-      <c r="AA6" s="13" t="n"/>
-      <c r="AB6" s="13" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
+      <c r="Y5" s="11" t="n"/>
+      <c r="Z5" s="11" t="n"/>
+      <c r="AA5" s="11" t="n"/>
+      <c r="AB5" s="11" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Rose Gold</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Pearl White</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>CM7901RG-F-4PC-TR</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>CM7901F-4PC-TR</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Bedroom Set</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>ALLIE 4 Pc. Bedroom Set w/ Trundle</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Rose Gold tones, the Fabric, Acrylic, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 58"W X 54"H&lt;br&gt;
-Size: Full&lt;/p&gt;
-&lt;p&gt;Features&lt;br&gt;
-- Padded Fabric Headboard w/ Radial Pleats and LED Light&lt;br&gt;
-- English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
-- Felt-lined Top Drawer&lt;br&gt;
-- Slat Kit Included&lt;br&gt;
-- Optional Convertible Trundle or Drawer Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;br&gt;
-- Trundle or Drawer: color: Rose Gold; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Rose Gold&lt;br&gt;
-Weight: 510.2 lbs&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle Full in Rose Gold | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>The ALLIE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>ALLIE</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="inlineStr">
-        <is>
-          <t>4 Pc. Full Bedroom Set w/ Trundle</t>
-        </is>
-      </c>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="13" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="N7" s="13" t="inlineStr">
-        <is>
-          <t>CM7901RG-F-HB, CM7901RG-F-FB, CM7901RG-F-R, CM7901RG-N, CM7901RG-D, CM7901RG-M, CM7901RG-TR</t>
-        </is>
-      </c>
-      <c r="O7" s="13" t="inlineStr">
-        <is>
-          <t>CM7901RG-TR-1.jpg,CM7901RG-1-Z.jpg,CM7901RG-5.jpg</t>
-        </is>
-      </c>
-      <c r="P7" s="13" t="n">
-        <v>1109</v>
-      </c>
-      <c r="Q7" s="14" t="n">
-        <v>1159</v>
-      </c>
-      <c r="R7" s="13" t="n">
-        <v>2967</v>
-      </c>
-      <c r="S7" s="13" t="n">
-        <v>510.2</v>
-      </c>
-      <c r="T7" s="13" t="inlineStr">
-        <is>
-          <t>80 1/2"L X 58"W X 54"H</t>
-        </is>
-      </c>
-      <c r="U7" s="13" t="inlineStr">
-        <is>
-          <t>Contemporary</t>
-        </is>
-      </c>
-      <c r="V7" s="13" t="inlineStr">
-        <is>
-          <t>Fabric, Acrylic, Solid Wood, Others</t>
-        </is>
-      </c>
-      <c r="W7" s="13" t="inlineStr">
-        <is>
-          <t>Contemporary,Rose Gold,Fabric, Acrylic, Solid Wood, Others,Padded Fabric Headboard w/ Radial Pleats and LED Light,Acrylic and Mirror Accents,English Dovetail Drawers with Ball-bearing Metal Side Glides,Felt-lined Top Drawer,Mirror w/ LED Light,Slat Kit Included,Optional Convertible Trundle/Drawer</t>
-        </is>
-      </c>
-      <c r="X7" s="13" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="Y7" s="13" t="n"/>
-      <c r="Z7" s="13" t="n"/>
-      <c r="AA7" s="13" t="n"/>
-      <c r="AB7" s="13" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>GOODDEGG</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Rose Gold</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Twin</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>CM7901RG-T-4PC</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Youth</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Bedroom Set</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>ALLIE 4 Pc. Bedroom Set</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALLIE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Acrylic, Solid Wood, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
-&lt;p&gt;Features&lt;br&gt;
-- Padded Fabric Headboard w/ Radial Pleats and LED Light&lt;br&gt;
-- English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
-- Felt-lined Top Drawer&lt;br&gt;
-- Slat Kit Included&lt;br&gt;
-- Optional Convertible Trundle or Drawer Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Rose Gold&lt;br&gt;
-Weight: 415 lbs&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>ALLIE 4 Pc. Bedroom Set Twin in Rose Gold | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>The ALLIE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>ALLIE</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>4 Pc. Twin Bedroom Set</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>CM7901RG-T-HB, CM7901RG-T-FB, CM7901RG-T-R, CM7901RG-N, CM7901RG-D, CM7901RG-M</t>
-        </is>
-      </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>CM7901RG-1-Z.jpg,CM7901RG-2.jpg,CM7901RG-3.jpg,CM7901RG-4.jpg,CM7901RG-5.jpg,CM7901RG-6.jpg,CM7901RG-7.jpg</t>
-        </is>
-      </c>
-      <c r="P8" s="11" t="n">
-        <v>959</v>
-      </c>
-      <c r="Q8" s="15" t="n">
-        <v>959</v>
-      </c>
-      <c r="R8" s="11" t="n">
-        <v>2577</v>
-      </c>
-      <c r="S8" s="11" t="n">
-        <v>415</v>
-      </c>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>80 1/2"L X 41 3/4"W X 54"H</t>
-        </is>
-      </c>
-      <c r="U8" s="11" t="inlineStr">
-        <is>
-          <t>Contemporary</t>
-        </is>
-      </c>
-      <c r="V8" s="11" t="inlineStr">
-        <is>
-          <t>Fabric, Acrylic, Solid Wood, Others</t>
-        </is>
-      </c>
-      <c r="W8" s="11" t="inlineStr">
-        <is>
-          <t>Contemporary,Rose Gold,Fabric, Acrylic, Solid Wood, Others,Acrylic and Mirror Accents,Padded Fabric Headboard w/ Radial Pleats and LED Light,English Dovetail Drawers with Ball-bearing Metal Side Glides,Felt-lined Top Drawer,Mirror w/ LED Light,Slat Kit Included,Optional Convertible Trundle/Drawer</t>
-        </is>
-      </c>
-      <c r="X8" s="11" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="Y8" s="11" t="n"/>
-      <c r="Z8" s="11" t="n"/>
-      <c r="AA8" s="11" t="n"/>
-      <c r="AB8" s="11" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>GOODDEGG</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Pearl White</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Twin</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>CM7901T-4PC</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Youth</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Bedroom Set</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>ALLIE 4 Pc. Bedroom Set</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALLIE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Acrylic, Solid Wood, then finished in Pearl White tones to suit a range of interiors.&lt;br&gt;
-Size: Twin&lt;/p&gt;
+ALLIE 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Acrylic, Solid Wood, construction and Pearl White tones, it blends durability with visual warmth.&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
 - English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Optional Convertible Trundle&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Pearl White&lt;br&gt;
-Weight: 413.22 lbs&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>ALLIE 4 Pc. Bedroom Set Twin in Pearl White | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>The ALLIE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
+- Nightstand: color: Pearl White or Rose Gold&lt;br&gt;
+- Dresser: color: Pearl White or Rose Gold&lt;br&gt;
+- Trundle: color: Pearl White or Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 506.76 or 510.2 or 483 or 480.42 lbs&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle Full in Pearl White | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>The ALLIE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>ALLIE</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>4 Pc. Twin Bedroom Set</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>4 Pc. Full Bedroom Set w/ Trundle</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>CM7901T-HB, CM7901T-FB, CM7901T-R, CM7901N, CM7901D, CM7901M</t>
-        </is>
-      </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t>CM7901F-HB, CM7901F-FB, CM7901F-R, CM7901N, CM7901D, CM7901M, CM7901TR</t>
+        </is>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>CM7901-1-Z.jpg,CM7901-2.jpg,CM7901-3.jpg,CM7901-4.jpg</t>
         </is>
       </c>
-      <c r="P9" s="11" t="n">
-        <v>959</v>
-      </c>
-      <c r="Q9" s="12" t="n">
-        <v>999</v>
-      </c>
-      <c r="R9" s="11" t="n">
-        <v>2577</v>
-      </c>
-      <c r="S9" s="11" t="n">
-        <v>413.22</v>
-      </c>
-      <c r="T9" s="11" t="n"/>
-      <c r="U9" s="11" t="inlineStr">
+      <c r="P6" s="13" t="n">
+        <v>1109</v>
+      </c>
+      <c r="Q6" s="14" t="n">
+        <v>1159</v>
+      </c>
+      <c r="R6" s="13" t="n">
+        <v>2967</v>
+      </c>
+      <c r="S6" s="13" t="n">
+        <v>506.76</v>
+      </c>
+      <c r="T6" s="13" t="n"/>
+      <c r="U6" s="13" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="V9" s="11" t="inlineStr">
+      <c r="V6" s="13" t="inlineStr">
         <is>
           <t>Fabric, Acrylic, Solid Wood, Others</t>
         </is>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W6" s="13" t="inlineStr">
         <is>
           <t>Contemporary,Pearl White,Fabric, Acrylic, Solid Wood, Others,Padded Headboard w/Radial Pleats &amp; LED Light,Acrylic &amp; Mirror Accents,Mirror w/ LED Light,English Dovetail Drawers &amp; Ball-bearing Glides,Felt-lined Top Drawers,Optional Convertible Trundle,Foundation Required</t>
         </is>
       </c>
-      <c r="X9" s="11" t="inlineStr">
+      <c r="X6" s="13" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y9" s="11" t="n"/>
-      <c r="Z9" s="11" t="n"/>
-      <c r="AA9" s="11" t="n"/>
-      <c r="AB9" s="11" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
+      <c r="Y6" s="13" t="n"/>
+      <c r="Z6" s="13" t="n"/>
+      <c r="AA6" s="13" t="n"/>
+      <c r="AB6" s="13" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Rose Gold</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Twin</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>CM7901RG-T-4PC-TR</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>CM7901RG-F-4PC-TR</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Youth</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Bedroom Set</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>ALLIE 4 Pc. Bedroom Set w/ Trundle</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Fabric, Acrylic, Solid Wood, construction and Rose Gold tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 41 3/4"W X 54"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
-&lt;p&gt;Features&lt;br&gt;
-- Padded Fabric Headboard w/ Radial Pleats and LED Light&lt;br&gt;
-- English Dovetail Drawers with Ball-bearing Metal Side Glides&lt;br&gt;
-- Felt-lined Top Drawer&lt;br&gt;
-- Slat Kit Included&lt;br&gt;
-- Optional Convertible Trundle or Drawer Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Rose Gold; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Rose Gold; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;br&gt;
-- Trundle or Drawer: color: Rose Gold; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Rose Gold&lt;br&gt;
-Weight: 483 lbs&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle Twin in Rose Gold | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>The ALLIE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>ALLIE</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>4 Pc. Twin Bedroom Set w/ Trundle</t>
-        </is>
-      </c>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="13" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
-        <is>
-          <t>CM7901RG-T-HB, CM7901RG-T-FB, CM7901RG-T-R, CM7901RG-N, CM7901RG-D, CM7901RG-M, CM7901RG-TR</t>
-        </is>
-      </c>
-      <c r="O10" s="13" t="inlineStr">
-        <is>
-          <t>CM7901RG-1-Z.jpg,CM7901RG-2.jpg,CM7901RG-3.jpg,CM7901RG-4.jpg,CM7901RG-5.jpg,CM7901RG-6.jpg,CM7901RG-7.jpg</t>
-        </is>
-      </c>
-      <c r="P10" s="13" t="n">
-        <v>1069</v>
-      </c>
-      <c r="Q10" s="16" t="n">
-        <v>1069</v>
-      </c>
-      <c r="R10" s="13" t="n">
-        <v>2877</v>
-      </c>
-      <c r="S10" s="13" t="n">
-        <v>483</v>
-      </c>
-      <c r="T10" s="13" t="inlineStr">
-        <is>
-          <t>80 1/2"L X 41 3/4"W X 54"H</t>
-        </is>
-      </c>
-      <c r="U10" s="13" t="inlineStr">
-        <is>
-          <t>Contemporary</t>
-        </is>
-      </c>
-      <c r="V10" s="13" t="inlineStr">
-        <is>
-          <t>Fabric, Acrylic, Solid Wood, Others</t>
-        </is>
-      </c>
-      <c r="W10" s="13" t="inlineStr">
-        <is>
-          <t>Contemporary,Rose Gold,Fabric, Acrylic, Solid Wood, Others,Acrylic and Mirror Accents,Padded Fabric Headboard w/ Radial Pleats and LED Light,English Dovetail Drawers with Ball-bearing Metal Side Glides,Felt-lined Top Drawer,Mirror w/ LED Light,Slat Kit Included,Optional Convertible Trundle/Drawer</t>
-        </is>
-      </c>
-      <c r="X10" s="13" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="Y10" s="13" t="n"/>
-      <c r="Z10" s="13" t="n"/>
-      <c r="AA10" s="13" t="n"/>
-      <c r="AB10" s="13" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>GOODDEGG</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Pearl White</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Twin</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>CM7901T-4PC-TR</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Youth</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Bedroom Set</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALLIE 4 Pc. Bedroom Set w/ Trundle completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Pearl White tones, the Fabric, Acrylic, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
-Size: Twin&lt;/p&gt;
+ALLIE 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Acrylic, Solid Wood, construction and Pearl White tones, it blends durability with visual warmth.&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
 - English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Optional Convertible Trundle&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Pearl White; dimensions: 22 7 or 8" W x 16 1 or 2"D x 24" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Pearl White; dimensions: 54 1 or 2" W x 16 1 or 2"D x 34" H; feature: Contemporary&lt;br&gt;
-- Trundle: color: Pearl White; dimensions: 75 1 or 4" L x 40 3 or 4" W x 11 5 or 8" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood.&lt;br&gt;
-Color: Pearl White&lt;br&gt;
-Weight: 480.42 lbs&lt;/p&gt;</t>
+- Nightstand: color: Pearl White or Rose Gold&lt;br&gt;
+- Dresser: color: Pearl White or Rose Gold&lt;br&gt;
+- Trundle: color: Pearl White or Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 506.76 or 510.2 or 483 or 480.42 lbs&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle Full in Rose Gold | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>The ALLIE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>ALLIE</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>4 Pc. Full Bedroom Set w/ Trundle</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>CM7901RG-F-HB, CM7901RG-F-FB, CM7901RG-F-R, CM7901RG-N, CM7901RG-D, CM7901RG-M, CM7901RG-TR</t>
+        </is>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>CM7901RG-TR-1.jpg,CM7901RG-1-Z.jpg,CM7901RG-5.jpg</t>
+        </is>
+      </c>
+      <c r="P7" s="13" t="n">
+        <v>1109</v>
+      </c>
+      <c r="Q7" s="14" t="n">
+        <v>1159</v>
+      </c>
+      <c r="R7" s="13" t="n">
+        <v>2967</v>
+      </c>
+      <c r="S7" s="13" t="n">
+        <v>510.2</v>
+      </c>
+      <c r="T7" s="13" t="inlineStr">
+        <is>
+          <t>80 1/2"L X 58"W X 54"H</t>
+        </is>
+      </c>
+      <c r="U7" s="13" t="inlineStr">
+        <is>
+          <t>Contemporary</t>
+        </is>
+      </c>
+      <c r="V7" s="13" t="inlineStr">
+        <is>
+          <t>Fabric, Acrylic, Solid Wood, Others</t>
+        </is>
+      </c>
+      <c r="W7" s="13" t="inlineStr">
+        <is>
+          <t>Contemporary,Rose Gold,Fabric, Acrylic, Solid Wood, Others,Padded Fabric Headboard w/ Radial Pleats and LED Light,Acrylic and Mirror Accents,English Dovetail Drawers with Ball-bearing Metal Side Glides,Felt-lined Top Drawer,Mirror w/ LED Light,Slat Kit Included,Optional Convertible Trundle/Drawer</t>
+        </is>
+      </c>
+      <c r="X7" s="13" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="Y7" s="13" t="n"/>
+      <c r="Z7" s="13" t="n"/>
+      <c r="AA7" s="13" t="n"/>
+      <c r="AB7" s="13" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Rose Gold</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Twin</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>CM7901RG-T-4PC</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Youth</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Bedroom Set</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>ALLIE 4 Pc. Bedroom Set</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Fabric, Acrylic, Solid Wood, and finished in Pearl White tones for a clean, cohesive look.&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
+- English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Optional Convertible Trundle&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White or Rose Gold&lt;br&gt;
+- Dresser: color: Pearl White or Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 439.56 or 442.2 or 415 or 413.22 lbs&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>ALLIE 4 Pc. Bedroom Set Twin in Rose Gold | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>The ALLIE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>ALLIE</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>4 Pc. Twin Bedroom Set</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="n"/>
+      <c r="M8" s="11" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>CM7901RG-T-HB, CM7901RG-T-FB, CM7901RG-T-R, CM7901RG-N, CM7901RG-D, CM7901RG-M</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>CM7901RG-1-Z.jpg,CM7901RG-2.jpg,CM7901RG-3.jpg,CM7901RG-4.jpg,CM7901RG-5.jpg,CM7901RG-6.jpg,CM7901RG-7.jpg</t>
+        </is>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>959</v>
+      </c>
+      <c r="Q8" s="15" t="n">
+        <v>959</v>
+      </c>
+      <c r="R8" s="11" t="n">
+        <v>2577</v>
+      </c>
+      <c r="S8" s="11" t="n">
+        <v>415</v>
+      </c>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>80 1/2"L X 41 3/4"W X 54"H</t>
+        </is>
+      </c>
+      <c r="U8" s="11" t="inlineStr">
+        <is>
+          <t>Contemporary</t>
+        </is>
+      </c>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>Fabric, Acrylic, Solid Wood, Others</t>
+        </is>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>Contemporary,Rose Gold,Fabric, Acrylic, Solid Wood, Others,Acrylic and Mirror Accents,Padded Fabric Headboard w/ Radial Pleats and LED Light,English Dovetail Drawers with Ball-bearing Metal Side Glides,Felt-lined Top Drawer,Mirror w/ LED Light,Slat Kit Included,Optional Convertible Trundle/Drawer</t>
+        </is>
+      </c>
+      <c r="X8" s="11" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="Y8" s="11" t="n"/>
+      <c r="Z8" s="11" t="n"/>
+      <c r="AA8" s="11" t="n"/>
+      <c r="AB8" s="11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Pearl White</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Twin</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>CM7901T-4PC</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Youth</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Bedroom Set</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>ALLIE 4 Pc. Bedroom Set</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Create a calm, coordinated retreat with ALLIE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Fabric, Acrylic, Solid Wood, and finished in Pearl White tones for a clean, cohesive look.&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
+- English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Optional Convertible Trundle&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White or Rose Gold&lt;br&gt;
+- Dresser: color: Pearl White or Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 439.56 or 442.2 or 415 or 413.22 lbs&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>ALLIE 4 Pc. Bedroom Set Twin in Pearl White | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>The ALLIE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>ALLIE</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>4 Pc. Twin Bedroom Set</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>CM7901T-HB, CM7901T-FB, CM7901T-R, CM7901N, CM7901D, CM7901M</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>CM7901-1-Z.jpg,CM7901-2.jpg,CM7901-3.jpg,CM7901-4.jpg</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>959</v>
+      </c>
+      <c r="Q9" s="12" t="n">
+        <v>999</v>
+      </c>
+      <c r="R9" s="11" t="n">
+        <v>2577</v>
+      </c>
+      <c r="S9" s="11" t="n">
+        <v>413.22</v>
+      </c>
+      <c r="T9" s="11" t="n"/>
+      <c r="U9" s="11" t="inlineStr">
+        <is>
+          <t>Contemporary</t>
+        </is>
+      </c>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>Fabric, Acrylic, Solid Wood, Others</t>
+        </is>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>Contemporary,Pearl White,Fabric, Acrylic, Solid Wood, Others,Padded Headboard w/Radial Pleats &amp; LED Light,Acrylic &amp; Mirror Accents,Mirror w/ LED Light,English Dovetail Drawers &amp; Ball-bearing Glides,Felt-lined Top Drawers,Optional Convertible Trundle,Foundation Required</t>
+        </is>
+      </c>
+      <c r="X9" s="11" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="Y9" s="11" t="n"/>
+      <c r="Z9" s="11" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="11" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Rose Gold</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Twin</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>CM7901RG-T-4PC-TR</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Youth</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Bedroom Set</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Acrylic, Solid Wood, construction and Pearl White tones, it blends durability with visual warmth.&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
+- English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Optional Convertible Trundle&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White or Rose Gold&lt;br&gt;
+- Dresser: color: Pearl White or Rose Gold&lt;br&gt;
+- Trundle: color: Pearl White or Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 506.76 or 510.2 or 483 or 480.42 lbs&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle Twin in Rose Gold | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>The ALLIE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>ALLIE</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>4 Pc. Twin Bedroom Set w/ Trundle</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>CM7901RG-T-HB, CM7901RG-T-FB, CM7901RG-T-R, CM7901RG-N, CM7901RG-D, CM7901RG-M, CM7901RG-TR</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>CM7901RG-1-Z.jpg,CM7901RG-2.jpg,CM7901RG-3.jpg,CM7901RG-4.jpg,CM7901RG-5.jpg,CM7901RG-6.jpg,CM7901RG-7.jpg</t>
+        </is>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>1069</v>
+      </c>
+      <c r="Q10" s="16" t="n">
+        <v>1069</v>
+      </c>
+      <c r="R10" s="13" t="n">
+        <v>2877</v>
+      </c>
+      <c r="S10" s="13" t="n">
+        <v>483</v>
+      </c>
+      <c r="T10" s="13" t="inlineStr">
+        <is>
+          <t>80 1/2"L X 41 3/4"W X 54"H</t>
+        </is>
+      </c>
+      <c r="U10" s="13" t="inlineStr">
+        <is>
+          <t>Contemporary</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="inlineStr">
+        <is>
+          <t>Fabric, Acrylic, Solid Wood, Others</t>
+        </is>
+      </c>
+      <c r="W10" s="13" t="inlineStr">
+        <is>
+          <t>Contemporary,Rose Gold,Fabric, Acrylic, Solid Wood, Others,Acrylic and Mirror Accents,Padded Fabric Headboard w/ Radial Pleats and LED Light,English Dovetail Drawers with Ball-bearing Metal Side Glides,Felt-lined Top Drawer,Mirror w/ LED Light,Slat Kit Included,Optional Convertible Trundle/Drawer</t>
+        </is>
+      </c>
+      <c r="X10" s="13" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="Y10" s="13" t="n"/>
+      <c r="Z10" s="13" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="13" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Youth, Bedroom Set, ALLIE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Bedroom Furniture Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Pearl White</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Twin</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>CM7901T-4PC-TR</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Youth</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Bedroom Set</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALLIE 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Acrylic, Solid Wood, construction and Pearl White tones, it blends durability with visual warmth.&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Padded Headboard w/ Radial Pleats &amp;amp; LED Light&lt;br&gt;
+- English Dovetail Drawers &amp;amp; Ball-bearing Glides&lt;br&gt;
+- Felt-lined Top Drawers&lt;br&gt;
+- Optional Convertible Trundle&lt;br&gt;
+- Foundation Required Included items and dimensions:&lt;br&gt;
+- Nightstand: color: Pearl White or Rose Gold&lt;br&gt;
+- Dresser: color: Pearl White or Rose Gold&lt;br&gt;
+- Trundle: color: Pearl White or Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Acrylic, Solid Wood, Others.&lt;br&gt;
+Color: Pearl White or Rose Gold&lt;br&gt;
+Weight: 506.76 or 510.2 or 483 or 480.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
@@ -2257,7 +2253,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2316,19 +2312,19 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 82 1/4"L X 58"W X 54"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 82 1/4"L X 58"W X 54"H / 82 3/4"L X 59"W X 58"H / 88 1/4 "L X 65"W X 58"H / 87 3/4"L X 65"W X 58"H / 82 1/4"L X 43"W X 54"H / 82 3/4"L X 43"W X 58"H&lt;br&gt;
+Size: Full/Queen/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard&lt;br&gt;
 - Button Tufted&lt;br&gt;
 - Crystal-like Acrylic Buttons&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Rose Gold&lt;br&gt;
+- Dresser: color: Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 396.34 lbs&lt;/p&gt;</t>
+Weight: 396.34 or 399.18 or 414.08 or 415.1 or 377.92 or 387.36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
@@ -2412,7 +2408,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2470,20 +2466,20 @@
       <c r="G13" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with ARISTON 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Leatherette, Mirror, Solid Wood, Wood Veneer, then finished in Rose Gold tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 82 3/4"L X 59"W X 58"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 58"W X 54"H / 82 3/4"L X 59"W X 58"H / 88 1/4 "L X 65"W X 58"H / 87 3/4"L X 65"W X 58"H / 82 1/4"L X 43"W X 54"H / 82 3/4"L X 43"W X 58"H&lt;br&gt;
+Size: Full/Queen/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard&lt;br&gt;
 - Button Tufted&lt;br&gt;
 - Crystal-like Acrylic Buttons&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Rose Gold&lt;br&gt;
+- Dresser: color: Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 399.18 lbs&lt;/p&gt;</t>
+Weight: 396.34 or 399.18 or 414.08 or 415.1 or 377.92 or 387.36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
@@ -2567,7 +2563,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2625,20 +2621,20 @@
       <c r="G14" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ARISTON 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Leatherette, Mirror, Solid Wood, Wood Veneer, construction and Rose Gold tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 88 1/4 "L X 65"W X 58"H&lt;br&gt;
-Size: Queen&lt;/p&gt;
+ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 58"W X 54"H / 82 3/4"L X 59"W X 58"H / 88 1/4 "L X 65"W X 58"H / 87 3/4"L X 65"W X 58"H / 82 1/4"L X 43"W X 54"H / 82 3/4"L X 43"W X 58"H&lt;br&gt;
+Size: Full/Queen/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard&lt;br&gt;
 - Button Tufted&lt;br&gt;
 - Crystal-like Acrylic Buttons&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Rose Gold&lt;br&gt;
+- Dresser: color: Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 414.08 lbs&lt;/p&gt;</t>
+Weight: 396.34 or 399.18 or 414.08 or 415.1 or 377.92 or 387.36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -2722,7 +2718,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2780,20 +2776,20 @@
       <c r="G15" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Rose Gold tones, the Leatherette, Mirror, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 87 3/4"L X 65"W X 58"H&lt;br&gt;
-Size: Queen&lt;/p&gt;
+ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 58"W X 54"H / 82 3/4"L X 59"W X 58"H / 88 1/4 "L X 65"W X 58"H / 87 3/4"L X 65"W X 58"H / 82 1/4"L X 43"W X 54"H / 82 3/4"L X 43"W X 58"H&lt;br&gt;
+Size: Full/Queen/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard&lt;br&gt;
 - Button Tufted&lt;br&gt;
 - Crystal-like Acrylic Buttons&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Rose Gold&lt;br&gt;
+- Dresser: color: Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 415.1 lbs&lt;/p&gt;</t>
+Weight: 396.34 or 399.18 or 414.08 or 415.1 or 377.92 or 387.36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -2877,7 +2873,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2935,20 +2931,20 @@
       <c r="G16" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with ARISTON 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 82 1/4"L X 43"W X 54"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 58"W X 54"H / 82 3/4"L X 59"W X 58"H / 88 1/4 "L X 65"W X 58"H / 87 3/4"L X 65"W X 58"H / 82 1/4"L X 43"W X 54"H / 82 3/4"L X 43"W X 58"H&lt;br&gt;
+Size: Full/Queen/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard&lt;br&gt;
 - Button Tufted&lt;br&gt;
 - Crystal-like Acrylic Buttons&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Rose Gold&lt;br&gt;
+- Dresser: color: Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 377.92 lbs&lt;/p&gt;</t>
+Weight: 396.34 or 399.18 or 414.08 or 415.1 or 377.92 or 387.36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -3032,7 +3028,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -3090,20 +3086,20 @@
       <c r="G17" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ARISTON 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Leatherette, Mirror, Solid Wood, Wood Veneer, then finished in Rose Gold tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 82 3/4"L X 43"W X 58"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+ARISTON 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Leatherette, Mirror, Solid Wood, Wood Veneer, and finished in Rose Gold tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 82 1/4"L X 58"W X 54"H / 82 3/4"L X 59"W X 58"H / 88 1/4 "L X 65"W X 58"H / 87 3/4"L X 65"W X 58"H / 82 1/4"L X 43"W X 54"H / 82 3/4"L X 43"W X 58"H&lt;br&gt;
+Size: Full/Queen/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard&lt;br&gt;
 - Button Tufted&lt;br&gt;
 - Crystal-like Acrylic Buttons&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Rose Gold; dimensions: 28" W x 17"D x 28" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Rose Gold; dimensions: 64" W x 17"D x 38" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Rose Gold&lt;br&gt;
+- Dresser: color: Rose Gold&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Rose Gold&lt;br&gt;
-Weight: 387.36 lbs&lt;/p&gt;</t>
+Weight: 396.34 or 399.18 or 414.08 or 415.1 or 377.92 or 387.36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
@@ -3187,7 +3183,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3246,8 +3242,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 BELVA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Finished in White tones, the Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 82"L X 58"W X 57 7/8"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 82"L X 58"W X 57 7/8"H / 82"L X 43"W X 56"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
 - Button Tufted Headboard w/ Nailhead Trim&lt;br&gt;
@@ -3257,11 +3253,11 @@
 - USB Charger in Night Stand&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand w/ USB: color: White; dimensions: 24" L X16" W x 27" H; feature: Traditional&lt;br&gt;
-- Dresser: color: White; dimensions: 56" L x 17" W x 37" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+- Nightstand w/ USB: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 374 lbs&lt;/p&gt;</t>
+Weight: 374 or 356.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
@@ -3345,7 +3341,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3403,9 +3399,9 @@
       <c r="G19" s="19" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELVA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Built from Leatherette, Solid Wood, and finished in White tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 82"L X 43"W X 56"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+BELVA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Finished in White tones, the Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 82"L X 58"W X 57 7/8"H / 82"L X 43"W X 56"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
 - Button Tufted Headboard w/ Nailhead Trim&lt;br&gt;
@@ -3415,11 +3411,11 @@
 - USB Charger in Night Stand&lt;br&gt;
 - Felt-lined Top Drawers&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand w/ USB: color: White; dimensions: 24" L X16" W x 27" H; feature: Traditional&lt;br&gt;
-- Dresser: color: White; dimensions: 56" L x 17" W x 37" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+- Nightstand w/ USB: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 356.4 lbs&lt;/p&gt;</t>
+Weight: 374 or 356.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H19" s="19" t="inlineStr">
@@ -3503,7 +3499,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3653,7 +3649,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3802,7 +3798,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3951,7 +3947,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -4010,8 +4006,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 CASTILE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 81 3/4"L X 60 7/8"W X 54"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 81 3/4"L X 60 7/8"W X 54"H / 81 3/4"L X 45 5/8"W X 54"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Crown Molding Details&lt;br&gt;
 - Cup Pulls and Round Knobs&lt;br&gt;
@@ -4020,11 +4016,11 @@
 - Full-extension Ball Bearing Glides&lt;br&gt;
 - USB Port on Night Stand&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand w/ USB: color: White; dimensions: 26" W x 16"D x 28" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 56" W x 18"D x 36" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand w/ USB: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 546.84 lbs&lt;/p&gt;</t>
+Weight: 546.84 or 513.18 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -4108,7 +4104,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4166,9 +4162,9 @@
       <c r="G24" s="21" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CASTILE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in White tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 81 3/4"L X 45 5/8"W X 54"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+CASTILE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 81 3/4"L X 60 7/8"W X 54"H / 81 3/4"L X 45 5/8"W X 54"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Crown Molding Details&lt;br&gt;
 - Cup Pulls and Round Knobs&lt;br&gt;
@@ -4177,11 +4173,11 @@
 - Full-extension Ball Bearing Glides&lt;br&gt;
 - USB Port on Night Stand&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand w/ USB: color: White; dimensions: 26" W x 16"D x 28" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 56" W x 18"D x 36" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand w/ USB: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 513.18 lbs&lt;/p&gt;</t>
+Weight: 546.84 or 513.18 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -4265,7 +4261,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4324,8 +4320,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 CASTLILE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Wood, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 83"L X 60 7/8"W X 52"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 83"L X 60 7/8"W X 52"H / 83"L X 45 5/8"W X 52"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Crown Molding Detail&lt;br&gt;
 - Cup Pulls and Round Knobs&lt;br&gt;
@@ -4334,11 +4330,11 @@
 - Full-extension Ball Bearing Glides&lt;br&gt;
 - USB Port on Night Stand&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand w/ USB: color: Gray; dimensions: 26" W x 16"D x 28" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Gray; dimensions: 56" W x 18"D x 36" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand w/ USB: color: Gray&lt;br&gt;
+- Dresser: color: Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: Gray&lt;br&gt;
-Weight: 534.6 lbs&lt;/p&gt;</t>
+Weight: 534.6 or 512.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -4422,7 +4418,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4480,9 +4476,9 @@
       <c r="G26" s="23" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with CASTLILE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 83"L X 45 5/8"W X 52"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+CASTLILE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Wood, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 83"L X 60 7/8"W X 52"H / 83"L X 45 5/8"W X 52"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Crown Molding Detail&lt;br&gt;
 - Cup Pulls and Round Knobs&lt;br&gt;
@@ -4491,11 +4487,11 @@
 - Full-extension Ball Bearing Glides&lt;br&gt;
 - USB Port on Night Stand&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand w/ USB: color: Gray; dimensions: 26" W x 16"D x 28" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Gray; dimensions: 56" W x 18"D x 36" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand w/ USB: color: Gray&lt;br&gt;
+- Dresser: color: Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: Gray&lt;br&gt;
-Weight: 512.6 lbs&lt;/p&gt;</t>
+Weight: 534.6 or 512.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
@@ -4579,7 +4575,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4638,14 +4634,14 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Create a calm, coordinated retreat with CRESWELL 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and Mahogany tones, it blends durability with visual warmth.&lt;br&gt;
-Size: Full&lt;/p&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Mahogany; dimensions: 21" W x 15"D x 25" H; feature: Rustic&lt;br&gt;
-- Dresser: color: Mahogany; dimensions: 52" W x 20.5"D x 34" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand: color: Mahogany&lt;br&gt;
+- Dresser: color: Mahogany&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: Mahogany&lt;br&gt;
-Weight: 205.6 lbs&lt;/p&gt;</t>
+Weight: 205.6 or 185.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H27" s="25" t="inlineStr">
@@ -4725,7 +4721,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -4783,15 +4779,15 @@
       <c r="G28" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CRESWELL 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Rustic character adds definition without feeling heavy. Finished in Mahogany tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Create a calm, coordinated retreat with CRESWELL 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Rustic styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and Mahogany tones, it blends durability with visual warmth.&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rustic Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Mahogany; dimensions: 21" W x 15"D x 25" H; feature: Rustic&lt;br&gt;
-- Dresser: color: Mahogany; dimensions: 52" W x 20.5"D x 34" H; feature: Rustic&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand: color: Mahogany&lt;br&gt;
+- Dresser: color: Mahogany&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: Mahogany&lt;br&gt;
-Weight: 185.8 lbs&lt;/p&gt;</t>
+Weight: 205.6 or 185.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H28" s="25" t="inlineStr">
@@ -4871,7 +4867,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4930,16 +4926,16 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 DANI 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in White tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H / 80 1/2"L X 42 1/4"W X 44 1/4"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 286 lbs&lt;/p&gt;</t>
+Weight: 286 or 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H29" s="27" t="inlineStr">
@@ -5023,7 +5019,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -5082,17 +5078,17 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Create a calm, coordinated retreat with DANI 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in White tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H / 80 1/2"L X 42 1/4"W X 44 1/4"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
-- Trundle: color: White; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;br&gt;
+- Trundle: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 385 lbs&lt;/p&gt;</t>
+Weight: 385 or 363 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" s="29" t="inlineStr">
@@ -5176,7 +5172,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -5234,17 +5230,17 @@
       <c r="G31" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-DANI 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Wood, Wood Veneer, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 42 1/4"W X 44 1/4"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+DANI 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H / 80 1/2"L X 42 1/4"W X 44 1/4"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 264 lbs&lt;/p&gt;</t>
+Weight: 286 or 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" s="27" t="inlineStr">
@@ -5328,7 +5324,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5386,18 +5382,18 @@
       <c r="G32" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-DANI 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in White tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 42 1/4"W X 44 1/4"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Create a calm, coordinated retreat with DANI 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H / 80 1/2"L X 42 1/4"W X 44 1/4"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
-- Trundle: color: White; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;br&gt;
+- Trundle: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 363 lbs&lt;/p&gt;</t>
+Weight: 385 or 363 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H32" s="29" t="inlineStr">
@@ -5481,7 +5477,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5540,18 +5536,18 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 DIANE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in Blue tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H / 80 1/2"L X 41 3/8"W X 44 1/4"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
 - Round Finials&lt;br&gt;
 - Optional Armoire &amp;amp; Closet Storage&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Blue&lt;br&gt;
+- Dresser: color: Blue&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Blue&lt;br&gt;
-Weight: 286 lbs&lt;/p&gt;</t>
+Weight: 286 or 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H33" s="31" t="inlineStr">
@@ -5635,7 +5631,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5694,19 +5690,19 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Create a calm, coordinated retreat with DIANE 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in Blue tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H / 80 1/2"L X 41 3/8"W X 44 1/4"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
 - Round Finials&lt;br&gt;
 - Optional Armoire &amp;amp; Closet Storage&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
-- Trundle: color: Blue; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Blue&lt;br&gt;
+- Dresser: color: Blue&lt;br&gt;
+- Trundle: color: Blue&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Blue&lt;br&gt;
-Weight: 385 lbs&lt;/p&gt;</t>
+Weight: 385 or 363 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H34" s="33" t="inlineStr">
@@ -5790,7 +5786,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -5848,19 +5844,19 @@
       <c r="G35" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-DIANE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Solid Wood, Wood Veneer, construction and Blue tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 41 3/8"W X 44 1/4"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+DIANE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in Blue tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H / 80 1/2"L X 41 3/8"W X 44 1/4"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
 - Round Finials&lt;br&gt;
 - Optional Armoire &amp;amp; Closet Storage&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Blue&lt;br&gt;
+- Dresser: color: Blue&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Blue&lt;br&gt;
-Weight: 264 lbs&lt;/p&gt;</t>
+Weight: 286 or 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" s="31" t="inlineStr">
@@ -5944,7 +5940,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -6002,20 +5998,20 @@
       <c r="G36" s="33" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-DIANE 4 Pc. Bedroom Set w/ Trundle brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Blue tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 80 1/2"L X 41 3/8"W X 44 1/4"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Create a calm, coordinated retreat with DIANE 4 Pc. Bedroom Set w/ Trundle. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in Blue tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 80 1/2"L X 57 1/2"W X 44 1/4"H / 80 1/2"L X 41 3/8"W X 44 1/4"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Plank Panel Headboard &amp;amp; Footboard&lt;br&gt;
 - Round Finials&lt;br&gt;
 - Optional Armoire &amp;amp; Closet Storage&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Blue; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Blue; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
-- Trundle: color: Blue; dimensions: 75 1 or 8" L x 41 1 or 2" W x 11 3 or 8" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Blue&lt;br&gt;
+- Dresser: color: Blue&lt;br&gt;
+- Trundle: color: Blue&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Blue&lt;br&gt;
-Weight: 363 lbs&lt;/p&gt;</t>
+Weight: 385 or 363 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H36" s="33" t="inlineStr">
@@ -6099,7 +6095,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -6249,7 +6245,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6308,8 +6304,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Create a calm, coordinated retreat with LAREINA 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Pearl White tones, the Solid Rubberwood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 58"W X 80.5"D X 52"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 58"W X 80.5"D X 52"H / 42.5"W X 80.5"D X 52"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Hidden Jewelry Drawers in Dresser&lt;br&gt;
 - Embossed Panels&lt;br&gt;
@@ -6318,11 +6314,11 @@
 - Metal Glide&lt;br&gt;
 - English Dovetails&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Pearl White; dimensions: 22.5" W x 17"D x 24" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Pearl White; dimensions: 54.5" W x 17"D x 34" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood.&lt;br&gt;
+- Nightstand: color: Pearl White&lt;br&gt;
+- Dresser: color: Pearl White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood or Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
 Color: Pearl White&lt;br&gt;
-Weight: 514.58 lbs&lt;/p&gt;</t>
+Weight: 514.58 or 516.81 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H38" s="35" t="inlineStr">
@@ -6406,7 +6402,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -6464,9 +6460,9 @@
       <c r="G39" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LAREINA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Fabric, Solid Rubberwood, Engineered Wood and finished in Pearl White tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 42.5"W X 80.5"D X 52"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Create a calm, coordinated retreat with LAREINA 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Pearl White tones, the Solid Rubberwood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 58"W X 80.5"D X 52"H / 42.5"W X 80.5"D X 52"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Hidden Jewelry Drawers in Dresser&lt;br&gt;
 - Embossed Panels&lt;br&gt;
@@ -6475,11 +6471,11 @@
 - Metal Glide&lt;br&gt;
 - English Dovetails&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Pearl White; dimensions: 22.5" W x 17"D x 24" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: Pearl White; dimensions: 54.5" W x 17"D x 34" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
+- Nightstand: color: Pearl White&lt;br&gt;
+- Dresser: color: Pearl White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Engineered Wood or Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
 Color: Pearl White&lt;br&gt;
-Weight: 516.81 lbs&lt;/p&gt;</t>
+Weight: 514.58 or 516.81 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H39" s="35" t="inlineStr">
@@ -6563,7 +6559,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -6716,7 +6712,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -6870,7 +6866,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -6929,17 +6925,17 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Oak tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H / 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Round Tapered Legs&lt;br&gt;
 - Recessed Drawer Handles&lt;br&gt;
 - Slat Kit Included Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Oak; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
-- Dresser: color: Oak; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Oak&lt;br&gt;
-Weight: 397.7 lbs&lt;/p&gt;</t>
+- Nightstand: color: Oak or Black or Gray or White&lt;br&gt;
+- Dresser: color: Oak or Black or Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Black or Gray or White&lt;br&gt;
+Weight: 397.7 or 385.71 or 344.8 or 388.9 or 373.4 or 367.71 or 321.4 or 363.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H42" s="37" t="inlineStr">
@@ -7023,7 +7019,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -7081,18 +7077,18 @@
       <c r="G43" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LENNART 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Crafted with Solid Wood, Wood Veneer, then finished in Black tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Oak tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H / 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Round Tapered Legs&lt;br&gt;
 - Recessed Drawer Handles&lt;br&gt;
 - Slat Kit Included Included items and dimensions:&lt;br&gt;
-- II Nightstand: color: Black; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
-- II Dresser: color: Black; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 385.71 lbs&lt;/p&gt;</t>
+- Nightstand: color: Oak or Black or Gray or White&lt;br&gt;
+- Dresser: color: Oak or Black or Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Black or Gray or White&lt;br&gt;
+Weight: 397.7 or 385.71 or 344.8 or 388.9 or 373.4 or 367.71 or 321.4 or 363.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H43" s="37" t="inlineStr">
@@ -7176,7 +7172,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -7234,18 +7230,18 @@
       <c r="G44" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LENNART 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. With Solid Wood, Wood Veneer, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Oak tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H / 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Round Tapered Legs&lt;br&gt;
 - Recessed Drawer Handles&lt;br&gt;
 - Slat Kit Included Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Gray; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
-- Dresser: color: Gray; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 344.8 lbs&lt;/p&gt;</t>
+- Nightstand: color: Oak or Black or Gray or White&lt;br&gt;
+- Dresser: color: Oak or Black or Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Black or Gray or White&lt;br&gt;
+Weight: 397.7 or 385.71 or 344.8 or 388.9 or 373.4 or 367.71 or 321.4 or 363.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" s="37" t="inlineStr">
@@ -7329,7 +7325,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -7387,18 +7383,18 @@
       <c r="G45" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Oak tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H / 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Round Tapered Legs&lt;br&gt;
 - Recessed Drawer Handles&lt;br&gt;
 - Slat Kit Included Included items and dimensions:&lt;br&gt;
-- II Nightstand: color: White; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
-- II Dresser: color: White; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 388.9 lbs&lt;/p&gt;</t>
+- Nightstand: color: Oak or Black or Gray or White&lt;br&gt;
+- Dresser: color: Oak or Black or Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Black or Gray or White&lt;br&gt;
+Weight: 397.7 or 385.71 or 344.8 or 388.9 or 373.4 or 367.71 or 321.4 or 363.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" s="37" t="inlineStr">
@@ -7482,7 +7478,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -7540,18 +7536,18 @@
       <c r="G46" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. With Solid Wood, Wood Veneer, construction and Oak tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Oak tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H / 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Round Tapered Legs&lt;br&gt;
 - Recessed Drawer Handles&lt;br&gt;
 - Slat Kit Included Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Oak; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
-- Dresser: color: Oak; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Oak&lt;br&gt;
-Weight: 373.4 lbs&lt;/p&gt;</t>
+- Nightstand: color: Oak or Black or Gray or White&lt;br&gt;
+- Dresser: color: Oak or Black or Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Black or Gray or White&lt;br&gt;
+Weight: 397.7 or 385.71 or 344.8 or 388.9 or 373.4 or 367.71 or 321.4 or 363.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H46" s="37" t="inlineStr">
@@ -7635,7 +7631,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -7693,18 +7689,18 @@
       <c r="G47" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LENNART 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. Finished in Black tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Oak tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H / 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Round Tapered Legs&lt;br&gt;
 - Recessed Drawer Handles&lt;br&gt;
 - Slat Kit Included Included items and dimensions:&lt;br&gt;
-- II Nightstand: color: Black; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
-- II Dresser: color: Black; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 367.71 lbs&lt;/p&gt;</t>
+- Nightstand: color: Oak or Black or Gray or White&lt;br&gt;
+- Dresser: color: Oak or Black or Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Black or Gray or White&lt;br&gt;
+Weight: 397.7 or 385.71 or 344.8 or 388.9 or 373.4 or 367.71 or 321.4 or 363.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H47" s="37" t="inlineStr">
@@ -7788,7 +7784,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -7846,18 +7842,18 @@
       <c r="G48" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LENNART 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Built from Solid Wood, Wood Veneer, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Oak tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H / 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Round Tapered Legs&lt;br&gt;
 - Recessed Drawer Handles&lt;br&gt;
 - Slat Kit Included Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Gray; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
-- Dresser: color: Gray; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 321.4 lbs&lt;/p&gt;</t>
+- Nightstand: color: Oak or Black or Gray or White&lt;br&gt;
+- Dresser: color: Oak or Black or Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Black or Gray or White&lt;br&gt;
+Weight: 397.7 or 385.71 or 344.8 or 388.9 or 373.4 or 367.71 or 321.4 or 363.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H48" s="37" t="inlineStr">
@@ -7941,7 +7937,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -7999,18 +7995,18 @@
       <c r="G49" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Wood Veneer, then finished in White tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Create a calm, coordinated retreat with LENNART 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in Oak tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 81 1/2"L X 58 1/2"W X 48"H / 81 1/2"L X 43 1/2"W X 48"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Round Tapered Legs&lt;br&gt;
 - Recessed Drawer Handles&lt;br&gt;
 - Slat Kit Included Included items and dimensions:&lt;br&gt;
-- II Nightstand: color: White; dimensions: 23 5 or 8" W x 17"D x 24" H; feature: Mid-Century Modern&lt;br&gt;
-- II Dresser: color: White; dimensions: 58" W x 17"D x 35 7 or 8" H; feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 363.6 lbs&lt;/p&gt;</t>
+- Nightstand: color: Oak or Black or Gray or White&lt;br&gt;
+- Dresser: color: Oak or Black or Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Black or Gray or White&lt;br&gt;
+Weight: 397.7 or 385.71 or 344.8 or 388.9 or 373.4 or 367.71 or 321.4 or 363.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" s="37" t="inlineStr">
@@ -8094,7 +8090,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -8153,16 +8149,16 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LYCORIDA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Light Gray tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: BED: 80 1/4"L X 56 3/4"W X 54"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: BED: 80 1/4"L X 56 3/4"W X 54"H / BED: 80 1/4"L X 42"W X 54"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - #REF!&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Light Gray; dimensions: 19" W x 16"D x 21 1 or 2" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Light Gray; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand: color: Light Gray&lt;br&gt;
+- Dresser: color: Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: Light Gray&lt;br&gt;
-Weight: 365.2 lbs&lt;/p&gt;</t>
+Weight: 365.2 or 338.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -8246,7 +8242,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -8304,22 +8300,17 @@
       <c r="G51" s="9" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LYCORIDA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Solid Wood, and finished in Light Gray tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: BED: 80 1/4"L X 42"W X 54"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+LYCORIDA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Light Gray tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: BED: 80 1/4"L X 56 3/4"W X 54"H / BED: 80 1/4"L X 42"W X 54"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Molding Details&lt;br&gt;
-- Dovetail Drawers&lt;br&gt;
-- Ball-bearing Glides&lt;br&gt;
-- Felt-lined Top Drawer&lt;br&gt;
-- Chrome Hanging Pulls&lt;br&gt;
-- Trundle Converts to Drawers&lt;br&gt;
+- #REF!&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Light Gray; dimensions: 19" W x 16"D x 21 1 or 2" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Light Gray; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand: color: Light Gray&lt;br&gt;
+- Dresser: color: Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: Light Gray&lt;br&gt;
-Weight: 338.8 lbs&lt;/p&gt;</t>
+Weight: 365.2 or 338.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -8403,7 +8394,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -8462,18 +8453,18 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LYCORIS 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Solid Wood, Engineered Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 56.5"W X 80"D X 54"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 56.5"W X 80"D X 54"H / 81.5"W X 43"D X 47"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Poster Design w/ Finials&lt;br&gt;
 - Molding Details&lt;br&gt;
 - Trundle Converts into Drawers&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21.5" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 357.4 lbs&lt;/p&gt;</t>
+Weight: 357.4 or 331 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -8557,7 +8548,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -8615,19 +8606,19 @@
       <c r="G53" s="13" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LYCORIS 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Solid Wood, Engineered Wood construction and White tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 81.5"W X 43"D X 47"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+LYCORIS 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Solid Wood, Engineered Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 56.5"W X 80"D X 54"H / 81.5"W X 43"D X 47"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Poster Design w/ Finials&lt;br&gt;
 - Molding Details&lt;br&gt;
 - Trundle Converts into Drawers&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21.5" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 331 lbs&lt;/p&gt;</t>
+Weight: 357.4 or 331 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -8711,7 +8702,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -8770,8 +8761,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MARILLA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Solid Wood, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H / 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bookcase Headboard&lt;br&gt;
 - Painted Hardware&lt;br&gt;
@@ -8779,11 +8770,11 @@
 - Optional Underbed Trundle&lt;br&gt;
 - Optional Underbed Trundle and Drawers Combo&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 267.3 lbs&lt;/p&gt;</t>
+Weight: 267.3 or 247.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
@@ -8867,7 +8858,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8926,8 +8917,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Create a calm, coordinated retreat with MARILLA 4 Pc. Bedroom Set w/ Storage. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H / 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bookcase Headboard&lt;br&gt;
 - Painted Hardware&lt;br&gt;
@@ -8935,12 +8926,12 @@
 - Optional Underbed Trundle&lt;br&gt;
 - Optional Underbed Trundle and Drawers Combo&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
-- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;br&gt;
+- Underbed Storage w/ Sliding Doors: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 320.1 lbs&lt;/p&gt;</t>
+Weight: 320.1 or 300.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H55" s="19" t="inlineStr">
@@ -9024,7 +9015,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -9082,9 +9073,9 @@
       <c r="G56" s="17" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MARILLA 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Solid Wood, and finished in White tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+MARILLA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Solid Wood, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H / 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bookcase Headboard&lt;br&gt;
 - Painted Hardware&lt;br&gt;
@@ -9092,11 +9083,11 @@
 - Optional Underbed Trundle&lt;br&gt;
 - Optional Underbed Trundle and Drawers Combo&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 247.5 lbs&lt;/p&gt;</t>
+Weight: 267.3 or 247.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
@@ -9180,7 +9171,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -9238,9 +9229,9 @@
       <c r="G57" s="19" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MARILLA 4 Pc. Bedroom Set w/ Storage brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Create a calm, coordinated retreat with MARILLA 4 Pc. Bedroom Set w/ Storage. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H / 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bookcase Headboard&lt;br&gt;
 - Painted Hardware&lt;br&gt;
@@ -9248,12 +9239,12 @@
 - Optional Underbed Trundle&lt;br&gt;
 - Optional Underbed Trundle and Drawers Combo&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34" H; feature: Transitional&lt;br&gt;
-- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;br&gt;
+- Underbed Storage w/ Sliding Doors: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 300.3 lbs&lt;/p&gt;</t>
+Weight: 320.1 or 300.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H57" s="19" t="inlineStr">
@@ -9337,7 +9328,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -9396,8 +9387,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MARLEE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in White tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 85 1/4"W X 59"D X 50"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 85 1/4"W X 59"D X 50"H / 85 1/4"W X 44"D X 50"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bookcase Headboard&lt;br&gt;
 - Storage on Both Sides of Headboard&lt;br&gt;
@@ -9405,11 +9396,11 @@
 - English Dovetail Drawer Construction&lt;br&gt;
 - Round Drawer Pulls&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34 1 or 8" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 341 lbs&lt;/p&gt;</t>
+Weight: 341 or 321.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H58" s="23" t="inlineStr">
@@ -9493,7 +9484,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -9551,9 +9542,9 @@
       <c r="G59" s="23" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with MARLEE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Solid Wood, Wood Veneer, and finished in White tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 85 1/4"W X 44"D X 50"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+MARLEE 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in White tones, the Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 85 1/4"W X 59"D X 50"H / 85 1/4"W X 44"D X 50"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bookcase Headboard&lt;br&gt;
 - Storage on Both Sides of Headboard&lt;br&gt;
@@ -9561,11 +9552,11 @@
 - English Dovetail Drawer Construction&lt;br&gt;
 - Round Drawer Pulls&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 19" W x 16"D x 21" H; feature: Transitional&lt;br&gt;
-- Dresser: color: White; dimensions: 48" W x 17"D x 34 1 or 8" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 321.2 lbs&lt;/p&gt;</t>
+Weight: 341 or 321.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H59" s="23" t="inlineStr">
@@ -9649,7 +9640,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -9708,8 +9699,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 OLIVIA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Leatherette, Solid Wood, Wood Veneer, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 80 1/4"L X 58 3/4"W X 55"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 80 1/4"L X 58 3/4"W X 55"H / 80 1/4"L X 44"W X 55"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
 - Padded Camelback Headboard&lt;br&gt;
@@ -9717,11 +9708,11 @@
 - Optional Trundle&lt;br&gt;
 - Turned Legs&lt;br&gt;
 - Slat Kit Included Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 24" W x 16"D x 26 5 or 8" H; feature: Traditional&lt;br&gt;
-- Dresser: color: White; dimensions: 53" W x 17"D x 34" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 372.9 lbs&lt;/p&gt;</t>
+Weight: 372.9 or 349.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H60" s="25" t="inlineStr">
@@ -9805,7 +9796,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -9863,9 +9854,9 @@
       <c r="G61" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with OLIVIA 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in White tones, the Leatherette, Solid Wood, Wood Veneer, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 80 1/4"L X 44"W X 55"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+OLIVIA 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Leatherette, Solid Wood, Wood Veneer, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 80 1/4"L X 58 3/4"W X 55"H / 80 1/4"L X 44"W X 55"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
 - Padded Camelback Headboard&lt;br&gt;
@@ -9873,11 +9864,11 @@
 - Optional Trundle&lt;br&gt;
 - Turned Legs&lt;br&gt;
 - Slat Kit Included Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White; dimensions: 24" W x 16"D x 26 5 or 8" H; feature: Traditional&lt;br&gt;
-- Dresser: color: White; dimensions: 53" W x 17"D x 34" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: White&lt;br&gt;
+- Dresser: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 349.8 lbs&lt;/p&gt;</t>
+Weight: 372.9 or 349.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="25" t="inlineStr">
@@ -9961,7 +9952,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -10020,8 +10011,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 PRIAM 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Solid Wood, then finished in White or Gray tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 79 5/8"L X 56 1/4"W X 50"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 79 5/8"L X 56 1/4"W X 50"H / 79 5/8"L X 41 1/2"W X 50"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - White or Gray&lt;br&gt;
 - Two-tone Color&lt;br&gt;
@@ -10031,11 +10022,11 @@
 - Dovetail Drawers&lt;br&gt;
 - Trundle Converts to Drawers&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Nightstand: color: White or Gray; dimensions: 22" W x 15 3 or 4"D x 23 7 or 8" H; feature: Contemporary&lt;br&gt;
-- Dresser: color: White or Gray; dimensions: 47 5 or 8" W x 18"D x 33 7 or 8" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand: color: White or Gray&lt;br&gt;
+- Dresser: color: White or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White or Gray&lt;br&gt;
-Weight: 306.3 lbs&lt;/p&gt;</t>
+Weight: 306.3 or 283 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="27" t="inlineStr">
@@ -10119,7 +10110,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -10177,9 +10168,9 @@
       <c r="G63" s="27" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PRIAM 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Solid Wood, construction and White or Gray tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 79 5/8"L X 41 1/2"W X 50"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+PRIAM 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Solid Wood, then finished in White or Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 79 5/8"L X 56 1/4"W X 50"H / 79 5/8"L X 41 1/2"W X 50"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - White or Gray&lt;br&gt;
 - Two-tone Color&lt;br&gt;
@@ -10189,11 +10180,11 @@
 - Dovetail Drawers&lt;br&gt;
 - Trundle Converts to Drawers&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Dresser: color: White or Gray; dimensions: 47 5 or 8" W x 18"D x 33 7 or 8" H; feature: Contemporary&lt;br&gt;
-- Nightstand: color: White or Gray; dimensions: 22" W x 15 3 or 4"D x 23 7 or 8" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Nightstand: color: White or Gray&lt;br&gt;
+- Dresser: color: White or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White or Gray&lt;br&gt;
-Weight: 283 lbs&lt;/p&gt;</t>
+Weight: 306.3 or 283 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="27" t="inlineStr">
@@ -10277,7 +10268,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -10336,7 +10327,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Create a calm, coordinated retreat with ROANNE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, Wood Veneer, and finished in Gray or Charcoal tones for a clean, cohesive look.&lt;br&gt;
-Size: Full&lt;/p&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Gray or Charcoal&lt;br&gt;
 - Button-Tufted&lt;br&gt;
@@ -10344,11 +10335,11 @@
 - Optional Trundle&lt;br&gt;
 - Black Rectangular Pulls&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Gray; dimensions: 19" W x 16 3 or 8"D x 24" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Gray; dimensions: 47 1 or 4" W x 16 3 or 8"D x 31 5 or 8" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Gray or Charcoal&lt;br&gt;
+- Dresser: color: Gray or Charcoal&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Gray or Charcoal&lt;br&gt;
-Weight: 272.9 lbs&lt;/p&gt;</t>
+Weight: 272.9 or 258.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" s="31" t="inlineStr">
@@ -10428,7 +10419,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -10486,8 +10477,8 @@
       <c r="G65" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ROANNE 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Fabric, Solid Wood, Wood Veneer, then finished in Gray or Charcoal tones to suit a range of interiors.&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Create a calm, coordinated retreat with ROANNE 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, Wood Veneer, and finished in Gray or Charcoal tones for a clean, cohesive look.&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Gray or Charcoal&lt;br&gt;
 - Button-Tufted&lt;br&gt;
@@ -10495,11 +10486,11 @@
 - Optional Trundle&lt;br&gt;
 - Black Rectangular Pulls&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Gray; dimensions: 19" W x 16 3 or 8"D x 24" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Gray; dimensions: 47 1 or 4" W x 16 3 or 8"D x 31 5 or 8" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Gray or Charcoal&lt;br&gt;
+- Dresser: color: Gray or Charcoal&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Gray or Charcoal&lt;br&gt;
-Weight: 258.7 lbs&lt;/p&gt;</t>
+Weight: 272.9 or 258.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" s="31" t="inlineStr">
@@ -10579,7 +10570,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -10638,19 +10629,19 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 VEVEY 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Solid Wood, Wood Veneer, and finished in Wire-Brushed Warm Gray tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 82 1/2"L X 58 3/8"W X 50"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 82 1/2"L X 58 3/8"W X 50"H / 82 1/2"L X 42 7/8"W X 50"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Felt-lined Top Drawer&lt;br&gt;
 - Optional Convertible Trundle&lt;br&gt;
 - Wood Grain Texture&lt;br&gt;
 - Round Pull Knobs&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Wire-Brushed Warm Gray; dimensions: 22" L x 15 3 or 4" W x 23 7 or 8" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Wire-Brushed Warm Gray; dimensions: 47 5 or 8" L x 18" W x 33 7 or 8" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Wire-Brushed Warm Gray&lt;br&gt;
+- Dresser: color: Wire-Brushed Warm Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Wire-Brushed Warm Gray&lt;br&gt;
-Weight: 293.7 lbs&lt;/p&gt;</t>
+Weight: 293.7 or 283.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" s="33" t="inlineStr">
@@ -10734,7 +10725,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
@@ -10792,20 +10783,20 @@
       <c r="G67" s="33" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-VEVEY 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Solid Wood, Wood Veneer, then finished in Wire-Brushed Warm Gray tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 82 1/2"L X 42 7/8"W X 50"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+VEVEY 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Solid Wood, Wood Veneer, and finished in Wire-Brushed Warm Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 82 1/2"L X 58 3/8"W X 50"H / 82 1/2"L X 42 7/8"W X 50"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Felt-lined Top Drawer&lt;br&gt;
 - Optional Convertible Trundle&lt;br&gt;
 - Wood Grain Texture&lt;br&gt;
 - Round Pull Knobs&lt;br&gt;
 - Foundation Required Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Wire-Brushed Warm Gray; dimensions: 22" L x 15 3 or 4" W x 23 7 or 8" H; feature: Transitional&lt;br&gt;
-- Dresser: color: Wire-Brushed Warm Gray; dimensions: 47 5 or 8" L x 18" W x 33 7 or 8" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+- Nightstand: color: Wire-Brushed Warm Gray&lt;br&gt;
+- Dresser: color: Wire-Brushed Warm Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Wire-Brushed Warm Gray&lt;br&gt;
-Weight: 283.8 lbs&lt;/p&gt;</t>
+Weight: 293.7 or 283.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" s="33" t="inlineStr">
@@ -10889,7 +10880,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -10948,19 +10939,19 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ZOHAR 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Finished in Pink tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 88 1/8"L X 76 1/2"W X 56 1/2"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 88 1/8"L X 76 1/2"W X 56 1/2"H / 88 1/8"L X 82 1/2"W X 56 1/2"H / 88 1/8"L X 62 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Full/Queen/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Fully Upholstered&lt;br&gt;
 - Wingback Design&lt;br&gt;
 - Button Tufted Headboard&lt;br&gt;
 - Crystal-Like Acrylic Buttons&lt;br&gt;
 - Cabriole Legs Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam&lt;br&gt;
-- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam&lt;/p&gt;
-&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+- Nightstand: color: Pink&lt;br&gt;
+- Dresser: color: Pink&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood, Others.&lt;br&gt;
 Color: Pink&lt;br&gt;
-Weight: 512.16 lbs&lt;/p&gt;</t>
+Weight: 512.16 or 530.16 or 482.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" s="35" t="inlineStr">
@@ -11044,7 +11035,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -11102,20 +11093,20 @@
       <c r="G69" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZOHAR 4 Pc. Bedroom Set brings a restful, finished feel to the bedroom. This youth bedroom set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Built from Velvet-like, Solid Wood, and finished in Pink tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 88 1/8"L X 82 1/2"W X 56 1/2"H&lt;br&gt;
-Size: Queen&lt;/p&gt;
+ZOHAR 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Finished in Pink tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 88 1/8"L X 76 1/2"W X 56 1/2"H / 88 1/8"L X 82 1/2"W X 56 1/2"H / 88 1/8"L X 62 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Full/Queen/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Fully Upholstered&lt;br&gt;
 - Wingback Design&lt;br&gt;
 - Button Tufted Headboard&lt;br&gt;
 - Crystal-Like Acrylic Buttons&lt;br&gt;
 - Cabriole Legs Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam&lt;br&gt;
-- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam&lt;/p&gt;
-&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+- Nightstand: color: Pink&lt;br&gt;
+- Dresser: color: Pink&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood, Others.&lt;br&gt;
 Color: Pink&lt;br&gt;
-Weight: 530.16 lbs&lt;/p&gt;</t>
+Weight: 512.16 or 530.16 or 482.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H69" s="35" t="inlineStr">
@@ -11199,7 +11190,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -11257,20 +11248,20 @@
       <c r="G70" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Create a calm, coordinated retreat with ZOHAR 4 Pc. Bedroom Set. Designed as a youth bedroom set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Crafted with Velvet-like, Solid Wood, then finished in Pink tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 88 1/8"L X 62 1/2"W X 56 1/2"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+ZOHAR 4 Pc. Bedroom Set completes the bedroom with a relaxed, pulled-together look. As a youth bedroom set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Finished in Pink tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 88 1/8"L X 76 1/2"W X 56 1/2"H / 88 1/8"L X 82 1/2"W X 56 1/2"H / 88 1/8"L X 62 1/2"W X 56 1/2"H&lt;br&gt;
+Size: Full/Queen/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Fully Upholstered&lt;br&gt;
 - Wingback Design&lt;br&gt;
 - Button Tufted Headboard&lt;br&gt;
 - Crystal-Like Acrylic Buttons&lt;br&gt;
 - Cabriole Legs Included items and dimensions:&lt;br&gt;
-- Nightstand: color: Pink; dimensions: 23" W x 17 1 or 2"D x 26" H; feature: Glam&lt;br&gt;
-- Dresser: color: Pink; dimensions: 58 1 or 2" W x 17 1 or 2"D x 36" H; feature: Glam&lt;/p&gt;
-&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+- Nightstand: color: Pink&lt;br&gt;
+- Dresser: color: Pink&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood, Others.&lt;br&gt;
 Color: Pink&lt;br&gt;
-Weight: 482.46 lbs&lt;/p&gt;</t>
+Weight: 512.16 or 530.16 or 482.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H70" s="35" t="inlineStr">
@@ -11354,7 +11345,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -11505,7 +11496,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -11657,7 +11648,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -11717,15 +11708,15 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LAREINA Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. As a youth bed, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Pearl White tones, the Fabric, Solid Rubberwood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 58"W X 80.5"D X 52"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Embossed Panels&lt;br&gt;
 - Acrylic Handles &amp;amp; Front Legs w/ Back Metal Legs&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Trundle: color: Pearl White; dimensions: 41" W x 75"D x 11" H; feature: Contemporary&lt;/p&gt;
+- Trundle: color: Pearl White&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
 Color: Pearl White&lt;br&gt;
-Weight: 256.62 lbs&lt;/p&gt;</t>
+Weight: 256.62 or 258.85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H73" s="44" t="inlineStr">
@@ -11809,7 +11800,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -11867,17 +11858,17 @@
       <c r="G74" s="44" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LAREINA Bed w/ Trundle is designed for everyday living, balancing comfort with a clean, finished look. This youth bed is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Built from Fabric, Solid Rubberwood, Engineered Wood and finished in Pearl White tones for a clean, cohesive look.&lt;br&gt;
+LAREINA Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. As a youth bed, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Pearl White tones, the Fabric, Solid Rubberwood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: 58"W X 80.5"D X 52"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Embossed Panels&lt;br&gt;
 - Acrylic Handles &amp;amp; Front Legs w/ Back Metal Legs&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Trundle: color: Pearl White; dimensions: 41" W x 75"D x 11" H; feature: Contemporary&lt;/p&gt;
+- Trundle: color: Pearl White&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Solid Rubberwood, Engineered Wood.&lt;br&gt;
 Color: Pearl White&lt;br&gt;
-Weight: 258.85 lbs&lt;/p&gt;</t>
+Weight: 256.62 or 258.85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" s="44" t="inlineStr">
@@ -11961,7 +11952,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -12020,12 +12011,12 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LYCORIDA Bed w/ Trundle offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a youth bed, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Engineered Wood, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 56.5"W X 80"D X 54"H&lt;br&gt;
-Size: Full Included items and dimensions:&lt;br&gt;
-- Trundle or Drawer: color: Light Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 203.5 lbs&lt;/p&gt;</t>
+Product Dimensions: 56.5"W X 80"D X 54"H / 80 1/4"L X 56 3/4"W X 54"H / 42"W X 80"D X 54"H / 80 1/4"L X 42"W X 54"H&lt;br&gt;
+Size: Full/Twin&lt;br&gt;
+- Trundle or Drawer: color: Gray or White or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood or Transitional.&lt;br&gt;
+Color: Gray or White or Light Gray&lt;br&gt;
+Weight: 203.5 or 177.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
@@ -12109,7 +12100,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -12167,13 +12158,13 @@
       <c r="G76" s="11" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LYCORIDA Bed w/ Trundle creates a cohesive setup that feels inviting the moment you walk in. As a youth bed, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Solid Wood, Engineered Wood construction and White tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 80 1/4"L X 56 3/4"W X 54"H&lt;br&gt;
-Size: Full Included items and dimensions:&lt;br&gt;
-- Trundle or Drawer: color: White; dimensions: 75.5" W x 40.5"D x 11" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 203.5 lbs&lt;/p&gt;</t>
+LYCORIDA Bed w/ Trundle offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a youth bed, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Engineered Wood, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 56.5"W X 80"D X 54"H / 80 1/4"L X 56 3/4"W X 54"H / 42"W X 80"D X 54"H / 80 1/4"L X 42"W X 54"H&lt;br&gt;
+Size: Full/Twin&lt;br&gt;
+- Trundle or Drawer: color: Gray or White or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood or Transitional.&lt;br&gt;
+Color: Gray or White or Light Gray&lt;br&gt;
+Weight: 203.5 or 177.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
@@ -12257,7 +12248,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
@@ -12315,13 +12306,13 @@
       <c r="G77" s="11" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LYCORIDA Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. This youth bed is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Light Gray tones, the Solid Wood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 42"W X 80"D X 54"H&lt;br&gt;
-Size: Twin Included items and dimensions:&lt;br&gt;
-- Trundle or Drawer: color: Light Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
-Weight: 177.1 lbs&lt;/p&gt;</t>
+LYCORIDA Bed w/ Trundle offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a youth bed, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Engineered Wood, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 56.5"W X 80"D X 54"H / 80 1/4"L X 56 3/4"W X 54"H / 42"W X 80"D X 54"H / 80 1/4"L X 42"W X 54"H&lt;br&gt;
+Size: Full/Twin&lt;br&gt;
+- Trundle or Drawer: color: Gray or White or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood or Transitional.&lt;br&gt;
+Color: Gray or White or Light Gray&lt;br&gt;
+Weight: 203.5 or 177.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
@@ -12409,7 +12400,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -12467,13 +12458,13 @@
       <c r="G78" s="11" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LYCORIDA Bed w/ Trundle is designed for everyday living, balancing comfort with a clean, finished look. Designed as a youth bed, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Transitional and finished in White tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 80 1/4"L X 42"W X 54"H&lt;br&gt;
-Size: Twin Included items and dimensions:&lt;br&gt;
-- Trundle or Drawer: color: White; dimensions: 75.5" W x 40.5"D x 11" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Transitional.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 177.1 lbs&lt;/p&gt;</t>
+LYCORIDA Bed w/ Trundle offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a youth bed, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Solid Wood, Engineered Wood, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 56.5"W X 80"D X 54"H / 80 1/4"L X 56 3/4"W X 54"H / 42"W X 80"D X 54"H / 80 1/4"L X 42"W X 54"H&lt;br&gt;
+Size: Full/Twin&lt;br&gt;
+- Trundle or Drawer: color: Gray or White or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood or Transitional.&lt;br&gt;
+Color: Gray or White or Light Gray&lt;br&gt;
+Weight: 203.5 or 177.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
@@ -12557,7 +12548,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -12616,8 +12607,8 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MARILLA Bed w/ Storage creates a cohesive setup that feels inviting the moment you walk in. Designed as a youth bed, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H&lt;br&gt;
-Size: Full&lt;/p&gt;
+Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H / 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bookcase Headboard&lt;br&gt;
 - Painted Hardware&lt;br&gt;
@@ -12625,10 +12616,10 @@
 - Optional Underbed Trundle&lt;br&gt;
 - Optional Underbed Trundle and Drawers Combo&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Underbed Storage w/ Sliding Doors: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 176 lbs&lt;/p&gt;</t>
+Weight: 176 or 156.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H79" s="21" t="inlineStr">
@@ -12712,7 +12703,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -12770,9 +12761,9 @@
       <c r="G80" s="21" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MARILLA Bed w/ Storage brings a composed, welcoming feel to the room without overwhelming the space. As a youth bed, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in White tones, the Solid Wood, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
-Size: Twin&lt;/p&gt;
+MARILLA Bed w/ Storage creates a cohesive setup that feels inviting the moment you walk in. Designed as a youth bed, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Solid Wood, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 86"L X 57 3/4"W X 46 5/8"H / 86"L X 42 7/8"W X 46 5/8"H&lt;br&gt;
+Size: Full/Twin&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bookcase Headboard&lt;br&gt;
 - Painted Hardware&lt;br&gt;
@@ -12780,10 +12771,10 @@
 - Optional Underbed Trundle&lt;br&gt;
 - Optional Underbed Trundle and Drawers Combo&lt;br&gt;
 - Mattress Ready Included items and dimensions:&lt;br&gt;
-- Underbed Storage w/ Sliding Doors: color: White; dimensions: 75 1 or 2" L X15 3 or 4 " W x 10 1 or 2" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+- Underbed Storage w/ Sliding Doors: color: White&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Others.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 156.2 lbs&lt;/p&gt;</t>
+Weight: 176 or 156.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H80" s="21" t="inlineStr">
@@ -12867,7 +12858,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
@@ -12926,12 +12917,12 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 PRIAM Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. Designed as a youth bed, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 56"W X 79.5"D X 50"H&lt;br&gt;
-Size: Full Included items and dimensions:&lt;br&gt;
-- Trundle or Drawers: color: White or Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Contemporary&lt;/p&gt;
+Product Dimensions: 56"W X 79.5"D X 50"H / 41.5"W X 79.5"D X 50"H&lt;br&gt;
+Size: Full/Twin&lt;br&gt;
+- Trundle or Drawers: color: White&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 195.3 lbs&lt;/p&gt;</t>
+Weight: 195.3 or 172 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H81" s="29" t="inlineStr">
@@ -13019,7 +13010,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -13077,13 +13068,13 @@
       <c r="G82" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PRIAM Bed w/ Trundle is designed for everyday living, balancing comfort with a clean, finished look. As a youth bed, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Solid Wood, Engineered Wood and finished in White tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 41.5"W X 79.5"D X 50"H&lt;br&gt;
-Size: Twin Included items and dimensions:&lt;br&gt;
-- Trundle or Drawers: color: White or Gray; dimensions: 75 5 or 8" L x 40 3 or 4" W x 11" H; feature: Contemporary&lt;/p&gt;
+PRIAM Bed w/ Trundle brings a composed, welcoming feel to the room without overwhelming the space. Designed as a youth bed, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in White tones, the Solid Wood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 56"W X 79.5"D X 50"H / 41.5"W X 79.5"D X 50"H&lt;br&gt;
+Size: Full/Twin&lt;br&gt;
+- Trundle or Drawers: color: White&lt;/p&gt;
 &lt;p&gt;Materials: Solid Wood, Engineered Wood.&lt;br&gt;
 Color: White&lt;br&gt;
-Weight: 172 lbs&lt;/p&gt;</t>
+Weight: 195.3 or 172 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H82" s="29" t="inlineStr">
@@ -13171,7 +13162,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr">

--- a/FOA SETS/Youth-Set.xlsx
+++ b/FOA SETS/Youth-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>CM7458WH-F-4PC</t>
+          <t>CM7458WH-T-4PC</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>ALECIA 4 Pc. Bedroom Set Full in White | GOODDEGG</t>
+          <t>ALECIA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>The ALECIA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALECIA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" s="9" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L2" s="9" t="n"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="N2" s="9" t="inlineStr">
         <is>
-          <t>CM7458WH-F-HB, CM7458WH-F-FB, CM7458WH-F-R, CM7458WH-N, CM7458WH-D, CM7458WH-M</t>
+          <t>CM7458WH-T-HB, CM7458WH-T-FB, CM7458WH-T-R, CM7458WH-N, CM7458WH-D, CM7458WH-M</t>
         </is>
       </c>
       <c r="O2" s="9" t="inlineStr">
@@ -833,20 +833,20 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>989</v>
+        <v>939</v>
       </c>
       <c r="Q2" s="10" t="n">
-        <v>989</v>
+        <v>939</v>
       </c>
       <c r="R2" s="9" t="n">
-        <v>2577</v>
+        <v>2427</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>330</v>
+        <v>305.8</v>
       </c>
       <c r="T2" s="9" t="inlineStr">
         <is>
-          <t>80 1/2"L X 58 5/8"W X 54"H</t>
+          <t>80 1/2"L X 43 5/8"W X 52"H</t>
         </is>
       </c>
       <c r="U2" s="9" t="inlineStr">
@@ -873,7 +873,7 @@
       <c r="Z2" s="9" t="n"/>
       <c r="AA2" s="9" t="n"/>
       <c r="AB2" s="9" t="n">
-        <v>50.2</v>
+        <v>47.5</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -909,12 +909,12 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>CM7458WH-T-4PC</t>
+          <t>CM7458WH-F-4PC</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>ALECIA 4 Pc. Bedroom Set Twin in White | GOODDEGG</t>
+          <t>ALECIA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>The ALECIA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALECIA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L3" s="9" t="n"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>CM7458WH-T-HB, CM7458WH-T-FB, CM7458WH-T-R, CM7458WH-N, CM7458WH-D, CM7458WH-M</t>
+          <t>CM7458WH-F-HB, CM7458WH-F-FB, CM7458WH-F-R, CM7458WH-N, CM7458WH-D, CM7458WH-M</t>
         </is>
       </c>
       <c r="O3" s="9" t="inlineStr">
@@ -989,20 +989,20 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>939</v>
+        <v>989</v>
       </c>
       <c r="Q3" s="10" t="n">
-        <v>939</v>
+        <v>989</v>
       </c>
       <c r="R3" s="9" t="n">
-        <v>2427</v>
+        <v>2577</v>
       </c>
       <c r="S3" s="9" t="n">
-        <v>305.8</v>
+        <v>330</v>
       </c>
       <c r="T3" s="9" t="inlineStr">
         <is>
-          <t>80 1/2"L X 43 5/8"W X 52"H</t>
+          <t>80 1/2"L X 58 5/8"W X 54"H</t>
         </is>
       </c>
       <c r="U3" s="9" t="inlineStr">
@@ -1029,7 +1029,7 @@
       <c r="Z3" s="9" t="n"/>
       <c r="AA3" s="9" t="n"/>
       <c r="AB3" s="9" t="n">
-        <v>47.5</v>
+        <v>50.2</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>ALLIE 4 Pc. Bedroom Set Full in Pearl White | GOODDEGG</t>
+          <t>ALLIE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>The ALLIE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALLIE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>ALLIE 4 Pc. Bedroom Set Full in Rose Gold | GOODDEGG</t>
+          <t>ALLIE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>The ALLIE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALLIE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle Full in Pearl White | GOODDEGG</t>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>The ALLIE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle Full in Rose Gold | GOODDEGG</t>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>The ALLIE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>ALLIE 4 Pc. Bedroom Set Twin in Rose Gold | GOODDEGG</t>
+          <t>ALLIE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>The ALLIE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALLIE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>ALLIE 4 Pc. Bedroom Set Twin in Pearl White | GOODDEGG</t>
+          <t>ALLIE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>The ALLIE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALLIE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle Twin in Rose Gold | GOODDEGG</t>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>The ALLIE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle Twin in Pearl White | GOODDEGG</t>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>The ALLIE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALLIE 4 Pc. Bedroom Set w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>ARISTON 4 Pc. Bedroom Set Full in Rose Gold | GOODDEGG</t>
+          <t>ARISTON 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>The ARISTON Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARISTON 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J12" s="17" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>ARISTON 4 Pc. Bedroom Set Full in Rose Gold | GOODDEGG</t>
+          <t>ARISTON 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>The ARISTON Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARISTON 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J13" s="17" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>ARISTON 4 Pc. Bedroom Set Queen in Rose Gold | GOODDEGG</t>
+          <t>ARISTON 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>The ARISTON Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARISTON 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J14" s="17" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>ARISTON 4 Pc. Bedroom Set Queen in Rose Gold | GOODDEGG</t>
+          <t>ARISTON 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>The ARISTON Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARISTON 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J15" s="17" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>ARISTON 4 Pc. Bedroom Set Twin in Rose Gold | GOODDEGG</t>
+          <t>ARISTON 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>The ARISTON Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARISTON 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J16" s="17" t="inlineStr">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>ARISTON 4 Pc. Bedroom Set Twin in Rose Gold | GOODDEGG</t>
+          <t>ARISTON 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>The ARISTON Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARISTON 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J17" s="17" t="inlineStr">
@@ -3215,12 +3215,12 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>CM7174F-4PC</t>
+          <t>CM7174T-4PC</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>BELVA 4 Pc. Bedroom Set Full in White | GOODDEGG</t>
+          <t>BELVA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>The BELVA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELVA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J18" s="19" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="K18" s="19" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L18" s="19" t="n"/>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>CM7174F-HB, CM7174F-FB, CM7174F-R, CM7174N, CM7174D, CM7174M</t>
+          <t>CM7174T-HB, CM7174T-FB, CM7174T-R, CM7174N, CM7174D, CM7174M</t>
         </is>
       </c>
       <c r="O18" s="19" t="inlineStr">
@@ -3297,20 +3297,20 @@
         </is>
       </c>
       <c r="P18" s="19" t="n">
-        <v>909</v>
+        <v>829</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>959</v>
+        <v>859</v>
       </c>
       <c r="R18" s="19" t="n">
-        <v>2277</v>
+        <v>2097</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>374</v>
+        <v>356.4</v>
       </c>
       <c r="T18" s="19" t="inlineStr">
         <is>
-          <t>82"L X 58"W X 57 7/8"H</t>
+          <t>82"L X 43"W X 56"H</t>
         </is>
       </c>
       <c r="U18" s="19" t="inlineStr">
@@ -3337,7 +3337,7 @@
       <c r="Z18" s="19" t="n"/>
       <c r="AA18" s="19" t="n"/>
       <c r="AB18" s="19" t="n">
-        <v>55.9</v>
+        <v>52.3</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -3373,12 +3373,12 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>CM7174T-4PC</t>
+          <t>CM7174F-4PC</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="H19" s="19" t="inlineStr">
         <is>
-          <t>BELVA 4 Pc. Bedroom Set Twin in White | GOODDEGG</t>
+          <t>BELVA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I19" s="19" t="inlineStr">
         <is>
-          <t>The BELVA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELVA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J19" s="19" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="K19" s="19" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L19" s="19" t="n"/>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>CM7174T-HB, CM7174T-FB, CM7174T-R, CM7174N, CM7174D, CM7174M</t>
+          <t>CM7174F-HB, CM7174F-FB, CM7174F-R, CM7174N, CM7174D, CM7174M</t>
         </is>
       </c>
       <c r="O19" s="19" t="inlineStr">
@@ -3455,20 +3455,20 @@
         </is>
       </c>
       <c r="P19" s="19" t="n">
-        <v>829</v>
+        <v>909</v>
       </c>
       <c r="Q19" s="20" t="n">
-        <v>859</v>
+        <v>959</v>
       </c>
       <c r="R19" s="19" t="n">
-        <v>2097</v>
+        <v>2277</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>356.4</v>
+        <v>374</v>
       </c>
       <c r="T19" s="19" t="inlineStr">
         <is>
-          <t>82"L X 43"W X 56"H</t>
+          <t>82"L X 58"W X 57 7/8"H</t>
         </is>
       </c>
       <c r="U19" s="19" t="inlineStr">
@@ -3495,7 +3495,7 @@
       <c r="Z19" s="19" t="n"/>
       <c r="AA19" s="19" t="n"/>
       <c r="AB19" s="19" t="n">
-        <v>52.3</v>
+        <v>55.9</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CARA 4 Pc. Bedroom Set Twin in Cherry | GOODDEGG</t>
+          <t>CARA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>The CARA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CARA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CAREN 4 Pc. Bedroom Set Twin in White | GOODDEGG</t>
+          <t>CAREN 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>The CAREN Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAREN 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CARUS 4 Pc. Bedroom Set Twin in Cherry | GOODDEGG</t>
+          <t>CARUS 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>The CARUS Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CARUS 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>CM7413WH-F-4PC</t>
+          <t>CM7413WH-T-4PC</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t>CASTILE 4 Pc. Bedroom Set Full in White | GOODDEGG</t>
+          <t>CASTILE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
-          <t>The CASTILE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CASTILE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="K23" s="21" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L23" s="21" t="n"/>
@@ -4051,29 +4051,29 @@
       </c>
       <c r="N23" s="21" t="inlineStr">
         <is>
-          <t>CM7413WH-F-1, CM7413WH-F-2, CM7413WH-F-3, CM7413WH-4-DR, CM7413WH-N, CM7413WH-D, CM7413WH-M</t>
+          <t>CM7413WH-T-1, CM7413WH-T-2, CM7413WH-T-3, CM7413WH-4-DR, CM7413WH-N, CM7413WH-D, CM7413WH-M</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
         <is>
-          <t>CM7413WH-1-Z.jpg,CM7413WH-2.jpg</t>
+          <t>CM7413WH-T-1-Z.jpg,CM7413WH-2.jpg</t>
         </is>
       </c>
       <c r="P23" s="21" t="n">
-        <v>1169</v>
+        <v>1129</v>
       </c>
       <c r="Q23" s="22" t="n">
         <v>1199</v>
       </c>
       <c r="R23" s="21" t="n">
-        <v>2967</v>
+        <v>2847</v>
       </c>
       <c r="S23" s="21" t="n">
-        <v>546.84</v>
+        <v>513.1799999999999</v>
       </c>
       <c r="T23" s="21" t="inlineStr">
         <is>
-          <t>81 3/4"L X 60 7/8"W X 54"H</t>
+          <t>81 3/4"L X 45 5/8"W X 54"H</t>
         </is>
       </c>
       <c r="U23" s="21" t="inlineStr">
@@ -4100,7 +4100,7 @@
       <c r="Z23" s="21" t="n"/>
       <c r="AA23" s="21" t="n"/>
       <c r="AB23" s="21" t="n">
-        <v>78.5</v>
+        <v>76</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>CM7413WH-T-4PC</t>
+          <t>CM7413WH-F-4PC</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
-          <t>CASTILE 4 Pc. Bedroom Set Twin in White | GOODDEGG</t>
+          <t>CASTILE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
         <is>
-          <t>The CASTILE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CASTILE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="K24" s="21" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L24" s="21" t="n"/>
@@ -4208,29 +4208,29 @@
       </c>
       <c r="N24" s="21" t="inlineStr">
         <is>
-          <t>CM7413WH-T-1, CM7413WH-T-2, CM7413WH-T-3, CM7413WH-4-DR, CM7413WH-N, CM7413WH-D, CM7413WH-M</t>
+          <t>CM7413WH-F-1, CM7413WH-F-2, CM7413WH-F-3, CM7413WH-4-DR, CM7413WH-N, CM7413WH-D, CM7413WH-M</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
         <is>
-          <t>CM7413WH-T-1-Z.jpg,CM7413WH-2.jpg</t>
+          <t>CM7413WH-1-Z.jpg,CM7413WH-2.jpg</t>
         </is>
       </c>
       <c r="P24" s="21" t="n">
-        <v>1129</v>
+        <v>1169</v>
       </c>
       <c r="Q24" s="22" t="n">
         <v>1199</v>
       </c>
       <c r="R24" s="21" t="n">
-        <v>2847</v>
+        <v>2967</v>
       </c>
       <c r="S24" s="21" t="n">
-        <v>513.1799999999999</v>
+        <v>546.84</v>
       </c>
       <c r="T24" s="21" t="inlineStr">
         <is>
-          <t>81 3/4"L X 45 5/8"W X 54"H</t>
+          <t>81 3/4"L X 60 7/8"W X 54"H</t>
         </is>
       </c>
       <c r="U24" s="21" t="inlineStr">
@@ -4257,7 +4257,7 @@
       <c r="Z24" s="21" t="n"/>
       <c r="AA24" s="21" t="n"/>
       <c r="AB24" s="21" t="n">
-        <v>76</v>
+        <v>78.5</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -4293,12 +4293,12 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>CM7413GY-F-4PC</t>
+          <t>CM7413GY-T-4PC</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>CASTLILE 4 Pc. Bedroom Set Full in Gray | GOODDEGG</t>
+          <t>CASTLILE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
         <is>
-          <t>The CASTLILE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CASTLILE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="K25" s="23" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L25" s="23" t="n"/>
@@ -4365,29 +4365,29 @@
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>CM7413GY-F-1, CM7413GY-F-2, CM7413GY-F-3, CM7413GY-4-DR, CM7413GY-N, CM7413GY-D, CM7413GY-M</t>
+          <t>CM7413GY-T-1, CM7413GY-T-2, CM7413GY-T-3, CM7413GY-4-DR, CM7413GY-N, CM7413GY-D, CM7413GY-M</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
         <is>
-          <t>CM7413GY-1-Z.jpg,CM7413GY-2.jpg,CM7413GY-5.jpg</t>
+          <t>CM7413GY-T-1-Z.jpg,CM7413GY-2.jpg,CM7413GY-5.jpg</t>
         </is>
       </c>
       <c r="P25" s="23" t="n">
-        <v>1169</v>
+        <v>1119</v>
       </c>
       <c r="Q25" s="24" t="n">
         <v>1199</v>
       </c>
       <c r="R25" s="23" t="n">
-        <v>2967</v>
+        <v>2847</v>
       </c>
       <c r="S25" s="23" t="n">
-        <v>534.6</v>
+        <v>512.6</v>
       </c>
       <c r="T25" s="23" t="inlineStr">
         <is>
-          <t>83"L X 60 7/8"W X 52"H</t>
+          <t>83"L X 45 5/8"W X 52"H</t>
         </is>
       </c>
       <c r="U25" s="23" t="inlineStr">
@@ -4414,7 +4414,7 @@
       <c r="Z25" s="23" t="n"/>
       <c r="AA25" s="23" t="n"/>
       <c r="AB25" s="23" t="n">
-        <v>78</v>
+        <v>76.2</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>CM7413GY-T-4PC</t>
+          <t>CM7413GY-F-4PC</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H26" s="23" t="inlineStr">
         <is>
-          <t>CASTLILE 4 Pc. Bedroom Set Twin in Gray | GOODDEGG</t>
+          <t>CASTLILE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>The CASTLILE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CASTLILE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="K26" s="23" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L26" s="23" t="n"/>
@@ -4522,29 +4522,29 @@
       </c>
       <c r="N26" s="23" t="inlineStr">
         <is>
-          <t>CM7413GY-T-1, CM7413GY-T-2, CM7413GY-T-3, CM7413GY-4-DR, CM7413GY-N, CM7413GY-D, CM7413GY-M</t>
+          <t>CM7413GY-F-1, CM7413GY-F-2, CM7413GY-F-3, CM7413GY-4-DR, CM7413GY-N, CM7413GY-D, CM7413GY-M</t>
         </is>
       </c>
       <c r="O26" s="23" t="inlineStr">
         <is>
-          <t>CM7413GY-T-1-Z.jpg,CM7413GY-2.jpg,CM7413GY-5.jpg</t>
+          <t>CM7413GY-1-Z.jpg,CM7413GY-2.jpg,CM7413GY-5.jpg</t>
         </is>
       </c>
       <c r="P26" s="23" t="n">
-        <v>1119</v>
+        <v>1169</v>
       </c>
       <c r="Q26" s="24" t="n">
         <v>1199</v>
       </c>
       <c r="R26" s="23" t="n">
-        <v>2847</v>
+        <v>2967</v>
       </c>
       <c r="S26" s="23" t="n">
-        <v>512.6</v>
+        <v>534.6</v>
       </c>
       <c r="T26" s="23" t="inlineStr">
         <is>
-          <t>83"L X 45 5/8"W X 52"H</t>
+          <t>83"L X 60 7/8"W X 52"H</t>
         </is>
       </c>
       <c r="U26" s="23" t="inlineStr">
@@ -4571,7 +4571,7 @@
       <c r="Z26" s="23" t="n"/>
       <c r="AA26" s="23" t="n"/>
       <c r="AB26" s="23" t="n">
-        <v>76.2</v>
+        <v>78</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>AM7972MH-F-4PC</t>
+          <t>AM7972MH-T-4PC</t>
         </is>
       </c>
       <c r="D27" s="25" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="H27" s="25" t="inlineStr">
         <is>
-          <t>CRESWELL 4 Pc. Bedroom Set Full in Mahogany | GOODDEGG</t>
+          <t>CRESWELL 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I27" s="25" t="inlineStr">
         <is>
-          <t>The CRESWELL Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRESWELL 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J27" s="25" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="K27" s="25" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L27" s="25" t="n"/>
@@ -4672,25 +4672,25 @@
       </c>
       <c r="N27" s="25" t="inlineStr">
         <is>
-          <t>AM7972MH-F-HBFB, AM7972MH-F-R, AM7002MH-N, AM7002MH-D, AM7002MH-M</t>
+          <t>AM7972MH-T-HBFB, AM7972MH-T-R, AM7002MH-N, AM7002MH-D, AM7002MH-M</t>
         </is>
       </c>
       <c r="O27" s="25" t="inlineStr">
         <is>
-          <t>AM7972MH-T-4PC-1.jpg,AM7972MH-F-1.jpg,AM7972MH-F-WB-1.jpg,AM7972MH-F-WB-2.jpg,AM7972MH-F-WB-3.jpg</t>
+          <t>AM7972MH-T-4PC-1.jpg,AM7972MH-T-1.jpg,AM7972MH-T-WB-1.jpg,AM7972MH-T-WB-2.jpg,AM7972MH-T-WB-3.jpg</t>
         </is>
       </c>
       <c r="P27" s="25" t="n">
-        <v>729</v>
+        <v>699</v>
       </c>
       <c r="Q27" s="26" t="n">
-        <v>729</v>
+        <v>699</v>
       </c>
       <c r="R27" s="25" t="n">
-        <v>2187</v>
+        <v>2097</v>
       </c>
       <c r="S27" s="25" t="n">
-        <v>205.6</v>
+        <v>185.8</v>
       </c>
       <c r="T27" s="25" t="n"/>
       <c r="U27" s="25" t="inlineStr">
@@ -4717,7 +4717,7 @@
       <c r="Z27" s="25" t="n"/>
       <c r="AA27" s="25" t="n"/>
       <c r="AB27" s="25" t="n">
-        <v>30.5</v>
+        <v>29.4</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>AM7972MH-T-4PC</t>
+          <t>AM7972MH-F-4PC</t>
         </is>
       </c>
       <c r="D28" s="25" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="H28" s="25" t="inlineStr">
         <is>
-          <t>CRESWELL 4 Pc. Bedroom Set Twin in Mahogany | GOODDEGG</t>
+          <t>CRESWELL 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I28" s="25" t="inlineStr">
         <is>
-          <t>The CRESWELL Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRESWELL 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J28" s="25" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="K28" s="25" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L28" s="25" t="n"/>
@@ -4818,25 +4818,25 @@
       </c>
       <c r="N28" s="25" t="inlineStr">
         <is>
-          <t>AM7972MH-T-HBFB, AM7972MH-T-R, AM7002MH-N, AM7002MH-D, AM7002MH-M</t>
+          <t>AM7972MH-F-HBFB, AM7972MH-F-R, AM7002MH-N, AM7002MH-D, AM7002MH-M</t>
         </is>
       </c>
       <c r="O28" s="25" t="inlineStr">
         <is>
-          <t>AM7972MH-T-4PC-1.jpg,AM7972MH-T-1.jpg,AM7972MH-T-WB-1.jpg,AM7972MH-T-WB-2.jpg,AM7972MH-T-WB-3.jpg</t>
+          <t>AM7972MH-T-4PC-1.jpg,AM7972MH-F-1.jpg,AM7972MH-F-WB-1.jpg,AM7972MH-F-WB-2.jpg,AM7972MH-F-WB-3.jpg</t>
         </is>
       </c>
       <c r="P28" s="25" t="n">
-        <v>699</v>
+        <v>729</v>
       </c>
       <c r="Q28" s="26" t="n">
-        <v>699</v>
+        <v>729</v>
       </c>
       <c r="R28" s="25" t="n">
-        <v>2097</v>
+        <v>2187</v>
       </c>
       <c r="S28" s="25" t="n">
-        <v>185.8</v>
+        <v>205.6</v>
       </c>
       <c r="T28" s="25" t="n"/>
       <c r="U28" s="25" t="inlineStr">
@@ -4863,7 +4863,7 @@
       <c r="Z28" s="25" t="n"/>
       <c r="AA28" s="25" t="n"/>
       <c r="AB28" s="25" t="n">
-        <v>29.4</v>
+        <v>30.5</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="H29" s="27" t="inlineStr">
         <is>
-          <t>DANI 4 Pc. Bedroom Set Full in White | GOODDEGG</t>
+          <t>DANI 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I29" s="27" t="inlineStr">
         <is>
-          <t>The DANI Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DANI 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J29" s="27" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="H30" s="29" t="inlineStr">
         <is>
-          <t>DANI 4 Pc. Bedroom Set w/ Trundle Full in White | GOODDEGG</t>
+          <t>DANI 4 Pc. Bedroom Set w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I30" s="29" t="inlineStr">
         <is>
-          <t>The DANI Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DANI 4 Pc. Bedroom Set w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J30" s="29" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="H31" s="27" t="inlineStr">
         <is>
-          <t>DANI 4 Pc. Bedroom Set Twin in White | GOODDEGG</t>
+          <t>DANI 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I31" s="27" t="inlineStr">
         <is>
-          <t>The DANI Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DANI 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J31" s="27" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H32" s="29" t="inlineStr">
         <is>
-          <t>DANI 4 Pc. Bedroom Set w/ Trundle Twin in White | GOODDEGG</t>
+          <t>DANI 4 Pc. Bedroom Set w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I32" s="29" t="inlineStr">
         <is>
-          <t>The DANI Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DANI 4 Pc. Bedroom Set w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J32" s="29" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H33" s="31" t="inlineStr">
         <is>
-          <t>DIANE 4 Pc. Bedroom Set Full in Blue | GOODDEGG</t>
+          <t>DIANE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I33" s="31" t="inlineStr">
         <is>
-          <t>The DIANE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIANE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J33" s="31" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="H34" s="33" t="inlineStr">
         <is>
-          <t>DIANE 4 Pc. Bedroom Set w/ Trundle Full in Blue | GOODDEGG</t>
+          <t>DIANE 4 Pc. Bedroom Set w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I34" s="33" t="inlineStr">
         <is>
-          <t>The DIANE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIANE 4 Pc. Bedroom Set w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J34" s="33" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="H35" s="31" t="inlineStr">
         <is>
-          <t>DIANE 4 Pc. Bedroom Set Twin in Blue | GOODDEGG</t>
+          <t>DIANE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I35" s="31" t="inlineStr">
         <is>
-          <t>The DIANE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIANE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J35" s="31" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="H36" s="33" t="inlineStr">
         <is>
-          <t>DIANE 4 Pc. Bedroom Set w/ Trundle Twin in Blue | GOODDEGG</t>
+          <t>DIANE 4 Pc. Bedroom Set w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I36" s="33" t="inlineStr">
         <is>
-          <t>The DIANE Bedroom w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIANE 4 Pc. Bedroom Set w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J36" s="33" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>GRIFFIN 4 Pc. Bedroom Set Twin in Charcoal Brown | GOODDEGG</t>
+          <t>GRIFFIN 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>The GRIFFIN Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRIFFIN 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C38" s="35" t="inlineStr">
         <is>
-          <t>FM72081WH-F-4PC</t>
+          <t>FM72081WH-T-4PC</t>
         </is>
       </c>
       <c r="D38" s="35" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="H38" s="35" t="inlineStr">
         <is>
-          <t>LAREINA 4 Pc. Bedroom Set Full in Pearl White | GOODDEGG</t>
+          <t>LAREINA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I38" s="35" t="inlineStr">
         <is>
-          <t>The LAREINA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAREINA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J38" s="35" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="K38" s="35" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L38" s="35" t="n"/>
@@ -6349,29 +6349,29 @@
       </c>
       <c r="N38" s="35" t="inlineStr">
         <is>
-          <t>FM72081WH-F-HB, FM72081WH-F-FB, FM72081WH-TF-R, FM72081WH-N, FM72081WH-D, FM72081WH-M</t>
+          <t>FM72081WH-T-HB, FM72081WH-T-FB, FM72081WH-TF-R, FM72081WH-N, FM72081WH-D, FM72081WH-M</t>
         </is>
       </c>
       <c r="O38" s="35" t="inlineStr">
         <is>
-          <t>FM72081WH-T-1-Z.jpg,FM72081WH-T-2.jpg,FM72081WH-T-4.jpg,FM72081WH-T-5.jpg,FM72081WH-T-7.jpg,FM72081WH-N-1.jpg,FM72081WH-N-2.jpg,FM72081WH-D-2.jpg,FM72081WH-D-2.jpg</t>
+          <t>FM72081WH-T-1-Z.jpg,FM72081WH-T-2.jpg,FM72081WH-T-7.jpg,FM72081WH-T-4.jpg,FM72081WH-N-1.jpg,FM72081WH-N-2.jpg,FM72081WH-N-3.jpg,FM72081WH-D-2.jpg</t>
         </is>
       </c>
       <c r="P38" s="35" t="n">
+        <v>1219</v>
+      </c>
+      <c r="Q38" s="36" t="n">
         <v>1249</v>
       </c>
-      <c r="Q38" s="36" t="n">
-        <v>1299</v>
-      </c>
       <c r="R38" s="35" t="n">
-        <v>3147</v>
+        <v>3087</v>
       </c>
       <c r="S38" s="35" t="n">
-        <v>514.58</v>
+        <v>516.8099999999999</v>
       </c>
       <c r="T38" s="35" t="inlineStr">
         <is>
-          <t>58"W X 80.5"D X 52"H</t>
+          <t>42.5"W X 80.5"D X 52"H</t>
         </is>
       </c>
       <c r="U38" s="35" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="V38" s="35" t="inlineStr">
         <is>
-          <t>Solid Rubberwood, Engineered Wood</t>
+          <t>Fabric, Solid Rubberwood, Engineered Wood</t>
         </is>
       </c>
       <c r="W38" s="35" t="inlineStr">
         <is>
-          <t>Contemporary,Pearl White,Solid Rubberwood, Engineered Wood,LED on Headboard &amp; Mirror,Beveled Mirror,Hidden Jewelry Drawers in Dresser,Embossed Panels,Acrylic Handles &amp; Front Legs w/ Back Metal Legs,Felt-Lined Top Drawer,Metal Glide,English Dovetails,Mattress Ready</t>
+          <t>Contemporary,Pearl White,Fabric, Solid Rubberwood, Engineered Wood,LED on Headboard &amp; Mirror,Beveled Mirror,Hidden Jewelry Drawers in Dresser,Embossed Panels,Acrylic Handles &amp; Front Legs w/ Back Metal Legs,Felt-Lined Top Drawer,Metal Glide,English Dovetails,Mattress Ready</t>
         </is>
       </c>
       <c r="X38" s="35" t="inlineStr">
@@ -6398,7 +6398,7 @@
       <c r="Z38" s="35" t="n"/>
       <c r="AA38" s="35" t="n"/>
       <c r="AB38" s="35" t="n">
-        <v>46.8</v>
+        <v>42.2</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C39" s="35" t="inlineStr">
         <is>
-          <t>FM72081WH-T-4PC</t>
+          <t>FM72081WH-F-4PC</t>
         </is>
       </c>
       <c r="D39" s="35" t="inlineStr">
@@ -6480,12 +6480,12 @@
       </c>
       <c r="H39" s="35" t="inlineStr">
         <is>
-          <t>LAREINA 4 Pc. Bedroom Set Twin in Pearl White | GOODDEGG</t>
+          <t>LAREINA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I39" s="35" t="inlineStr">
         <is>
-          <t>The LAREINA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAREINA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J39" s="35" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="K39" s="35" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L39" s="35" t="n"/>
@@ -6506,29 +6506,29 @@
       </c>
       <c r="N39" s="35" t="inlineStr">
         <is>
-          <t>FM72081WH-T-HB, FM72081WH-T-FB, FM72081WH-TF-R, FM72081WH-N, FM72081WH-D, FM72081WH-M</t>
+          <t>FM72081WH-F-HB, FM72081WH-F-FB, FM72081WH-TF-R, FM72081WH-N, FM72081WH-D, FM72081WH-M</t>
         </is>
       </c>
       <c r="O39" s="35" t="inlineStr">
         <is>
-          <t>FM72081WH-T-1-Z.jpg,FM72081WH-T-2.jpg,FM72081WH-T-7.jpg,FM72081WH-T-4.jpg,FM72081WH-N-1.jpg,FM72081WH-N-2.jpg,FM72081WH-N-3.jpg,FM72081WH-D-2.jpg</t>
+          <t>FM72081WH-T-1-Z.jpg,FM72081WH-T-2.jpg,FM72081WH-T-4.jpg,FM72081WH-T-5.jpg,FM72081WH-T-7.jpg,FM72081WH-N-1.jpg,FM72081WH-N-2.jpg,FM72081WH-D-2.jpg,FM72081WH-D-2.jpg</t>
         </is>
       </c>
       <c r="P39" s="35" t="n">
-        <v>1219</v>
+        <v>1249</v>
       </c>
       <c r="Q39" s="36" t="n">
-        <v>1249</v>
+        <v>1299</v>
       </c>
       <c r="R39" s="35" t="n">
-        <v>3087</v>
+        <v>3147</v>
       </c>
       <c r="S39" s="35" t="n">
-        <v>516.8099999999999</v>
+        <v>514.58</v>
       </c>
       <c r="T39" s="35" t="inlineStr">
         <is>
-          <t>42.5"W X 80.5"D X 52"H</t>
+          <t>58"W X 80.5"D X 52"H</t>
         </is>
       </c>
       <c r="U39" s="35" t="inlineStr">
@@ -6538,12 +6538,12 @@
       </c>
       <c r="V39" s="35" t="inlineStr">
         <is>
-          <t>Fabric, Solid Rubberwood, Engineered Wood</t>
+          <t>Solid Rubberwood, Engineered Wood</t>
         </is>
       </c>
       <c r="W39" s="35" t="inlineStr">
         <is>
-          <t>Contemporary,Pearl White,Fabric, Solid Rubberwood, Engineered Wood,LED on Headboard &amp; Mirror,Beveled Mirror,Hidden Jewelry Drawers in Dresser,Embossed Panels,Acrylic Handles &amp; Front Legs w/ Back Metal Legs,Felt-Lined Top Drawer,Metal Glide,English Dovetails,Mattress Ready</t>
+          <t>Contemporary,Pearl White,Solid Rubberwood, Engineered Wood,LED on Headboard &amp; Mirror,Beveled Mirror,Hidden Jewelry Drawers in Dresser,Embossed Panels,Acrylic Handles &amp; Front Legs w/ Back Metal Legs,Felt-Lined Top Drawer,Metal Glide,English Dovetails,Mattress Ready</t>
         </is>
       </c>
       <c r="X39" s="35" t="inlineStr">
@@ -6555,7 +6555,7 @@
       <c r="Z39" s="35" t="n"/>
       <c r="AA39" s="35" t="n"/>
       <c r="AB39" s="35" t="n">
-        <v>42.2</v>
+        <v>46.8</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -6637,12 +6637,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>LAREINA 5 Pc. Bedroom Set w/ 2NS Twin in Pearl White | GOODDEGG</t>
+          <t>LAREINA 5 Pc. Bedroom Set w/ 2NS | GOODDEGG</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>The LAREINA Bedroom w/ 2NS creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAREINA 5 Pc. Bedroom Set w/ 2NS supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>LAREINA 5 Pc. Bedroom Set w/ Chest Twin in Pearl White | GOODDEGG</t>
+          <t>LAREINA 5 Pc. Bedroom Set w/ Chest | GOODDEGG</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>The LAREINA Bedroom w/ Chest creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAREINA 5 Pc. Bedroom Set w/ Chest supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="H42" s="37" t="inlineStr">
         <is>
-          <t>LENNART 4 Pc. Bedroom Set Full in Oak | GOODDEGG</t>
+          <t>LENNART 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I42" s="37" t="inlineStr">
         <is>
-          <t>The LENNART Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LENNART 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J42" s="37" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="H43" s="37" t="inlineStr">
         <is>
-          <t>LENNART 4 Pc. Bedroom Set Full in Black | GOODDEGG</t>
+          <t>LENNART 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I43" s="37" t="inlineStr">
         <is>
-          <t>The LENNART Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LENNART 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J43" s="37" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="H44" s="37" t="inlineStr">
         <is>
-          <t>LENNART 4 Pc. Bedroom Set Full in Gray | GOODDEGG</t>
+          <t>LENNART 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I44" s="37" t="inlineStr">
         <is>
-          <t>The LENNART Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LENNART 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J44" s="37" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="H45" s="37" t="inlineStr">
         <is>
-          <t>LENNART 4 Pc. Bedroom Set Full in White | GOODDEGG</t>
+          <t>LENNART 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I45" s="37" t="inlineStr">
         <is>
-          <t>The LENNART Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LENNART 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J45" s="37" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="H46" s="37" t="inlineStr">
         <is>
-          <t>LENNART 4 Pc. Bedroom Set Twin in Oak | GOODDEGG</t>
+          <t>LENNART 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I46" s="37" t="inlineStr">
         <is>
-          <t>The LENNART Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LENNART 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J46" s="37" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="H47" s="37" t="inlineStr">
         <is>
-          <t>LENNART 4 Pc. Bedroom Set Twin in Black | GOODDEGG</t>
+          <t>LENNART 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I47" s="37" t="inlineStr">
         <is>
-          <t>The LENNART Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LENNART 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J47" s="37" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="H48" s="37" t="inlineStr">
         <is>
-          <t>LENNART 4 Pc. Bedroom Set Twin in Gray | GOODDEGG</t>
+          <t>LENNART 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I48" s="37" t="inlineStr">
         <is>
-          <t>The LENNART Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LENNART 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J48" s="37" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="H49" s="37" t="inlineStr">
         <is>
-          <t>LENNART 4 Pc. Bedroom Set Twin in White | GOODDEGG</t>
+          <t>LENNART 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I49" s="37" t="inlineStr">
         <is>
-          <t>The LENNART Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LENNART 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J49" s="37" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>CM7477GY-F-4PC</t>
+          <t>CM7477GY-T-4PC</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>LYCORIDA 4 Pc. Bedroom Set Full in Light Gray | GOODDEGG</t>
+          <t>LYCORIDA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>The LYCORIDA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYCORIDA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J50" s="9" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L50" s="9" t="n"/>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="N50" s="9" t="inlineStr">
         <is>
-          <t>CM7477GY-F-HBFB, CM7477GY-F-R, CM7477GY-N, CM7477GY-D, CM7477GY-M</t>
+          <t>CM7477GY-T-HBFB, CM7477GY-T-R, CM7477GY-N, CM7477GY-D, CM7477GY-M</t>
         </is>
       </c>
       <c r="O50" s="9" t="inlineStr">
@@ -8198,20 +8198,20 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>679</v>
+        <v>649</v>
       </c>
       <c r="Q50" s="10" t="n">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="R50" s="9" t="n">
-        <v>1737</v>
+        <v>1647</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>365.2</v>
+        <v>338.8</v>
       </c>
       <c r="T50" s="9" t="inlineStr">
         <is>
-          <t>BED: 80 1/4"L X 56 3/4"W X 54"H</t>
+          <t>BED: 80 1/4"L X 42"W X 54"H</t>
         </is>
       </c>
       <c r="U50" s="9" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
-          <t>Transitional,Light Gray,Solid Wood, Others,#REF!,Mattress Ready</t>
+          <t>Transitional,Light Gray,Solid Wood, Others,Molding Details,Dovetail Drawers,Ball-bearing Glides,Felt-lined Top Drawer,Chrome Hanging Pulls,Trundle Converts to Drawers,Mattress Ready</t>
         </is>
       </c>
       <c r="X50" s="9" t="inlineStr">
@@ -8238,7 +8238,7 @@
       <c r="Z50" s="9" t="n"/>
       <c r="AA50" s="9" t="n"/>
       <c r="AB50" s="9" t="n">
-        <v>40.6</v>
+        <v>38.3</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>CM7477GY-T-4PC</t>
+          <t>CM7477GY-F-4PC</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>LYCORIDA 4 Pc. Bedroom Set Twin in Light Gray | GOODDEGG</t>
+          <t>LYCORIDA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>The LYCORIDA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYCORIDA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J51" s="9" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L51" s="9" t="n"/>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="N51" s="9" t="inlineStr">
         <is>
-          <t>CM7477GY-T-HBFB, CM7477GY-T-R, CM7477GY-N, CM7477GY-D, CM7477GY-M</t>
+          <t>CM7477GY-F-HBFB, CM7477GY-F-R, CM7477GY-N, CM7477GY-D, CM7477GY-M</t>
         </is>
       </c>
       <c r="O51" s="9" t="inlineStr">
@@ -8350,20 +8350,20 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
-        <v>649</v>
+        <v>679</v>
       </c>
       <c r="Q51" s="10" t="n">
-        <v>699</v>
+        <v>739</v>
       </c>
       <c r="R51" s="9" t="n">
-        <v>1647</v>
+        <v>1737</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>338.8</v>
+        <v>365.2</v>
       </c>
       <c r="T51" s="9" t="inlineStr">
         <is>
-          <t>BED: 80 1/4"L X 42"W X 54"H</t>
+          <t>BED: 80 1/4"L X 56 3/4"W X 54"H</t>
         </is>
       </c>
       <c r="U51" s="9" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
-          <t>Transitional,Light Gray,Solid Wood, Others,Molding Details,Dovetail Drawers,Ball-bearing Glides,Felt-lined Top Drawer,Chrome Hanging Pulls,Trundle Converts to Drawers,Mattress Ready</t>
+          <t>Transitional,Light Gray,Solid Wood, Others,#REF!,Mattress Ready</t>
         </is>
       </c>
       <c r="X51" s="9" t="inlineStr">
@@ -8390,7 +8390,7 @@
       <c r="Z51" s="9" t="n"/>
       <c r="AA51" s="9" t="n"/>
       <c r="AB51" s="9" t="n">
-        <v>38.3</v>
+        <v>40.6</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -8426,12 +8426,12 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>CM7477WH-F-4PC</t>
+          <t>CM7477WH-T-4PC</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>LYCORIS 4 Pc. Bedroom Set Full in White | GOODDEGG</t>
+          <t>LYCORIS 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>The LYCORIS Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYCORIS 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J52" s="13" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L52" s="13" t="n"/>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="N52" s="13" t="inlineStr">
         <is>
-          <t>CM7477WH-F-HBFB, CM7477WH-F-R, CM7477WH-N, CM7477WH-D, CM7477WH-M</t>
+          <t>CM7477WH-T-HBFB, CM7477WH-T-R, CM7477WH-N, CM7477WH-D, CM7477WH-M</t>
         </is>
       </c>
       <c r="O52" s="13" t="inlineStr">
@@ -8504,20 +8504,20 @@
         </is>
       </c>
       <c r="P52" s="13" t="n">
-        <v>679</v>
+        <v>649</v>
       </c>
       <c r="Q52" s="14" t="n">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="R52" s="13" t="n">
-        <v>1737</v>
+        <v>1647</v>
       </c>
       <c r="S52" s="13" t="n">
-        <v>357.4</v>
+        <v>331</v>
       </c>
       <c r="T52" s="13" t="inlineStr">
         <is>
-          <t>56.5"W X 80"D X 54"H</t>
+          <t>81.5"W X 43"D X 47"H</t>
         </is>
       </c>
       <c r="U52" s="13" t="inlineStr">
@@ -8544,7 +8544,7 @@
       <c r="Z52" s="13" t="n"/>
       <c r="AA52" s="13" t="n"/>
       <c r="AB52" s="13" t="n">
-        <v>41.2</v>
+        <v>38.8</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>CM7477WH-T-4PC</t>
+          <t>CM7477WH-F-4PC</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
-          <t>LYCORIS 4 Pc. Bedroom Set Twin in White | GOODDEGG</t>
+          <t>LYCORIS 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>The LYCORIS Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYCORIS 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J53" s="13" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L53" s="13" t="n"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="N53" s="13" t="inlineStr">
         <is>
-          <t>CM7477WH-T-HBFB, CM7477WH-T-R, CM7477WH-N, CM7477WH-D, CM7477WH-M</t>
+          <t>CM7477WH-F-HBFB, CM7477WH-F-R, CM7477WH-N, CM7477WH-D, CM7477WH-M</t>
         </is>
       </c>
       <c r="O53" s="13" t="inlineStr">
@@ -8658,20 +8658,20 @@
         </is>
       </c>
       <c r="P53" s="13" t="n">
-        <v>649</v>
+        <v>679</v>
       </c>
       <c r="Q53" s="14" t="n">
-        <v>699</v>
+        <v>739</v>
       </c>
       <c r="R53" s="13" t="n">
-        <v>1647</v>
+        <v>1737</v>
       </c>
       <c r="S53" s="13" t="n">
-        <v>331</v>
+        <v>357.4</v>
       </c>
       <c r="T53" s="13" t="inlineStr">
         <is>
-          <t>81.5"W X 43"D X 47"H</t>
+          <t>56.5"W X 80"D X 54"H</t>
         </is>
       </c>
       <c r="U53" s="13" t="inlineStr">
@@ -8698,7 +8698,7 @@
       <c r="Z53" s="13" t="n"/>
       <c r="AA53" s="13" t="n"/>
       <c r="AB53" s="13" t="n">
-        <v>38.8</v>
+        <v>41.2</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -8779,12 +8779,12 @@
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>MARILLA 4 Pc. Bedroom Set Full in White | GOODDEGG</t>
+          <t>MARILLA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>The MARILLA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARILLA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J54" s="17" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H55" s="19" t="inlineStr">
         <is>
-          <t>MARILLA 4 Pc. Bedroom Set w/ Storage Full in White | GOODDEGG</t>
+          <t>MARILLA 4 Pc. Bedroom Set w/ Storage | GOODDEGG</t>
         </is>
       </c>
       <c r="I55" s="19" t="inlineStr">
         <is>
-          <t>The MARILLA Bedroom w/ Storage creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARILLA 4 Pc. Bedroom Set w/ Storage supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J55" s="19" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>MARILLA 4 Pc. Bedroom Set Twin in White | GOODDEGG</t>
+          <t>MARILLA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>The MARILLA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARILLA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J56" s="17" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="H57" s="19" t="inlineStr">
         <is>
-          <t>MARILLA 4 Pc. Bedroom Set w/ Storage Twin in White | GOODDEGG</t>
+          <t>MARILLA 4 Pc. Bedroom Set w/ Storage | GOODDEGG</t>
         </is>
       </c>
       <c r="I57" s="19" t="inlineStr">
         <is>
-          <t>The MARILLA Bedroom w/ Storage creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARILLA 4 Pc. Bedroom Set w/ Storage supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J57" s="19" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C58" s="23" t="inlineStr">
         <is>
-          <t>CM7651WH-F-4PC</t>
+          <t>CM7651WH-T-4PC</t>
         </is>
       </c>
       <c r="D58" s="23" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="H58" s="23" t="inlineStr">
         <is>
-          <t>MARLEE 4 Pc. Bedroom Set Full in White | GOODDEGG</t>
+          <t>MARLEE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I58" s="23" t="inlineStr">
         <is>
-          <t>The MARLEE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARLEE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J58" s="23" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="K58" s="23" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L58" s="23" t="n"/>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="N58" s="23" t="inlineStr">
         <is>
-          <t>CM7651WH-F-1, CM7651WH-F-2, CM7651WH-F-3, CM7651WH-N, CM7651WH-D, CM7651WH-M</t>
+          <t>CM7651WH-T-1, CM7651WH-T-2, CM7651WH-T-3, CM7651WH-N, CM7651WH-D, CM7651WH-M</t>
         </is>
       </c>
       <c r="O58" s="23" t="inlineStr">
@@ -9440,20 +9440,20 @@
         </is>
       </c>
       <c r="P58" s="23" t="n">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="Q58" s="41" t="n">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="R58" s="23" t="n">
-        <v>1437</v>
+        <v>1317</v>
       </c>
       <c r="S58" s="23" t="n">
-        <v>341</v>
+        <v>321.2</v>
       </c>
       <c r="T58" s="23" t="inlineStr">
         <is>
-          <t>85 1/4"W X 59"D X 50"H</t>
+          <t>85 1/4"W X 44"D X 50"H</t>
         </is>
       </c>
       <c r="U58" s="23" t="inlineStr">
@@ -9480,7 +9480,7 @@
       <c r="Z58" s="23" t="n"/>
       <c r="AA58" s="23" t="n"/>
       <c r="AB58" s="23" t="n">
-        <v>44.3</v>
+        <v>42.4</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -9516,12 +9516,12 @@
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr">
         <is>
-          <t>CM7651WH-T-4PC</t>
+          <t>CM7651WH-F-4PC</t>
         </is>
       </c>
       <c r="D59" s="23" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="H59" s="23" t="inlineStr">
         <is>
-          <t>MARLEE 4 Pc. Bedroom Set Twin in White | GOODDEGG</t>
+          <t>MARLEE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I59" s="23" t="inlineStr">
         <is>
-          <t>The MARLEE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARLEE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J59" s="23" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="K59" s="23" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L59" s="23" t="n"/>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="N59" s="23" t="inlineStr">
         <is>
-          <t>CM7651WH-T-1, CM7651WH-T-2, CM7651WH-T-3, CM7651WH-N, CM7651WH-D, CM7651WH-M</t>
+          <t>CM7651WH-F-1, CM7651WH-F-2, CM7651WH-F-3, CM7651WH-N, CM7651WH-D, CM7651WH-M</t>
         </is>
       </c>
       <c r="O59" s="23" t="inlineStr">
@@ -9596,20 +9596,20 @@
         </is>
       </c>
       <c r="P59" s="23" t="n">
-        <v>549</v>
+        <v>599</v>
       </c>
       <c r="Q59" s="41" t="n">
-        <v>549</v>
+        <v>599</v>
       </c>
       <c r="R59" s="23" t="n">
-        <v>1317</v>
+        <v>1437</v>
       </c>
       <c r="S59" s="23" t="n">
-        <v>321.2</v>
+        <v>341</v>
       </c>
       <c r="T59" s="23" t="inlineStr">
         <is>
-          <t>85 1/4"W X 44"D X 50"H</t>
+          <t>85 1/4"W X 59"D X 50"H</t>
         </is>
       </c>
       <c r="U59" s="23" t="inlineStr">
@@ -9636,7 +9636,7 @@
       <c r="Z59" s="23" t="n"/>
       <c r="AA59" s="23" t="n"/>
       <c r="AB59" s="23" t="n">
-        <v>42.4</v>
+        <v>44.3</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -9672,12 +9672,12 @@
       </c>
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C60" s="25" t="inlineStr">
         <is>
-          <t>CM7155WH-F-4PC</t>
+          <t>CM7155WH-T-4PC</t>
         </is>
       </c>
       <c r="D60" s="25" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="H60" s="25" t="inlineStr">
         <is>
-          <t>OLIVIA 4 Pc. Bedroom Set Full in White | GOODDEGG</t>
+          <t>OLIVIA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I60" s="25" t="inlineStr">
         <is>
-          <t>The OLIVIA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLIVIA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J60" s="25" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="K60" s="25" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L60" s="25" t="n"/>
@@ -9743,29 +9743,29 @@
       </c>
       <c r="N60" s="25" t="inlineStr">
         <is>
-          <t>CM7155WH-F-HB, CM7155WH-F-FB, CM7155WH-F-R, CM7155WH-N, CM7155WH-D, CM7155WH-M</t>
+          <t>CM7155WH-T-HB, CM7155WH-T-FB, CM7155WH-T-R, CM7155WH-N, CM7155WH-D, CM7155WH-M</t>
         </is>
       </c>
       <c r="O60" s="25" t="inlineStr">
         <is>
-          <t>CM7155WH.jpg,CM7155WH-CLOSEUP.jpg,CM7155WH-1.jpg</t>
+          <t>CM7155WH.jpg,CM7155WH-CLOSEUP.jpg,CM7155WH-WB.jpg,CM7155WH-1.jpg</t>
         </is>
       </c>
       <c r="P60" s="25" t="n">
-        <v>809</v>
+        <v>759</v>
       </c>
       <c r="Q60" s="26" t="n">
-        <v>849</v>
+        <v>799</v>
       </c>
       <c r="R60" s="25" t="n">
-        <v>2067</v>
+        <v>1917</v>
       </c>
       <c r="S60" s="25" t="n">
-        <v>372.9</v>
+        <v>349.8</v>
       </c>
       <c r="T60" s="25" t="inlineStr">
         <is>
-          <t>80 1/4"L X 58 3/4"W X 55"H</t>
+          <t>80 1/4"L X 44"W X 55"H</t>
         </is>
       </c>
       <c r="U60" s="25" t="inlineStr">
@@ -9792,7 +9792,7 @@
       <c r="Z60" s="25" t="n"/>
       <c r="AA60" s="25" t="n"/>
       <c r="AB60" s="25" t="n">
-        <v>48.1</v>
+        <v>44.2</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -9828,12 +9828,12 @@
       </c>
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C61" s="25" t="inlineStr">
         <is>
-          <t>CM7155WH-T-4PC</t>
+          <t>CM7155WH-F-4PC</t>
         </is>
       </c>
       <c r="D61" s="25" t="inlineStr">
@@ -9873,12 +9873,12 @@
       </c>
       <c r="H61" s="25" t="inlineStr">
         <is>
-          <t>OLIVIA 4 Pc. Bedroom Set Twin in White | GOODDEGG</t>
+          <t>OLIVIA 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I61" s="25" t="inlineStr">
         <is>
-          <t>The OLIVIA Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLIVIA 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J61" s="25" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="K61" s="25" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L61" s="25" t="n"/>
@@ -9899,29 +9899,29 @@
       </c>
       <c r="N61" s="25" t="inlineStr">
         <is>
-          <t>CM7155WH-T-HB, CM7155WH-T-FB, CM7155WH-T-R, CM7155WH-N, CM7155WH-D, CM7155WH-M</t>
+          <t>CM7155WH-F-HB, CM7155WH-F-FB, CM7155WH-F-R, CM7155WH-N, CM7155WH-D, CM7155WH-M</t>
         </is>
       </c>
       <c r="O61" s="25" t="inlineStr">
         <is>
-          <t>CM7155WH.jpg,CM7155WH-CLOSEUP.jpg,CM7155WH-WB.jpg,CM7155WH-1.jpg</t>
+          <t>CM7155WH.jpg,CM7155WH-CLOSEUP.jpg,CM7155WH-1.jpg</t>
         </is>
       </c>
       <c r="P61" s="25" t="n">
-        <v>759</v>
+        <v>809</v>
       </c>
       <c r="Q61" s="26" t="n">
-        <v>799</v>
+        <v>849</v>
       </c>
       <c r="R61" s="25" t="n">
-        <v>1917</v>
+        <v>2067</v>
       </c>
       <c r="S61" s="25" t="n">
-        <v>349.8</v>
+        <v>372.9</v>
       </c>
       <c r="T61" s="25" t="inlineStr">
         <is>
-          <t>80 1/4"L X 44"W X 55"H</t>
+          <t>80 1/4"L X 58 3/4"W X 55"H</t>
         </is>
       </c>
       <c r="U61" s="25" t="inlineStr">
@@ -9948,7 +9948,7 @@
       <c r="Z61" s="25" t="n"/>
       <c r="AA61" s="25" t="n"/>
       <c r="AB61" s="25" t="n">
-        <v>44.2</v>
+        <v>48.1</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -9984,12 +9984,12 @@
       </c>
       <c r="B62" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C62" s="27" t="inlineStr">
         <is>
-          <t>CM7467WH-F-4PC</t>
+          <t>CM7467WH-T-4PC</t>
         </is>
       </c>
       <c r="D62" s="27" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="H62" s="27" t="inlineStr">
         <is>
-          <t>PRIAM 4 Pc. Bedroom Set Full in White Gray | GOODDEGG</t>
+          <t>PRIAM 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I62" s="27" t="inlineStr">
         <is>
-          <t>The PRIAM Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PRIAM 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J62" s="27" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="K62" s="27" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L62" s="27" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="N62" s="27" t="inlineStr">
         <is>
-          <t>CM7467WH-F-HBFB, CM7467WH-F-R, CM7467WH-N, CM7467WH-D, CM7467WH-M</t>
+          <t>CM7467WH-T-HBFB, CM7467WH-D, CM7467WH-M, CM7467WH-T-R, CM7467WH-N</t>
         </is>
       </c>
       <c r="O62" s="27" t="inlineStr">
@@ -10066,20 +10066,20 @@
         </is>
       </c>
       <c r="P62" s="27" t="n">
-        <v>679</v>
+        <v>649</v>
       </c>
       <c r="Q62" s="28" t="n">
-        <v>679</v>
+        <v>649</v>
       </c>
       <c r="R62" s="27" t="n">
-        <v>1737</v>
+        <v>1647</v>
       </c>
       <c r="S62" s="27" t="n">
-        <v>306.3</v>
+        <v>283</v>
       </c>
       <c r="T62" s="27" t="inlineStr">
         <is>
-          <t>79 5/8"L X 56 1/4"W X 50"H</t>
+          <t>79 5/8"L X 41 1/2"W X 50"H</t>
         </is>
       </c>
       <c r="U62" s="27" t="inlineStr">
@@ -10106,7 +10106,7 @@
       <c r="Z62" s="27" t="n"/>
       <c r="AA62" s="27" t="n"/>
       <c r="AB62" s="27" t="n">
-        <v>41.4</v>
+        <v>39.6</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -10142,12 +10142,12 @@
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C63" s="27" t="inlineStr">
         <is>
-          <t>CM7467WH-T-4PC</t>
+          <t>CM7467WH-F-4PC</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="H63" s="27" t="inlineStr">
         <is>
-          <t>PRIAM 4 Pc. Bedroom Set Twin in White Gray | GOODDEGG</t>
+          <t>PRIAM 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I63" s="27" t="inlineStr">
         <is>
-          <t>The PRIAM Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PRIAM 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J63" s="27" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="K63" s="27" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L63" s="27" t="n"/>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="N63" s="27" t="inlineStr">
         <is>
-          <t>CM7467WH-T-HBFB, CM7467WH-D, CM7467WH-M, CM7467WH-T-R, CM7467WH-N</t>
+          <t>CM7467WH-F-HBFB, CM7467WH-F-R, CM7467WH-N, CM7467WH-D, CM7467WH-M</t>
         </is>
       </c>
       <c r="O63" s="27" t="inlineStr">
@@ -10224,20 +10224,20 @@
         </is>
       </c>
       <c r="P63" s="27" t="n">
-        <v>649</v>
+        <v>679</v>
       </c>
       <c r="Q63" s="28" t="n">
-        <v>649</v>
+        <v>679</v>
       </c>
       <c r="R63" s="27" t="n">
-        <v>1647</v>
+        <v>1737</v>
       </c>
       <c r="S63" s="27" t="n">
-        <v>283</v>
+        <v>306.3</v>
       </c>
       <c r="T63" s="27" t="inlineStr">
         <is>
-          <t>79 5/8"L X 41 1/2"W X 50"H</t>
+          <t>79 5/8"L X 56 1/4"W X 50"H</t>
         </is>
       </c>
       <c r="U63" s="27" t="inlineStr">
@@ -10264,7 +10264,7 @@
       <c r="Z63" s="27" t="n"/>
       <c r="AA63" s="27" t="n"/>
       <c r="AB63" s="27" t="n">
-        <v>39.6</v>
+        <v>41.4</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="B64" s="31" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C64" s="31" t="inlineStr">
         <is>
-          <t>FOA7927F-4PC</t>
+          <t>FOA7927T-4PC</t>
         </is>
       </c>
       <c r="D64" s="31" t="inlineStr">
@@ -10344,12 +10344,12 @@
       </c>
       <c r="H64" s="31" t="inlineStr">
         <is>
-          <t>ROANNE 4 Pc. Bedroom Set Full in Gray Charcoal | GOODDEGG</t>
+          <t>ROANNE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I64" s="31" t="inlineStr">
         <is>
-          <t>The ROANNE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROANNE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J64" s="31" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="K64" s="31" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L64" s="31" t="n"/>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="N64" s="31" t="inlineStr">
         <is>
-          <t>FOA7927F-HBFB, FOA7927F-R, FOA7927N, FOA7927D, FOA7927M</t>
+          <t>FOA7927T-HBFB, FOA7927T-R, FOA7927N, FOA7927D, FOA7927M</t>
         </is>
       </c>
       <c r="O64" s="31" t="inlineStr">
@@ -10379,16 +10379,16 @@
         </is>
       </c>
       <c r="P64" s="31" t="n">
-        <v>489</v>
+        <v>459</v>
       </c>
       <c r="Q64" s="42" t="n">
-        <v>539</v>
+        <v>479</v>
       </c>
       <c r="R64" s="31" t="n">
-        <v>1257</v>
+        <v>1167</v>
       </c>
       <c r="S64" s="31" t="n">
-        <v>272.9</v>
+        <v>258.7</v>
       </c>
       <c r="T64" s="31" t="n"/>
       <c r="U64" s="31" t="inlineStr">
@@ -10415,7 +10415,7 @@
       <c r="Z64" s="31" t="n"/>
       <c r="AA64" s="31" t="n"/>
       <c r="AB64" s="31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
@@ -10451,12 +10451,12 @@
       </c>
       <c r="B65" s="31" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C65" s="31" t="inlineStr">
         <is>
-          <t>FOA7927T-4PC</t>
+          <t>FOA7927F-4PC</t>
         </is>
       </c>
       <c r="D65" s="31" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="H65" s="31" t="inlineStr">
         <is>
-          <t>ROANNE 4 Pc. Bedroom Set Twin in Gray Charcoal | GOODDEGG</t>
+          <t>ROANNE 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I65" s="31" t="inlineStr">
         <is>
-          <t>The ROANNE Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROANNE 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J65" s="31" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="K65" s="31" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L65" s="31" t="n"/>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="N65" s="31" t="inlineStr">
         <is>
-          <t>FOA7927T-HBFB, FOA7927T-R, FOA7927N, FOA7927D, FOA7927M</t>
+          <t>FOA7927F-HBFB, FOA7927F-R, FOA7927N, FOA7927D, FOA7927M</t>
         </is>
       </c>
       <c r="O65" s="31" t="inlineStr">
@@ -10530,16 +10530,16 @@
         </is>
       </c>
       <c r="P65" s="31" t="n">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="Q65" s="42" t="n">
-        <v>479</v>
+        <v>539</v>
       </c>
       <c r="R65" s="31" t="n">
-        <v>1167</v>
+        <v>1257</v>
       </c>
       <c r="S65" s="31" t="n">
-        <v>258.7</v>
+        <v>272.9</v>
       </c>
       <c r="T65" s="31" t="n"/>
       <c r="U65" s="31" t="inlineStr">
@@ -10566,7 +10566,7 @@
       <c r="Z65" s="31" t="n"/>
       <c r="AA65" s="31" t="n"/>
       <c r="AB65" s="31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
@@ -10602,12 +10602,12 @@
       </c>
       <c r="B66" s="33" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>FOA7175F-4PC</t>
+          <t>FOA7175T-4PC</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H66" s="33" t="inlineStr">
         <is>
-          <t>VEVEY 4 Pc. Bedroom Set Full in Wire-Brushed Warm Gray | GOODDEGG</t>
+          <t>VEVEY 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I66" s="33" t="inlineStr">
         <is>
-          <t>The VEVEY Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VEVEY 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J66" s="33" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="K66" s="33" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L66" s="33" t="n"/>
@@ -10672,29 +10672,29 @@
       </c>
       <c r="N66" s="33" t="inlineStr">
         <is>
-          <t>FOA7175F-HB, FOA7175F-FB, FOA7175F-R, FOA7175N, FOA7175D, FOA7175M</t>
+          <t>FOA7175T-HB, FOA7175T-FB, FOA7175T-R, FOA7175N, FOA7175D, FOA7175M</t>
         </is>
       </c>
       <c r="O66" s="33" t="inlineStr">
         <is>
-          <t>FOA7175-1-Z.jpg,FOA7175-4.jpg,FOA7175-5.jpg,FOA7175-6.jpg,FOA7175-7.jpg</t>
+          <t>FOA7175-1-Z.jpg,FOA7175-2.jpg,FOA7175-3.jpg</t>
         </is>
       </c>
       <c r="P66" s="33" t="n">
-        <v>759</v>
+        <v>709</v>
       </c>
       <c r="Q66" s="43" t="n">
-        <v>799</v>
+        <v>749</v>
       </c>
       <c r="R66" s="33" t="n">
-        <v>1857</v>
+        <v>1737</v>
       </c>
       <c r="S66" s="33" t="n">
-        <v>293.7</v>
+        <v>283.8</v>
       </c>
       <c r="T66" s="33" t="inlineStr">
         <is>
-          <t>82 1/2"L X 58 3/8"W X 50"H</t>
+          <t>82 1/2"L X 42 7/8"W X 50"H</t>
         </is>
       </c>
       <c r="U66" s="33" t="inlineStr">
@@ -10721,7 +10721,7 @@
       <c r="Z66" s="33" t="n"/>
       <c r="AA66" s="33" t="n"/>
       <c r="AB66" s="33" t="n">
-        <v>46.4</v>
+        <v>45.8</v>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
@@ -10757,12 +10757,12 @@
       </c>
       <c r="B67" s="33" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>FOA7175T-4PC</t>
+          <t>FOA7175F-4PC</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
@@ -10801,12 +10801,12 @@
       </c>
       <c r="H67" s="33" t="inlineStr">
         <is>
-          <t>VEVEY 4 Pc. Bedroom Set Twin in Wire-Brushed Warm Gray | GOODDEGG</t>
+          <t>VEVEY 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I67" s="33" t="inlineStr">
         <is>
-          <t>The VEVEY Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VEVEY 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J67" s="33" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="K67" s="33" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L67" s="33" t="n"/>
@@ -10827,29 +10827,29 @@
       </c>
       <c r="N67" s="33" t="inlineStr">
         <is>
-          <t>FOA7175T-HB, FOA7175T-FB, FOA7175T-R, FOA7175N, FOA7175D, FOA7175M</t>
+          <t>FOA7175F-HB, FOA7175F-FB, FOA7175F-R, FOA7175N, FOA7175D, FOA7175M</t>
         </is>
       </c>
       <c r="O67" s="33" t="inlineStr">
         <is>
-          <t>FOA7175-1-Z.jpg,FOA7175-2.jpg,FOA7175-3.jpg</t>
+          <t>FOA7175-1-Z.jpg,FOA7175-4.jpg,FOA7175-5.jpg,FOA7175-6.jpg,FOA7175-7.jpg</t>
         </is>
       </c>
       <c r="P67" s="33" t="n">
-        <v>709</v>
+        <v>759</v>
       </c>
       <c r="Q67" s="43" t="n">
-        <v>749</v>
+        <v>799</v>
       </c>
       <c r="R67" s="33" t="n">
-        <v>1737</v>
+        <v>1857</v>
       </c>
       <c r="S67" s="33" t="n">
-        <v>283.8</v>
+        <v>293.7</v>
       </c>
       <c r="T67" s="33" t="inlineStr">
         <is>
-          <t>82 1/2"L X 42 7/8"W X 50"H</t>
+          <t>82 1/2"L X 58 3/8"W X 50"H</t>
         </is>
       </c>
       <c r="U67" s="33" t="inlineStr">
@@ -10876,7 +10876,7 @@
       <c r="Z67" s="33" t="n"/>
       <c r="AA67" s="33" t="n"/>
       <c r="AB67" s="33" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
@@ -10912,12 +10912,12 @@
       </c>
       <c r="B68" s="35" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C68" s="35" t="inlineStr">
         <is>
-          <t>CM7130PK-F-4PC</t>
+          <t>CM7130PK-T-4PC</t>
         </is>
       </c>
       <c r="D68" s="35" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="H68" s="35" t="inlineStr">
         <is>
-          <t>ZOHAR 4 Pc. Bedroom Set Full in Pink | GOODDEGG</t>
+          <t>ZOHAR 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I68" s="35" t="inlineStr">
         <is>
-          <t>The ZOHAR Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZOHAR 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J68" s="35" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="K68" s="35" t="inlineStr">
         <is>
-          <t>4 Pc. Full Bedroom Set</t>
+          <t>4 Pc. Twin Bedroom Set</t>
         </is>
       </c>
       <c r="L68" s="35" t="n"/>
@@ -10982,29 +10982,29 @@
       </c>
       <c r="N68" s="35" t="inlineStr">
         <is>
-          <t>CM7130PK-F-1, CM7130PK-F-2, CM7130PK-F-3, CM7130PK-N, CM7130PK-D, CM7130PK-M</t>
+          <t>CM7130PK-T-1, CM7130PK-T-2, CM7130PK-T-3, CM7130PK-N, CM7130PK-D, CM7130PK-M</t>
         </is>
       </c>
       <c r="O68" s="35" t="inlineStr">
         <is>
-          <t>CM7130PK-1-Z.jpg,CM7130PK-2.jpg,CM7130PK-3.jpg,CM7130PK-4.jpg</t>
+          <t>CM7130PK-T-1-Z.jpg,CM7130PK-3.jpg,CM7130PK-4.jpg</t>
         </is>
       </c>
       <c r="P68" s="35" t="n">
-        <v>859</v>
+        <v>819</v>
       </c>
       <c r="Q68" s="36" t="n">
-        <v>899</v>
+        <v>839</v>
       </c>
       <c r="R68" s="35" t="n">
-        <v>2157</v>
+        <v>2037</v>
       </c>
       <c r="S68" s="35" t="n">
-        <v>512.16</v>
+        <v>482.46</v>
       </c>
       <c r="T68" s="35" t="inlineStr">
         <is>
-          <t>88 1/8"L X 76 1/2"W X 56 1/2"H</t>
+          <t>88 1/8"L X 62 1/2"W X 56 1/2"H</t>
         </is>
       </c>
       <c r="U68" s="35" t="inlineStr">
@@ -11031,7 +11031,7 @@
       <c r="Z68" s="35" t="n"/>
       <c r="AA68" s="35" t="n"/>
       <c r="AB68" s="35" t="n">
-        <v>66.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
@@ -11067,12 +11067,12 @@
       </c>
       <c r="B69" s="35" t="inlineStr">
         <is>
-          <t>Queen</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C69" s="35" t="inlineStr">
         <is>
-          <t>CM7130PK-Q-4PC</t>
+          <t>CM7130PK-F-4PC</t>
         </is>
       </c>
       <c r="D69" s="35" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="H69" s="35" t="inlineStr">
         <is>
-          <t>ZOHAR 4 Pc. Bedroom Set Queen in Pink | GOODDEGG</t>
+          <t>ZOHAR 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I69" s="35" t="inlineStr">
         <is>
-          <t>The ZOHAR Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZOHAR 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J69" s="35" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K69" s="35" t="inlineStr">
         <is>
-          <t>4 Pc. Queen Bedroom Set</t>
+          <t>4 Pc. Full Bedroom Set</t>
         </is>
       </c>
       <c r="L69" s="35" t="n"/>
@@ -11137,7 +11137,7 @@
       </c>
       <c r="N69" s="35" t="inlineStr">
         <is>
-          <t>CM7130PK-Q-1, CM7130PK-Q-2, CM7130PK-Q-3, CM7130PK-N, CM7130PK-D, CM7130PK-M</t>
+          <t>CM7130PK-F-1, CM7130PK-F-2, CM7130PK-F-3, CM7130PK-N, CM7130PK-D, CM7130PK-M</t>
         </is>
       </c>
       <c r="O69" s="35" t="inlineStr">
@@ -11146,20 +11146,20 @@
         </is>
       </c>
       <c r="P69" s="35" t="n">
-        <v>909</v>
+        <v>859</v>
       </c>
       <c r="Q69" s="36" t="n">
-        <v>959</v>
+        <v>899</v>
       </c>
       <c r="R69" s="35" t="n">
-        <v>2277</v>
+        <v>2157</v>
       </c>
       <c r="S69" s="35" t="n">
-        <v>530.16</v>
+        <v>512.16</v>
       </c>
       <c r="T69" s="35" t="inlineStr">
         <is>
-          <t>88 1/8"L X 82 1/2"W X 56 1/2"H</t>
+          <t>88 1/8"L X 76 1/2"W X 56 1/2"H</t>
         </is>
       </c>
       <c r="U69" s="35" t="inlineStr">
@@ -11186,7 +11186,7 @@
       <c r="Z69" s="35" t="n"/>
       <c r="AA69" s="35" t="n"/>
       <c r="AB69" s="35" t="n">
-        <v>67</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
@@ -11222,12 +11222,12 @@
       </c>
       <c r="B70" s="35" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C70" s="35" t="inlineStr">
         <is>
-          <t>CM7130PK-T-4PC</t>
+          <t>CM7130PK-Q-4PC</t>
         </is>
       </c>
       <c r="D70" s="35" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="H70" s="35" t="inlineStr">
         <is>
-          <t>ZOHAR 4 Pc. Bedroom Set Twin in Pink | GOODDEGG</t>
+          <t>ZOHAR 4 Pc. Bedroom Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I70" s="35" t="inlineStr">
         <is>
-          <t>The ZOHAR Bedroom creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZOHAR 4 Pc. Bedroom Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J70" s="35" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="K70" s="35" t="inlineStr">
         <is>
-          <t>4 Pc. Twin Bedroom Set</t>
+          <t>4 Pc. Queen Bedroom Set</t>
         </is>
       </c>
       <c r="L70" s="35" t="n"/>
@@ -11292,29 +11292,29 @@
       </c>
       <c r="N70" s="35" t="inlineStr">
         <is>
-          <t>CM7130PK-T-1, CM7130PK-T-2, CM7130PK-T-3, CM7130PK-N, CM7130PK-D, CM7130PK-M</t>
+          <t>CM7130PK-Q-1, CM7130PK-Q-2, CM7130PK-Q-3, CM7130PK-N, CM7130PK-D, CM7130PK-M</t>
         </is>
       </c>
       <c r="O70" s="35" t="inlineStr">
         <is>
-          <t>CM7130PK-T-1-Z.jpg,CM7130PK-3.jpg,CM7130PK-4.jpg</t>
+          <t>CM7130PK-1-Z.jpg,CM7130PK-2.jpg,CM7130PK-3.jpg,CM7130PK-4.jpg</t>
         </is>
       </c>
       <c r="P70" s="35" t="n">
-        <v>819</v>
+        <v>909</v>
       </c>
       <c r="Q70" s="36" t="n">
-        <v>839</v>
+        <v>959</v>
       </c>
       <c r="R70" s="35" t="n">
-        <v>2037</v>
+        <v>2277</v>
       </c>
       <c r="S70" s="35" t="n">
-        <v>482.46</v>
+        <v>530.16</v>
       </c>
       <c r="T70" s="35" t="inlineStr">
         <is>
-          <t>88 1/8"L X 62 1/2"W X 56 1/2"H</t>
+          <t>88 1/8"L X 82 1/2"W X 56 1/2"H</t>
         </is>
       </c>
       <c r="U70" s="35" t="inlineStr">
@@ -11341,7 +11341,7 @@
       <c r="Z70" s="35" t="n"/>
       <c r="AA70" s="35" t="n"/>
       <c r="AB70" s="35" t="n">
-        <v>64.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
@@ -11421,12 +11421,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ZOHAR 5 Pc. Bedroom Set w/ 2NS Queen in Pink | GOODDEGG</t>
+          <t>ZOHAR 5 Pc. Bedroom Set w/ 2NS | GOODDEGG</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>The ZOHAR Bedroom w/ 2NS creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZOHAR 5 Pc. Bedroom Set w/ 2NS supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -11573,12 +11573,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ZOHAR 5 Pc. Bedroom Set w/ Chest Queen in Pink | GOODDEGG</t>
+          <t>ZOHAR 5 Pc. Bedroom Set w/ Chest | GOODDEGG</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>The ZOHAR Bedroom w/ Chest creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZOHAR 5 Pc. Bedroom Set w/ Chest supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="B73" s="44" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C73" s="44" t="inlineStr">
         <is>
-          <t>FM72081WH-F-BED+TR</t>
+          <t>FM72081WH-T-BED+TR</t>
         </is>
       </c>
       <c r="D73" s="44" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="H73" s="44" t="inlineStr">
         <is>
-          <t>LAREINA Bed w/ Trundle Full in Pearl White | GOODDEGG</t>
+          <t>LAREINA Bed w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I73" s="44" t="inlineStr">
         <is>
-          <t>The LAREINA Bed w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAREINA Bed w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J73" s="44" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="K73" s="44" t="inlineStr">
         <is>
-          <t>Full Bed w/ Trundle</t>
+          <t>Twin Bed w/ Trundle</t>
         </is>
       </c>
       <c r="L73" s="44" t="n"/>
@@ -11747,25 +11747,25 @@
       </c>
       <c r="N73" s="44" t="inlineStr">
         <is>
-          <t>FM72081WH-F-HB, FM72081WH-F-FB, FM72081WH-TF-R, FM72081WH-TR</t>
+          <t>FM72081WH-T-HB, FM72081WH-T-FB, FM72081WH-TF-R, FM72081WH-TR</t>
         </is>
       </c>
       <c r="O73" s="44" t="inlineStr">
         <is>
-          <t>FM72081WH-T-1-Z.jpg,FM72081WH-T-2.jpg,FM72081WH-T-4.jpg,FM72081WH-T-5.jpg,FM72081WH-T-7.jpg,FM72081WH-N-1.jpg,FM72081WH-N-2.jpg,FM72081WH-D-2.jpg,FM72081WH-D-2.jpg</t>
+          <t>FM72081WH-T-1-Z.jpg,FM72081WH-T-2.jpg,FM72081WH-T-7.jpg,FM72081WH-T-4.jpg</t>
         </is>
       </c>
       <c r="P73" s="44" t="n">
+        <v>529</v>
+      </c>
+      <c r="Q73" s="45" t="n">
         <v>549</v>
       </c>
-      <c r="Q73" s="45" t="n">
-        <v>599</v>
-      </c>
       <c r="R73" s="44" t="n">
-        <v>1497</v>
+        <v>1437</v>
       </c>
       <c r="S73" s="44" t="n">
-        <v>256.62</v>
+        <v>258.85</v>
       </c>
       <c r="T73" s="44" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
       <c r="Z73" s="44" t="n"/>
       <c r="AA73" s="44" t="n"/>
       <c r="AB73" s="44" t="n">
-        <v>17.9</v>
+        <v>13.3</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
@@ -11832,12 +11832,12 @@
       </c>
       <c r="B74" s="44" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C74" s="44" t="inlineStr">
         <is>
-          <t>FM72081WH-T-BED+TR</t>
+          <t>FM72081WH-F-BED+TR</t>
         </is>
       </c>
       <c r="D74" s="44" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="H74" s="44" t="inlineStr">
         <is>
-          <t>LAREINA Bed w/ Trundle Twin in Pearl White | GOODDEGG</t>
+          <t>LAREINA Bed w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I74" s="44" t="inlineStr">
         <is>
-          <t>The LAREINA Bed w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAREINA Bed w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J74" s="44" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="K74" s="44" t="inlineStr">
         <is>
-          <t>Twin Bed w/ Trundle</t>
+          <t>Full Bed w/ Trundle</t>
         </is>
       </c>
       <c r="L74" s="44" t="n"/>
@@ -11899,25 +11899,25 @@
       </c>
       <c r="N74" s="44" t="inlineStr">
         <is>
-          <t>FM72081WH-T-HB, FM72081WH-T-FB, FM72081WH-TF-R, FM72081WH-TR</t>
+          <t>FM72081WH-F-HB, FM72081WH-F-FB, FM72081WH-TF-R, FM72081WH-TR</t>
         </is>
       </c>
       <c r="O74" s="44" t="inlineStr">
         <is>
-          <t>FM72081WH-T-1-Z.jpg,FM72081WH-T-2.jpg,FM72081WH-T-7.jpg,FM72081WH-T-4.jpg</t>
+          <t>FM72081WH-T-1-Z.jpg,FM72081WH-T-2.jpg,FM72081WH-T-4.jpg,FM72081WH-T-5.jpg,FM72081WH-T-7.jpg,FM72081WH-N-1.jpg,FM72081WH-N-2.jpg,FM72081WH-D-2.jpg,FM72081WH-D-2.jpg</t>
         </is>
       </c>
       <c r="P74" s="44" t="n">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="Q74" s="45" t="n">
-        <v>549</v>
+        <v>599</v>
       </c>
       <c r="R74" s="44" t="n">
-        <v>1437</v>
+        <v>1497</v>
       </c>
       <c r="S74" s="44" t="n">
-        <v>258.85</v>
+        <v>256.62</v>
       </c>
       <c r="T74" s="44" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
       <c r="Z74" s="44" t="n"/>
       <c r="AA74" s="44" t="n"/>
       <c r="AB74" s="44" t="n">
-        <v>13.3</v>
+        <v>17.9</v>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
@@ -12021,12 +12021,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>LYCORIDA Bed w/ Trundle Full in Gray | GOODDEGG</t>
+          <t>LYCORIDA Bed w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>The LYCORIDA Bed w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYCORIDA Bed w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
@@ -12169,12 +12169,12 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>LYCORIDA Bed w/ Trundle Full in White | GOODDEGG</t>
+          <t>LYCORIDA Bed w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>The LYCORIDA Bed w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYCORIDA Bed w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
@@ -12317,12 +12317,12 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>LYCORIDA Bed w/ Trundle Twin in Light Gray | GOODDEGG</t>
+          <t>LYCORIDA Bed w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>The LYCORIDA Bed w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYCORIDA Bed w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>LYCORIDA Bed w/ Trundle Twin in White | GOODDEGG</t>
+          <t>LYCORIDA Bed w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>The LYCORIDA Bed w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYCORIDA Bed w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="B79" s="21" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C79" s="21" t="inlineStr">
         <is>
-          <t>FOA7256WH-F-BED-SR</t>
+          <t>FOA7256WH-T-BED-SR</t>
         </is>
       </c>
       <c r="D79" s="21" t="inlineStr">
@@ -12624,12 +12624,12 @@
       </c>
       <c r="H79" s="21" t="inlineStr">
         <is>
-          <t>MARILLA Bed w/ Storage Full in White | GOODDEGG</t>
+          <t>MARILLA Bed w/ Storage | GOODDEGG</t>
         </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
-          <t>The MARILLA Bed w/ Storage creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARILLA Bed w/ Storage supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J79" s="21" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="K79" s="21" t="inlineStr">
         <is>
-          <t>Full Bed w/ Storage</t>
+          <t>Twin Bed w/ Storage</t>
         </is>
       </c>
       <c r="L79" s="21" t="n"/>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="N79" s="21" t="inlineStr">
         <is>
-          <t>FOA7256WH-F-1, FOA7256WH-F-2, FOA7256WH-F-3, CM-SR452-WH</t>
+          <t>FOA7256WH-T-1, FOA7256WH-T-2, FOA7256WH-T-3, CM-SR452-WH</t>
         </is>
       </c>
       <c r="O79" s="21" t="inlineStr">
@@ -12659,20 +12659,20 @@
         </is>
       </c>
       <c r="P79" s="21" t="n">
-        <v>519</v>
+        <v>439</v>
       </c>
       <c r="Q79" s="46" t="n">
-        <v>519</v>
+        <v>439</v>
       </c>
       <c r="R79" s="21" t="n">
-        <v>1377</v>
+        <v>1167</v>
       </c>
       <c r="S79" s="21" t="n">
-        <v>176</v>
+        <v>156.2</v>
       </c>
       <c r="T79" s="21" t="inlineStr">
         <is>
-          <t>86"L X 57 3/4"W X 46 5/8"H</t>
+          <t>86"L X 42 7/8"W X 46 5/8"H</t>
         </is>
       </c>
       <c r="U79" s="21" t="inlineStr">
@@ -12699,7 +12699,7 @@
       <c r="Z79" s="21" t="n"/>
       <c r="AA79" s="21" t="n"/>
       <c r="AB79" s="21" t="n">
-        <v>26.7</v>
+        <v>23.5</v>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
@@ -12735,12 +12735,12 @@
       </c>
       <c r="B80" s="21" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C80" s="21" t="inlineStr">
         <is>
-          <t>FOA7256WH-T-BED-SR</t>
+          <t>FOA7256WH-F-BED-SR</t>
         </is>
       </c>
       <c r="D80" s="21" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="H80" s="21" t="inlineStr">
         <is>
-          <t>MARILLA Bed w/ Storage Twin in White | GOODDEGG</t>
+          <t>MARILLA Bed w/ Storage | GOODDEGG</t>
         </is>
       </c>
       <c r="I80" s="21" t="inlineStr">
         <is>
-          <t>The MARILLA Bed w/ Storage creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARILLA Bed w/ Storage supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J80" s="21" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="K80" s="21" t="inlineStr">
         <is>
-          <t>Twin Bed w/ Storage</t>
+          <t>Full Bed w/ Storage</t>
         </is>
       </c>
       <c r="L80" s="21" t="n"/>
@@ -12805,7 +12805,7 @@
       </c>
       <c r="N80" s="21" t="inlineStr">
         <is>
-          <t>FOA7256WH-T-1, FOA7256WH-T-2, FOA7256WH-T-3, CM-SR452-WH</t>
+          <t>FOA7256WH-F-1, FOA7256WH-F-2, FOA7256WH-F-3, CM-SR452-WH</t>
         </is>
       </c>
       <c r="O80" s="21" t="inlineStr">
@@ -12814,20 +12814,20 @@
         </is>
       </c>
       <c r="P80" s="21" t="n">
-        <v>439</v>
+        <v>519</v>
       </c>
       <c r="Q80" s="46" t="n">
-        <v>439</v>
+        <v>519</v>
       </c>
       <c r="R80" s="21" t="n">
-        <v>1167</v>
+        <v>1377</v>
       </c>
       <c r="S80" s="21" t="n">
-        <v>156.2</v>
+        <v>176</v>
       </c>
       <c r="T80" s="21" t="inlineStr">
         <is>
-          <t>86"L X 42 7/8"W X 46 5/8"H</t>
+          <t>86"L X 57 3/4"W X 46 5/8"H</t>
         </is>
       </c>
       <c r="U80" s="21" t="inlineStr">
@@ -12854,7 +12854,7 @@
       <c r="Z80" s="21" t="n"/>
       <c r="AA80" s="21" t="n"/>
       <c r="AB80" s="21" t="n">
-        <v>23.5</v>
+        <v>26.7</v>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="B81" s="29" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C81" s="29" t="inlineStr">
         <is>
-          <t>CM7467WH-F-BED+TR</t>
+          <t>CM7467WH-T-BED+TR</t>
         </is>
       </c>
       <c r="D81" s="29" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="H81" s="29" t="inlineStr">
         <is>
-          <t>PRIAM Bed w/ Trundle Full in White | GOODDEGG</t>
+          <t>PRIAM Bed w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I81" s="29" t="inlineStr">
         <is>
-          <t>The PRIAM Bed w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PRIAM Bed w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J81" s="29" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="K81" s="29" t="inlineStr">
         <is>
-          <t>Full Bed w/ Trundle</t>
+          <t>Twin Bed w/ Trundle</t>
         </is>
       </c>
       <c r="L81" s="29" t="inlineStr">
@@ -12957,29 +12957,29 @@
       </c>
       <c r="N81" s="29" t="inlineStr">
         <is>
-          <t>CM7467WH-F-HBFB, CM7467WH-F-R, CM7467WH-TR</t>
+          <t>CM7467WH-T-HBFB, CM7467WH-T-R, CM7467WH-TR</t>
         </is>
       </c>
       <c r="O81" s="29" t="inlineStr">
         <is>
-          <t>CM7467WH-1.jpg,CM7467WH-D-2.jpg,CM7467WH-D-3.jpg,CM7467WH-T-3.jpg</t>
+          <t>CM7467WH-T-1.jpg,CM7467WH-D-2.jpg,CM7467WH-D-3.jpg,CM7467WH-T-3.jpg</t>
         </is>
       </c>
       <c r="P81" s="29" t="n">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="Q81" s="30" t="n">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="R81" s="29" t="n">
-        <v>807</v>
+        <v>717</v>
       </c>
       <c r="S81" s="29" t="n">
-        <v>195.3</v>
+        <v>172</v>
       </c>
       <c r="T81" s="29" t="inlineStr">
         <is>
-          <t>56"W X 79.5"D X 50"H</t>
+          <t>41.5"W X 79.5"D X 50"H</t>
         </is>
       </c>
       <c r="U81" s="29" t="inlineStr">
@@ -13006,7 +13006,7 @@
       <c r="Z81" s="29" t="n"/>
       <c r="AA81" s="29" t="n"/>
       <c r="AB81" s="29" t="n">
-        <v>12.5</v>
+        <v>10.7</v>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
@@ -13042,12 +13042,12 @@
       </c>
       <c r="B82" s="29" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="C82" s="29" t="inlineStr">
         <is>
-          <t>CM7467WH-T-BED+TR</t>
+          <t>CM7467WH-F-BED+TR</t>
         </is>
       </c>
       <c r="D82" s="29" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H82" s="29" t="inlineStr">
         <is>
-          <t>PRIAM Bed w/ Trundle Twin in White | GOODDEGG</t>
+          <t>PRIAM Bed w/ Trundle | GOODDEGG</t>
         </is>
       </c>
       <c r="I82" s="29" t="inlineStr">
         <is>
-          <t>The PRIAM Bed w/ Trundle creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PRIAM Bed w/ Trundle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J82" s="29" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K82" s="29" t="inlineStr">
         <is>
-          <t>Twin Bed w/ Trundle</t>
+          <t>Full Bed w/ Trundle</t>
         </is>
       </c>
       <c r="L82" s="29" t="inlineStr">
@@ -13109,29 +13109,29 @@
       </c>
       <c r="N82" s="29" t="inlineStr">
         <is>
-          <t>CM7467WH-T-HBFB, CM7467WH-T-R, CM7467WH-TR</t>
+          <t>CM7467WH-F-HBFB, CM7467WH-F-R, CM7467WH-TR</t>
         </is>
       </c>
       <c r="O82" s="29" t="inlineStr">
         <is>
-          <t>CM7467WH-T-1.jpg,CM7467WH-D-2.jpg,CM7467WH-D-3.jpg,CM7467WH-T-3.jpg</t>
+          <t>CM7467WH-1.jpg,CM7467WH-D-2.jpg,CM7467WH-D-3.jpg,CM7467WH-T-3.jpg</t>
         </is>
       </c>
       <c r="P82" s="29" t="n">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="Q82" s="30" t="n">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="R82" s="29" t="n">
-        <v>717</v>
+        <v>807</v>
       </c>
       <c r="S82" s="29" t="n">
-        <v>172</v>
+        <v>195.3</v>
       </c>
       <c r="T82" s="29" t="inlineStr">
         <is>
-          <t>41.5"W X 79.5"D X 50"H</t>
+          <t>56"W X 79.5"D X 50"H</t>
         </is>
       </c>
       <c r="U82" s="29" t="inlineStr">
@@ -13158,7 +13158,7 @@
       <c r="Z82" s="29" t="n"/>
       <c r="AA82" s="29" t="n"/>
       <c r="AB82" s="29" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
